--- a/Catch models/cmsy_out_macarellus_cmsy.xlsx
+++ b/Catch models/cmsy_out_macarellus_cmsy.xlsx
@@ -897,7 +897,7 @@
         <v>0.1</v>
       </c>
       <c r="L2">
-        <v>0.4915354416004519</v>
+        <v>0.491675852849026</v>
       </c>
       <c r="M2">
         <v>1.5</v>
@@ -906,133 +906,133 @@
         <v>0.1</v>
       </c>
       <c r="O2">
-        <v>0.1671930735693909</v>
+        <v>0.1541836166563351</v>
       </c>
       <c r="P2">
-        <v>0.28</v>
+        <v>0.25</v>
       </c>
       <c r="Q2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R2">
-        <v>28.78777785649794</v>
+        <v>23.54940713793097</v>
       </c>
       <c r="S2">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="T2">
-        <v>31.53</v>
+        <v>22.78</v>
       </c>
       <c r="U2">
-        <v>51.13096362285511</v>
+        <v>41.42459946873139</v>
       </c>
       <c r="V2">
-        <v>74.92</v>
+        <v>62.14</v>
       </c>
       <c r="W2">
         <v>0.01</v>
       </c>
       <c r="X2">
-        <v>0.5053773919063651</v>
+        <v>0.5048356154464563</v>
       </c>
       <c r="Y2">
         <v>1</v>
       </c>
       <c r="Z2">
-        <v>0.16</v>
+        <v>0.09</v>
       </c>
       <c r="AA2">
-        <v>0.5195527665774432</v>
+        <v>0.4403198319832484</v>
       </c>
       <c r="AB2">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AC2">
-        <v>1.7</v>
+        <v>1.37</v>
       </c>
       <c r="AD2">
-        <v>2.1306</v>
+        <v>1.7104614</v>
       </c>
       <c r="AE2">
-        <v>2.56</v>
+        <v>2.05</v>
       </c>
       <c r="AF2">
-        <v>1.38</v>
+        <v>1.11</v>
       </c>
       <c r="AG2">
-        <v>2.1</v>
+        <v>1.49</v>
       </c>
       <c r="AH2">
-        <v>2.95</v>
+        <v>2.07</v>
       </c>
       <c r="AI2">
         <v>0.05</v>
       </c>
       <c r="AJ2">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AK2">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AL2">
-        <v>15.76</v>
+        <v>11.39</v>
       </c>
       <c r="AM2">
-        <v>21.1</v>
+        <v>16.24</v>
       </c>
       <c r="AN2">
-        <v>37.46</v>
+        <v>31.07</v>
       </c>
       <c r="AO2">
-        <v>0.64</v>
+        <v>0.06</v>
       </c>
       <c r="AP2">
-        <v>1.56</v>
+        <v>0.17</v>
       </c>
       <c r="AQ2">
-        <v>0.14</v>
+        <v>0.06</v>
       </c>
       <c r="AR2">
-        <v>0.32</v>
+        <v>0.12</v>
       </c>
       <c r="AS2">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AT2">
-        <v>0.32</v>
+        <v>0.18</v>
       </c>
       <c r="AU2">
-        <v>1.06</v>
+        <v>0.9</v>
       </c>
       <c r="AV2">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AW2">
-        <v>0.18</v>
+        <v>0.136</v>
       </c>
       <c r="AX2">
-        <v>0.576</v>
+        <v>0.631</v>
       </c>
       <c r="AY2">
-        <v>0.311</v>
+        <v>0.265</v>
       </c>
       <c r="AZ2">
-        <v>0.606</v>
+        <v>0.537</v>
       </c>
       <c r="BA2">
-        <v>0.303</v>
+        <v>0.379</v>
       </c>
       <c r="BB2">
-        <v>0.45</v>
+        <v>0.385</v>
       </c>
       <c r="BC2">
-        <v>0.725</v>
+        <v>0.736</v>
       </c>
       <c r="BD2">
-        <v>0.925</v>
+        <v>0.914</v>
       </c>
       <c r="BE2">
-        <v>0.733</v>
+        <v>0.619</v>
       </c>
       <c r="BF2">
         <v>-0.9485599924429405</v>
@@ -1041,10 +1041,10 @@
         <v>0.6770125502755524</v>
       </c>
       <c r="BH2">
-        <v>3.099664465708683</v>
+        <v>2.875714737352825</v>
       </c>
       <c r="BI2">
-        <v>0.729571897151486</v>
+        <v>0.7512147970114545</v>
       </c>
     </row>
     <row r="3" spans="1:61">
@@ -1079,157 +1079,157 @@
         <v>69</v>
       </c>
       <c r="K3">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="L3">
-        <v>0.5011611356473387</v>
+        <v>0.6489503689411591</v>
       </c>
       <c r="M3">
-        <v>0.79</v>
+        <v>1</v>
       </c>
       <c r="N3">
-        <v>0.3</v>
+        <v>0.35</v>
       </c>
       <c r="O3">
-        <v>0.4150138503251474</v>
+        <v>0.486216409352817</v>
       </c>
       <c r="P3">
-        <v>0.59</v>
+        <v>0.68</v>
       </c>
       <c r="Q3">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="R3">
-        <v>18.74806698348622</v>
+        <v>11.76860740953261</v>
       </c>
       <c r="S3">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="T3">
-        <v>14.96</v>
+        <v>9.23</v>
       </c>
       <c r="U3">
-        <v>21.15268230730636</v>
+        <v>12.36288515201704</v>
       </c>
       <c r="V3">
-        <v>28.46</v>
+        <v>15.89</v>
       </c>
       <c r="W3">
         <v>0.01</v>
       </c>
       <c r="X3">
-        <v>0.5007563559659175</v>
+        <v>0.5101571285450368</v>
       </c>
       <c r="Y3">
         <v>1</v>
       </c>
       <c r="Z3">
-        <v>0.2</v>
+        <v>0.23</v>
       </c>
       <c r="AA3">
-        <v>0.5355136341257407</v>
+        <v>0.6604505475331751</v>
       </c>
       <c r="AB3">
-        <v>0.86</v>
+        <v>0.95</v>
       </c>
       <c r="AC3">
-        <v>1.7</v>
+        <v>1.37</v>
       </c>
       <c r="AD3">
-        <v>2.1306</v>
+        <v>1.7104614</v>
       </c>
       <c r="AE3">
-        <v>2.56</v>
+        <v>2.05</v>
       </c>
       <c r="AF3">
-        <v>1.74</v>
+        <v>1.26</v>
       </c>
       <c r="AG3">
-        <v>2.25</v>
+        <v>1.5</v>
       </c>
       <c r="AH3">
-        <v>2.84</v>
+        <v>1.71</v>
       </c>
       <c r="AI3">
-        <v>0.15</v>
+        <v>0.17</v>
       </c>
       <c r="AJ3">
-        <v>0.23</v>
+        <v>0.27</v>
       </c>
       <c r="AK3">
+        <v>0.34</v>
+      </c>
+      <c r="AL3">
+        <v>4.62</v>
+      </c>
+      <c r="AM3">
+        <v>5.65</v>
+      </c>
+      <c r="AN3">
+        <v>7.94</v>
+      </c>
+      <c r="AO3">
+        <v>0.06</v>
+      </c>
+      <c r="AP3">
+        <v>0.17</v>
+      </c>
+      <c r="AQ3">
+        <v>0.05</v>
+      </c>
+      <c r="AR3">
+        <v>0.08</v>
+      </c>
+      <c r="AS3">
         <v>0.29</v>
       </c>
-      <c r="AL3">
-        <v>7.48</v>
-      </c>
-      <c r="AM3">
-        <v>9.74</v>
-      </c>
-      <c r="AN3">
-        <v>14.23</v>
-      </c>
-      <c r="AO3">
-        <v>0.64</v>
-      </c>
-      <c r="AP3">
-        <v>1.56</v>
-      </c>
-      <c r="AQ3">
-        <v>0.13</v>
-      </c>
-      <c r="AR3">
-        <v>0.3</v>
-      </c>
-      <c r="AS3">
-        <v>1.17</v>
-      </c>
       <c r="AT3">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="AU3">
-        <v>1.07</v>
+        <v>1.41</v>
       </c>
       <c r="AV3">
-        <v>1.72</v>
+        <v>1.9</v>
       </c>
       <c r="AW3">
-        <v>0.589</v>
+        <v>0.66</v>
       </c>
       <c r="AX3">
-        <v>0.232</v>
+        <v>0.188</v>
       </c>
       <c r="AY3">
-        <v>0.666</v>
+        <v>0.498</v>
       </c>
       <c r="AZ3">
-        <v>0.903</v>
+        <v>0.786</v>
       </c>
       <c r="BA3">
-        <v>0.356</v>
+        <v>0.737</v>
       </c>
       <c r="BB3">
-        <v>0.404</v>
+        <v>0.141</v>
       </c>
       <c r="BC3">
-        <v>0.775</v>
+        <v>0.723</v>
       </c>
       <c r="BD3">
-        <v>0.945</v>
+        <v>0.9370000000000001</v>
       </c>
       <c r="BE3">
-        <v>0.758</v>
+        <v>0.582</v>
       </c>
       <c r="BF3">
-        <v>-0.719847568923503</v>
+        <v>-0.4581453659370775</v>
       </c>
       <c r="BG3">
-        <v>0.2420626177012166</v>
+        <v>0.2290726829685387</v>
       </c>
       <c r="BH3">
-        <v>2.853192576856886</v>
+        <v>2.390251899774196</v>
       </c>
       <c r="BI3">
-        <v>0.3833308252405199</v>
+        <v>0.3710831562350971</v>
       </c>
     </row>
     <row r="4" spans="1:61">
@@ -1267,154 +1267,154 @@
         <v>0.05</v>
       </c>
       <c r="L4">
-        <v>0.1594241274384801</v>
+        <v>0.2154609734743236</v>
       </c>
       <c r="M4">
-        <v>0.39</v>
+        <v>0.6</v>
       </c>
       <c r="N4">
         <v>0.05</v>
       </c>
       <c r="O4">
-        <v>0.08022786577436851</v>
+        <v>0.07692141890233418</v>
       </c>
       <c r="P4">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="Q4">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="R4">
-        <v>74.37858766769642</v>
+        <v>49.17004767989699</v>
       </c>
       <c r="S4">
-        <v>201</v>
+        <v>156</v>
       </c>
       <c r="T4">
-        <v>71.06</v>
+        <v>51.04</v>
       </c>
       <c r="U4">
-        <v>114.833414275845</v>
+        <v>85.5576451004337</v>
       </c>
       <c r="V4">
-        <v>168.3</v>
+        <v>128.06</v>
       </c>
       <c r="W4">
         <v>0.01</v>
       </c>
       <c r="X4">
-        <v>0.5032829462605021</v>
+        <v>0.5113909820946287</v>
       </c>
       <c r="Y4">
         <v>1</v>
       </c>
       <c r="Z4">
-        <v>0.27</v>
+        <v>0.1</v>
       </c>
       <c r="AA4">
-        <v>0.5395963785102903</v>
+        <v>0.3596237132106905</v>
       </c>
       <c r="AB4">
-        <v>0.85</v>
+        <v>0.66</v>
       </c>
       <c r="AC4">
-        <v>1.7</v>
+        <v>1.37</v>
       </c>
       <c r="AD4">
-        <v>2.1306</v>
+        <v>1.7104614</v>
       </c>
       <c r="AE4">
-        <v>2.56</v>
+        <v>2.05</v>
       </c>
       <c r="AF4">
-        <v>1.46</v>
+        <v>1.05</v>
       </c>
       <c r="AG4">
-        <v>2.22</v>
+        <v>1.56</v>
       </c>
       <c r="AH4">
-        <v>3.29</v>
+        <v>2.3</v>
       </c>
       <c r="AI4">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="AJ4">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="AK4">
         <v>0.06</v>
       </c>
       <c r="AL4">
-        <v>35.53</v>
+        <v>25.52</v>
       </c>
       <c r="AM4">
-        <v>48.14</v>
+        <v>35.29</v>
       </c>
       <c r="AN4">
-        <v>84.15000000000001</v>
+        <v>64.03</v>
       </c>
       <c r="AO4">
-        <v>0.64</v>
+        <v>0.06</v>
       </c>
       <c r="AP4">
-        <v>1.56</v>
+        <v>0.17</v>
       </c>
       <c r="AQ4">
-        <v>0.13</v>
+        <v>0.06</v>
       </c>
       <c r="AR4">
-        <v>0.29</v>
+        <v>0.15</v>
       </c>
       <c r="AS4">
-        <v>0.77</v>
+        <v>1.54</v>
       </c>
       <c r="AT4">
-        <v>0.54</v>
+        <v>0.19</v>
       </c>
       <c r="AU4">
-        <v>1.07</v>
+        <v>0.71</v>
       </c>
       <c r="AV4">
-        <v>1.7</v>
+        <v>1.32</v>
       </c>
       <c r="AW4">
-        <v>0.261</v>
+        <v>0.165</v>
       </c>
       <c r="AX4">
-        <v>0.489</v>
+        <v>0.594</v>
       </c>
       <c r="AY4">
-        <v>0.411</v>
+        <v>0.291</v>
       </c>
       <c r="AZ4">
-        <v>0.703</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="BA4">
-        <v>0.246</v>
+        <v>0.294</v>
       </c>
       <c r="BB4">
-        <v>0.504</v>
+        <v>0.458</v>
       </c>
       <c r="BC4">
-        <v>0.657</v>
+        <v>0.644</v>
       </c>
       <c r="BD4">
-        <v>0.897</v>
+        <v>0.858</v>
       </c>
       <c r="BE4">
-        <v>0.786</v>
+        <v>0.68</v>
       </c>
       <c r="BF4">
-        <v>-1.968670406706218</v>
+        <v>-1.753278948659991</v>
       </c>
       <c r="BG4">
-        <v>0.5135309334238864</v>
+        <v>0.621226662447</v>
       </c>
       <c r="BH4">
-        <v>4.125433587046269</v>
+        <v>3.672524970449063</v>
       </c>
       <c r="BI4">
-        <v>0.5882525383053667</v>
+        <v>0.688346914557648</v>
       </c>
     </row>
     <row r="5" spans="1:61">
@@ -1449,157 +1449,157 @@
         <v>69</v>
       </c>
       <c r="K5">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="L5">
-        <v>0.268223419918096</v>
+        <v>0.4230288165789025</v>
       </c>
       <c r="M5">
-        <v>0.59</v>
+        <v>0.8</v>
       </c>
       <c r="N5">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="O5">
-        <v>0.1544550552189288</v>
+        <v>0.2572141999587597</v>
       </c>
       <c r="P5">
-        <v>0.24</v>
+        <v>0.39</v>
       </c>
       <c r="Q5">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="R5">
-        <v>40.86734846360184</v>
+        <v>19.35678174798427</v>
       </c>
       <c r="S5">
-        <v>103</v>
+        <v>43</v>
       </c>
       <c r="T5">
-        <v>34.94</v>
+        <v>14.75</v>
       </c>
       <c r="U5">
-        <v>56.11484301271222</v>
+        <v>21.36212428246962</v>
       </c>
       <c r="V5">
-        <v>81.87</v>
+        <v>28.89</v>
       </c>
       <c r="W5">
         <v>0.01</v>
       </c>
       <c r="X5">
-        <v>0.507172954457795</v>
+        <v>0.5068518019025201</v>
       </c>
       <c r="Y5">
         <v>1</v>
       </c>
       <c r="Z5">
-        <v>0.16</v>
+        <v>0.19</v>
       </c>
       <c r="AA5">
-        <v>0.5238686762749902</v>
+        <v>0.5375897654080184</v>
       </c>
       <c r="AB5">
-        <v>0.82</v>
+        <v>0.87</v>
       </c>
       <c r="AC5">
-        <v>1.7</v>
+        <v>1.37</v>
       </c>
       <c r="AD5">
-        <v>2.1306</v>
+        <v>1.7104614</v>
       </c>
       <c r="AE5">
-        <v>2.56</v>
+        <v>2.05</v>
       </c>
       <c r="AF5">
-        <v>1.44</v>
+        <v>1.06</v>
       </c>
       <c r="AG5">
-        <v>2.11</v>
+        <v>1.41</v>
       </c>
       <c r="AH5">
-        <v>3.06</v>
+        <v>1.72</v>
       </c>
       <c r="AI5">
+        <v>0.09</v>
+      </c>
+      <c r="AJ5">
+        <v>0.14</v>
+      </c>
+      <c r="AK5">
+        <v>0.19</v>
+      </c>
+      <c r="AL5">
+        <v>7.38</v>
+      </c>
+      <c r="AM5">
+        <v>9.779999999999999</v>
+      </c>
+      <c r="AN5">
+        <v>14.44</v>
+      </c>
+      <c r="AO5">
+        <v>0.06</v>
+      </c>
+      <c r="AP5">
+        <v>0.17</v>
+      </c>
+      <c r="AQ5">
         <v>0.05</v>
       </c>
-      <c r="AJ5">
-        <v>0.09</v>
-      </c>
-      <c r="AK5">
-        <v>0.12</v>
-      </c>
-      <c r="AL5">
-        <v>17.47</v>
-      </c>
-      <c r="AM5">
-        <v>24.37</v>
-      </c>
-      <c r="AN5">
-        <v>40.93</v>
-      </c>
-      <c r="AO5">
-        <v>0.64</v>
-      </c>
-      <c r="AP5">
-        <v>1.56</v>
-      </c>
-      <c r="AQ5">
-        <v>0.14</v>
-      </c>
       <c r="AR5">
-        <v>0.31</v>
+        <v>0.11</v>
       </c>
       <c r="AS5">
-        <v>2.12</v>
+        <v>0.43</v>
       </c>
       <c r="AT5">
-        <v>0.32</v>
+        <v>0.38</v>
       </c>
       <c r="AU5">
         <v>1.07</v>
       </c>
       <c r="AV5">
-        <v>1.65</v>
+        <v>1.74</v>
       </c>
       <c r="AW5">
-        <v>0.297</v>
+        <v>0.376</v>
       </c>
       <c r="AX5">
-        <v>0.455</v>
+        <v>0.387</v>
       </c>
       <c r="AY5">
-        <v>0.447</v>
+        <v>0.404</v>
       </c>
       <c r="AZ5">
-        <v>0.731</v>
+        <v>0.6870000000000001</v>
       </c>
       <c r="BA5">
-        <v>0.28</v>
+        <v>0.327</v>
       </c>
       <c r="BB5">
-        <v>0.471</v>
+        <v>0.428</v>
       </c>
       <c r="BC5">
-        <v>0.68</v>
+        <v>0.716</v>
       </c>
       <c r="BD5">
-        <v>0.919</v>
+        <v>0.93</v>
       </c>
       <c r="BE5">
-        <v>0.795</v>
+        <v>0.642</v>
       </c>
       <c r="BF5">
-        <v>-1.415108917538209</v>
+        <v>-0.916290731874155</v>
       </c>
       <c r="BG5">
-        <v>0.4437380877279183</v>
+        <v>0.3465735902799726</v>
       </c>
       <c r="BH5">
-        <v>3.567482311287568</v>
+        <v>2.850400664966368</v>
       </c>
       <c r="BI5">
-        <v>0.5350075755156646</v>
+        <v>0.4550732019756537</v>
       </c>
     </row>
     <row r="6" spans="1:61">
@@ -1637,142 +1637,142 @@
         <v>0.1</v>
       </c>
       <c r="L6">
-        <v>0.4857400590928166</v>
+        <v>0.4810072577223167</v>
       </c>
       <c r="M6">
         <v>1.5</v>
       </c>
       <c r="N6">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="O6">
-        <v>0.1643931267738514</v>
+        <v>0.141961907142805</v>
       </c>
       <c r="P6">
-        <v>0.26</v>
+        <v>0.24</v>
       </c>
       <c r="Q6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R6">
-        <v>28.39122793570717</v>
+        <v>23.71850153060247</v>
       </c>
       <c r="S6">
-        <v>93</v>
+        <v>77</v>
       </c>
       <c r="T6">
-        <v>31.34</v>
+        <v>22.41</v>
       </c>
       <c r="U6">
-        <v>49.8483878901657</v>
+        <v>38.79766015777813</v>
       </c>
       <c r="V6">
-        <v>73.31</v>
+        <v>58.46</v>
       </c>
       <c r="W6">
         <v>0.2</v>
       </c>
       <c r="X6">
-        <v>0.4509848316005128</v>
+        <v>0.4493045480402115</v>
       </c>
       <c r="Y6">
         <v>0.7</v>
       </c>
       <c r="Z6">
-        <v>0.28</v>
+        <v>0.22</v>
       </c>
       <c r="AA6">
-        <v>0.4872763313970561</v>
+        <v>0.4191014617982123</v>
       </c>
       <c r="AB6">
-        <v>0.6899999999999999</v>
+        <v>0.6</v>
       </c>
       <c r="AC6">
-        <v>1.7</v>
+        <v>1.37</v>
       </c>
       <c r="AD6">
-        <v>2.1306</v>
+        <v>1.7104614</v>
       </c>
       <c r="AE6">
-        <v>2.56</v>
+        <v>2.05</v>
       </c>
       <c r="AF6">
-        <v>1.44</v>
+        <v>0.95</v>
       </c>
       <c r="AG6">
-        <v>2.01</v>
+        <v>1.35</v>
       </c>
       <c r="AH6">
-        <v>2.71</v>
+        <v>1.86</v>
       </c>
       <c r="AI6">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="AJ6">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AK6">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="AL6">
-        <v>15.67</v>
+        <v>11.21</v>
       </c>
       <c r="AM6">
-        <v>21.71</v>
+        <v>16.02</v>
       </c>
       <c r="AN6">
-        <v>36.65</v>
+        <v>29.23</v>
       </c>
       <c r="AO6">
-        <v>0.64</v>
+        <v>0.06</v>
       </c>
       <c r="AP6">
-        <v>1.56</v>
+        <v>0.17</v>
       </c>
       <c r="AQ6">
-        <v>0.18</v>
+        <v>0.08</v>
       </c>
       <c r="AR6">
-        <v>0.35</v>
+        <v>0.15</v>
       </c>
       <c r="AS6">
-        <v>0.8</v>
+        <v>0.37</v>
       </c>
       <c r="AT6">
-        <v>0.5600000000000001</v>
+        <v>0.45</v>
       </c>
       <c r="AU6">
-        <v>0.98</v>
+        <v>0.84</v>
       </c>
       <c r="AV6">
-        <v>1.38</v>
+        <v>1.21</v>
       </c>
       <c r="AW6">
-        <v>0.152</v>
+        <v>0.157</v>
       </c>
       <c r="AX6">
-        <v>0.61</v>
+        <v>0.604</v>
       </c>
       <c r="AY6">
-        <v>0.292</v>
+        <v>0.242</v>
       </c>
       <c r="AZ6">
-        <v>0.5610000000000001</v>
+        <v>0.522</v>
       </c>
       <c r="BA6">
-        <v>0.657</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="BB6">
-        <v>0.189</v>
+        <v>0.247</v>
       </c>
       <c r="BC6">
-        <v>0.845</v>
+        <v>0.838</v>
       </c>
       <c r="BD6">
-        <v>0.977</v>
+        <v>0.969</v>
       </c>
       <c r="BE6">
-        <v>0.242</v>
+        <v>0.124</v>
       </c>
       <c r="BF6">
         <v>-0.9485599924429405</v>
@@ -1781,10 +1781,10 @@
         <v>0.6770125502755524</v>
       </c>
       <c r="BH6">
-        <v>3.071908211823252</v>
+        <v>2.889246458864603</v>
       </c>
       <c r="BI6">
-        <v>0.7326917185750288</v>
+        <v>0.7300315680902167</v>
       </c>
     </row>
     <row r="7" spans="1:61">
@@ -1819,157 +1819,157 @@
         <v>81</v>
       </c>
       <c r="K7">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="L7">
-        <v>0.5020840068300791</v>
+        <v>0.6453522843629236</v>
       </c>
       <c r="M7">
-        <v>0.79</v>
+        <v>1</v>
       </c>
       <c r="N7">
-        <v>0.3</v>
+        <v>0.34</v>
       </c>
       <c r="O7">
-        <v>0.4044838341079494</v>
+        <v>0.451968778307284</v>
       </c>
       <c r="P7">
-        <v>0.5600000000000001</v>
+        <v>0.61</v>
       </c>
       <c r="Q7">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="R7">
-        <v>18.77575642462946</v>
+        <v>11.83398262644842</v>
       </c>
       <c r="S7">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="T7">
-        <v>15</v>
+        <v>10.03</v>
       </c>
       <c r="U7">
-        <v>20.73541877664977</v>
+        <v>12.96679646573161</v>
       </c>
       <c r="V7">
-        <v>27.26</v>
+        <v>16.29</v>
       </c>
       <c r="W7">
         <v>0.2</v>
       </c>
       <c r="X7">
-        <v>0.4477857415844201</v>
+        <v>0.4513492008437517</v>
       </c>
       <c r="Y7">
         <v>0.7</v>
       </c>
       <c r="Z7">
-        <v>0.26</v>
+        <v>0.24</v>
       </c>
       <c r="AA7">
-        <v>0.4775918304257069</v>
+        <v>0.5450466723391323</v>
       </c>
       <c r="AB7">
-        <v>0.6899999999999999</v>
+        <v>0.77</v>
       </c>
       <c r="AC7">
-        <v>1.7</v>
+        <v>1.37</v>
       </c>
       <c r="AD7">
-        <v>2.1306</v>
+        <v>1.7104614</v>
       </c>
       <c r="AE7">
-        <v>2.56</v>
+        <v>2.05</v>
       </c>
       <c r="AF7">
-        <v>1.74</v>
+        <v>1.24</v>
       </c>
       <c r="AG7">
-        <v>2.11</v>
+        <v>1.48</v>
       </c>
       <c r="AH7">
-        <v>2.48</v>
+        <v>1.67</v>
       </c>
       <c r="AI7">
-        <v>0.15</v>
+        <v>0.17</v>
       </c>
       <c r="AJ7">
-        <v>0.22</v>
+        <v>0.24</v>
       </c>
       <c r="AK7">
-        <v>0.28</v>
+        <v>0.3</v>
       </c>
       <c r="AL7">
-        <v>7.5</v>
+        <v>5.01</v>
       </c>
       <c r="AM7">
-        <v>9.5</v>
+        <v>6.04</v>
       </c>
       <c r="AN7">
-        <v>13.63</v>
+        <v>8.15</v>
       </c>
       <c r="AO7">
-        <v>0.64</v>
+        <v>0.06</v>
       </c>
       <c r="AP7">
-        <v>1.56</v>
+        <v>0.17</v>
       </c>
       <c r="AQ7">
-        <v>0.19</v>
+        <v>0.06</v>
       </c>
       <c r="AR7">
-        <v>0.34</v>
+        <v>0.1</v>
       </c>
       <c r="AS7">
-        <v>0.77</v>
+        <v>0.25</v>
       </c>
       <c r="AT7">
-        <v>0.52</v>
+        <v>0.48</v>
       </c>
       <c r="AU7">
-        <v>0.96</v>
+        <v>1.13</v>
       </c>
       <c r="AV7">
-        <v>1.38</v>
+        <v>1.53</v>
       </c>
       <c r="AW7">
-        <v>0.505</v>
+        <v>0.486</v>
       </c>
       <c r="AX7">
-        <v>0.289</v>
+        <v>0.303</v>
       </c>
       <c r="AY7">
-        <v>0.613</v>
+        <v>0.378</v>
       </c>
       <c r="AZ7">
-        <v>0.868</v>
+        <v>0.67</v>
       </c>
       <c r="BA7">
-        <v>0.747</v>
+        <v>1.082</v>
       </c>
       <c r="BB7">
-        <v>0.135</v>
+        <v>-0.04</v>
       </c>
       <c r="BC7">
-        <v>0.872</v>
+        <v>0.671</v>
       </c>
       <c r="BD7">
-        <v>0.986</v>
+        <v>0.9320000000000001</v>
       </c>
       <c r="BE7">
-        <v>0.296</v>
+        <v>0.04</v>
       </c>
       <c r="BF7">
-        <v>-0.719847568923503</v>
+        <v>-0.4581453659370775</v>
       </c>
       <c r="BG7">
-        <v>0.2420626177012166</v>
+        <v>0.2290726829685387</v>
       </c>
       <c r="BH7">
-        <v>2.854893731005248</v>
+        <v>2.3873081824834</v>
       </c>
       <c r="BI7">
-        <v>0.3835717865081756</v>
+        <v>0.3737833072133447</v>
       </c>
     </row>
     <row r="8" spans="1:61">
@@ -2007,154 +2007,154 @@
         <v>0.05</v>
       </c>
       <c r="L8">
-        <v>0.1614086438308021</v>
+        <v>0.2103511494347962</v>
       </c>
       <c r="M8">
-        <v>0.39</v>
+        <v>0.6</v>
       </c>
       <c r="N8">
         <v>0.05</v>
       </c>
       <c r="O8">
-        <v>0.07953337404776999</v>
+        <v>0.07513850728983745</v>
       </c>
       <c r="P8">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="Q8">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="R8">
-        <v>72.70313695842322</v>
+        <v>51.28831068419486</v>
       </c>
       <c r="S8">
-        <v>201</v>
+        <v>156</v>
       </c>
       <c r="T8">
-        <v>70.65000000000001</v>
+        <v>52.44</v>
       </c>
       <c r="U8">
-        <v>112.7274236324106</v>
+        <v>88.02675496729147</v>
       </c>
       <c r="V8">
-        <v>165.35</v>
+        <v>130.73</v>
       </c>
       <c r="W8">
         <v>0.2</v>
       </c>
       <c r="X8">
-        <v>0.4490391659585528</v>
+        <v>0.4501295422533491</v>
       </c>
       <c r="Y8">
         <v>0.7</v>
       </c>
       <c r="Z8">
-        <v>0.28</v>
+        <v>0.23</v>
       </c>
       <c r="AA8">
-        <v>0.4923645875091819</v>
+        <v>0.40552801320639</v>
       </c>
       <c r="AB8">
-        <v>0.6899999999999999</v>
+        <v>0.59</v>
       </c>
       <c r="AC8">
-        <v>1.7</v>
+        <v>1.37</v>
       </c>
       <c r="AD8">
-        <v>2.1306</v>
+        <v>1.7104614</v>
       </c>
       <c r="AE8">
-        <v>2.56</v>
+        <v>2.05</v>
       </c>
       <c r="AF8">
-        <v>1.45</v>
+        <v>1.07</v>
       </c>
       <c r="AG8">
-        <v>2.16</v>
+        <v>1.56</v>
       </c>
       <c r="AH8">
-        <v>3.15</v>
+        <v>2.33</v>
       </c>
       <c r="AI8">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="AJ8">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="AK8">
         <v>0.06</v>
       </c>
       <c r="AL8">
-        <v>35.33</v>
+        <v>26.22</v>
       </c>
       <c r="AM8">
-        <v>47.84</v>
+        <v>36.14</v>
       </c>
       <c r="AN8">
-        <v>82.67</v>
+        <v>65.36</v>
       </c>
       <c r="AO8">
-        <v>0.64</v>
+        <v>0.06</v>
       </c>
       <c r="AP8">
-        <v>1.56</v>
+        <v>0.17</v>
       </c>
       <c r="AQ8">
-        <v>0.16</v>
+        <v>0.06</v>
       </c>
       <c r="AR8">
-        <v>0.32</v>
+        <v>0.13</v>
       </c>
       <c r="AS8">
-        <v>0.73</v>
+        <v>0.28</v>
       </c>
       <c r="AT8">
-        <v>0.5600000000000001</v>
+        <v>0.46</v>
       </c>
       <c r="AU8">
-        <v>0.99</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AV8">
-        <v>1.38</v>
+        <v>1.18</v>
       </c>
       <c r="AW8">
-        <v>0.237</v>
+        <v>0.165</v>
       </c>
       <c r="AX8">
-        <v>0.513</v>
+        <v>0.594</v>
       </c>
       <c r="AY8">
-        <v>0.386</v>
+        <v>0.291</v>
       </c>
       <c r="AZ8">
-        <v>0.674</v>
+        <v>0.57</v>
       </c>
       <c r="BA8">
-        <v>0.605</v>
+        <v>0.506</v>
       </c>
       <c r="BB8">
-        <v>0.222</v>
+        <v>0.288</v>
       </c>
       <c r="BC8">
-        <v>0.8070000000000001</v>
+        <v>0.784</v>
       </c>
       <c r="BD8">
-        <v>0.969</v>
+        <v>0.954</v>
       </c>
       <c r="BE8">
-        <v>0.427</v>
+        <v>0.262</v>
       </c>
       <c r="BF8">
-        <v>-1.968670406706218</v>
+        <v>-1.753278948659991</v>
       </c>
       <c r="BG8">
-        <v>0.5135309334238864</v>
+        <v>0.621226662447</v>
       </c>
       <c r="BH8">
-        <v>4.11667305995427</v>
+        <v>3.685176336563495</v>
       </c>
       <c r="BI8">
-        <v>0.5930296377400027</v>
+        <v>0.6832453480998351</v>
       </c>
     </row>
     <row r="9" spans="1:61">
@@ -2189,157 +2189,157 @@
         <v>81</v>
       </c>
       <c r="K9">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="L9">
-        <v>0.2693832296540138</v>
+        <v>0.4232690266053805</v>
       </c>
       <c r="M9">
-        <v>0.59</v>
+        <v>0.8</v>
       </c>
       <c r="N9">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="O9">
-        <v>0.1500757129805849</v>
+        <v>0.2517769179080505</v>
       </c>
       <c r="P9">
-        <v>0.23</v>
+        <v>0.37</v>
       </c>
       <c r="Q9">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="R9">
-        <v>40.05400563958715</v>
+        <v>19.03604960324683</v>
       </c>
       <c r="S9">
-        <v>100</v>
+        <v>42</v>
       </c>
       <c r="T9">
-        <v>34.86</v>
+        <v>14.78</v>
       </c>
       <c r="U9">
-        <v>54.9552603122402</v>
+        <v>21.37778594006091</v>
       </c>
       <c r="V9">
-        <v>79.34</v>
+        <v>28.65</v>
       </c>
       <c r="W9">
         <v>0.2</v>
       </c>
       <c r="X9">
-        <v>0.4489347457768512</v>
+        <v>0.4481053744470482</v>
       </c>
       <c r="Y9">
         <v>0.7</v>
       </c>
       <c r="Z9">
+        <v>0.27</v>
+      </c>
+      <c r="AA9">
+        <v>0.4859006883017687</v>
+      </c>
+      <c r="AB9">
+        <v>0.7</v>
+      </c>
+      <c r="AC9">
+        <v>1.37</v>
+      </c>
+      <c r="AD9">
+        <v>1.7104614</v>
+      </c>
+      <c r="AE9">
+        <v>2.05</v>
+      </c>
+      <c r="AF9">
+        <v>1.06</v>
+      </c>
+      <c r="AG9">
+        <v>1.34</v>
+      </c>
+      <c r="AH9">
+        <v>1.62</v>
+      </c>
+      <c r="AI9">
+        <v>0.09</v>
+      </c>
+      <c r="AJ9">
+        <v>0.14</v>
+      </c>
+      <c r="AK9">
+        <v>0.19</v>
+      </c>
+      <c r="AL9">
+        <v>7.39</v>
+      </c>
+      <c r="AM9">
+        <v>9.640000000000001</v>
+      </c>
+      <c r="AN9">
+        <v>14.33</v>
+      </c>
+      <c r="AO9">
+        <v>0.06</v>
+      </c>
+      <c r="AP9">
+        <v>0.17</v>
+      </c>
+      <c r="AQ9">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="AR9">
+        <v>0.13</v>
+      </c>
+      <c r="AS9">
         <v>0.26</v>
       </c>
-      <c r="AA9">
-        <v>0.4766381378464563</v>
-      </c>
-      <c r="AB9">
-        <v>0.68</v>
-      </c>
-      <c r="AC9">
-        <v>1.7</v>
-      </c>
-      <c r="AD9">
-        <v>2.1306</v>
-      </c>
-      <c r="AE9">
-        <v>2.56</v>
-      </c>
-      <c r="AF9">
-        <v>1.43</v>
-      </c>
-      <c r="AG9">
-        <v>2.01</v>
-      </c>
-      <c r="AH9">
-        <v>2.76</v>
-      </c>
-      <c r="AI9">
-        <v>0.05</v>
-      </c>
-      <c r="AJ9">
-        <v>0.08</v>
-      </c>
-      <c r="AK9">
-        <v>0.12</v>
-      </c>
-      <c r="AL9">
-        <v>17.43</v>
-      </c>
-      <c r="AM9">
-        <v>23.77</v>
-      </c>
-      <c r="AN9">
-        <v>39.67</v>
-      </c>
-      <c r="AO9">
-        <v>0.64</v>
-      </c>
-      <c r="AP9">
-        <v>1.56</v>
-      </c>
-      <c r="AQ9">
-        <v>0.19</v>
-      </c>
-      <c r="AR9">
-        <v>0.36</v>
-      </c>
-      <c r="AS9">
-        <v>0.84</v>
-      </c>
       <c r="AT9">
-        <v>0.52</v>
+        <v>0.54</v>
       </c>
       <c r="AU9">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="AV9">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="AW9">
-        <v>0.279</v>
+        <v>0.345</v>
       </c>
       <c r="AX9">
-        <v>0.472</v>
+        <v>0.413</v>
       </c>
       <c r="AY9">
-        <v>0.427</v>
+        <v>0.369</v>
       </c>
       <c r="AZ9">
-        <v>0.716</v>
+        <v>0.67</v>
       </c>
       <c r="BA9">
-        <v>0.658</v>
+        <v>0.678</v>
       </c>
       <c r="BB9">
-        <v>0.189</v>
+        <v>0.177</v>
       </c>
       <c r="BC9">
-        <v>0.855</v>
+        <v>0.85</v>
       </c>
       <c r="BD9">
-        <v>0.981</v>
+        <v>0.977</v>
       </c>
       <c r="BE9">
-        <v>0.385</v>
+        <v>0.11</v>
       </c>
       <c r="BF9">
-        <v>-1.415108917538209</v>
+        <v>-0.916290731874155</v>
       </c>
       <c r="BG9">
-        <v>0.4437380877279183</v>
+        <v>0.3465735902799726</v>
       </c>
       <c r="BH9">
-        <v>3.549751363868384</v>
+        <v>2.838167305393239</v>
       </c>
       <c r="BI9">
-        <v>0.5300688684225715</v>
+        <v>0.4494892631910257</v>
       </c>
     </row>
     <row r="10" spans="1:61">
@@ -2377,142 +2377,142 @@
         <v>0.1</v>
       </c>
       <c r="L10">
-        <v>0.4859537361199389</v>
+        <v>0.4862414173515686</v>
       </c>
       <c r="M10">
         <v>1.5</v>
       </c>
       <c r="N10">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="O10">
-        <v>0.1577013018345943</v>
+        <v>0.1364650287549802</v>
       </c>
       <c r="P10">
-        <v>0.26</v>
+        <v>0.21</v>
       </c>
       <c r="Q10">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R10">
-        <v>28.57837617863843</v>
+        <v>23.73255206558759</v>
       </c>
       <c r="S10">
-        <v>96</v>
+        <v>80</v>
       </c>
       <c r="T10">
-        <v>30.78</v>
+        <v>25.34</v>
       </c>
       <c r="U10">
-        <v>50.04391635683037</v>
+        <v>41.52635480301053</v>
       </c>
       <c r="V10">
-        <v>72.22</v>
+        <v>62.68</v>
       </c>
       <c r="W10">
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
       <c r="X10">
-        <v>0.3711534829424806</v>
+        <v>0.1984895488750122</v>
       </c>
       <c r="Y10">
-        <v>0.6899999999999999</v>
+        <v>0.39</v>
       </c>
       <c r="Z10">
-        <v>0.19</v>
+        <v>0.06</v>
       </c>
       <c r="AA10">
-        <v>0.4106032903786178</v>
+        <v>0.2288361080750454</v>
       </c>
       <c r="AB10">
-        <v>0.67</v>
+        <v>0.45</v>
       </c>
       <c r="AC10">
-        <v>1.7</v>
+        <v>1.37</v>
       </c>
       <c r="AD10">
-        <v>2.1306</v>
+        <v>1.7104614</v>
       </c>
       <c r="AE10">
-        <v>2.56</v>
+        <v>2.05</v>
       </c>
       <c r="AF10">
-        <v>1.37</v>
+        <v>0.96</v>
       </c>
       <c r="AG10">
-        <v>1.95</v>
+        <v>1.36</v>
       </c>
       <c r="AH10">
-        <v>2.63</v>
+        <v>1.96</v>
       </c>
       <c r="AI10">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="AJ10">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AK10">
-        <v>0.13</v>
+        <v>0.11</v>
       </c>
       <c r="AL10">
-        <v>15.39</v>
+        <v>12.67</v>
       </c>
       <c r="AM10">
-        <v>21.15</v>
+        <v>17.83</v>
       </c>
       <c r="AN10">
-        <v>36.11</v>
+        <v>31.34</v>
       </c>
       <c r="AO10">
-        <v>0.64</v>
+        <v>0.06</v>
       </c>
       <c r="AP10">
-        <v>1.56</v>
+        <v>0.17</v>
       </c>
       <c r="AQ10">
-        <v>0.2</v>
+        <v>0.11</v>
       </c>
       <c r="AR10">
-        <v>0.45</v>
+        <v>0.32</v>
       </c>
       <c r="AS10">
-        <v>1.43</v>
+        <v>4.61</v>
       </c>
       <c r="AT10">
-        <v>0.39</v>
+        <v>0.12</v>
       </c>
       <c r="AU10">
-        <v>0.8100000000000001</v>
+        <v>0.44</v>
       </c>
       <c r="AV10">
-        <v>1.33</v>
+        <v>0.9</v>
       </c>
       <c r="AW10">
-        <v>0.146</v>
+        <v>0.126</v>
       </c>
       <c r="AX10">
-        <v>0.617</v>
+        <v>0.645</v>
       </c>
       <c r="AY10">
-        <v>0.277</v>
+        <v>0.207</v>
       </c>
       <c r="AZ10">
-        <v>0.551</v>
+        <v>0.461</v>
       </c>
       <c r="BA10">
-        <v>0.439</v>
+        <v>1.09</v>
       </c>
       <c r="BB10">
-        <v>0.338</v>
+        <v>-0.044</v>
       </c>
       <c r="BC10">
-        <v>0.789</v>
+        <v>0.872</v>
       </c>
       <c r="BD10">
-        <v>0.953</v>
+        <v>0.987</v>
       </c>
       <c r="BE10">
-        <v>0.256</v>
+        <v>0.184</v>
       </c>
       <c r="BF10">
         <v>-0.9485599924429405</v>
@@ -2521,10 +2521,10 @@
         <v>0.6770125502755524</v>
       </c>
       <c r="BH10">
-        <v>3.087162041767213</v>
+        <v>2.890433338639702</v>
       </c>
       <c r="BI10">
-        <v>0.7368383910469918</v>
+        <v>0.7449064785752859</v>
       </c>
     </row>
     <row r="11" spans="1:61">
@@ -2559,157 +2559,157 @@
         <v>90</v>
       </c>
       <c r="K11">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="L11">
-        <v>0.5026571302060574</v>
+        <v>0.6504329366864346</v>
       </c>
       <c r="M11">
-        <v>0.79</v>
+        <v>1</v>
       </c>
       <c r="N11">
-        <v>0.29</v>
+        <v>0.35</v>
       </c>
       <c r="O11">
-        <v>0.3987100993625148</v>
+        <v>0.46345291550084</v>
       </c>
       <c r="P11">
-        <v>0.5600000000000001</v>
+        <v>0.63</v>
       </c>
       <c r="Q11">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="R11">
-        <v>18.8340797245099</v>
+        <v>11.59784635031798</v>
       </c>
       <c r="S11">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="T11">
-        <v>14.95</v>
+        <v>9.74</v>
       </c>
       <c r="U11">
-        <v>21.02174618507651</v>
+        <v>12.58392667347656</v>
       </c>
       <c r="V11">
-        <v>27.91</v>
+        <v>15.5</v>
       </c>
       <c r="W11">
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
       <c r="X11">
-        <v>0.3699725004192143</v>
+        <v>0.1992673932305912</v>
       </c>
       <c r="Y11">
-        <v>0.6899999999999999</v>
+        <v>0.39</v>
       </c>
       <c r="Z11">
-        <v>0.19</v>
+        <v>0.03</v>
       </c>
       <c r="AA11">
-        <v>0.4558158547892102</v>
+        <v>0.1843684096371254</v>
       </c>
       <c r="AB11">
-        <v>0.73</v>
+        <v>0.44</v>
       </c>
       <c r="AC11">
-        <v>1.7</v>
+        <v>1.37</v>
       </c>
       <c r="AD11">
-        <v>2.1306</v>
+        <v>1.7104614</v>
       </c>
       <c r="AE11">
-        <v>2.56</v>
+        <v>2.05</v>
       </c>
       <c r="AF11">
-        <v>1.71</v>
+        <v>1.25</v>
       </c>
       <c r="AG11">
-        <v>2.12</v>
+        <v>1.47</v>
       </c>
       <c r="AH11">
-        <v>2.54</v>
+        <v>1.66</v>
       </c>
       <c r="AI11">
-        <v>0.14</v>
+        <v>0.18</v>
       </c>
       <c r="AJ11">
-        <v>0.22</v>
+        <v>0.25</v>
       </c>
       <c r="AK11">
-        <v>0.28</v>
+        <v>0.31</v>
       </c>
       <c r="AL11">
-        <v>7.48</v>
+        <v>4.87</v>
       </c>
       <c r="AM11">
-        <v>9.57</v>
+        <v>5.77</v>
       </c>
       <c r="AN11">
-        <v>13.96</v>
+        <v>7.75</v>
       </c>
       <c r="AO11">
-        <v>0.64</v>
+        <v>0.06</v>
       </c>
       <c r="AP11">
-        <v>1.56</v>
+        <v>0.17</v>
       </c>
       <c r="AQ11">
-        <v>0.17</v>
+        <v>0.12</v>
       </c>
       <c r="AR11">
-        <v>0.37</v>
+        <v>0.55</v>
       </c>
       <c r="AS11">
-        <v>1.31</v>
+        <v>14.88</v>
       </c>
       <c r="AT11">
-        <v>0.38</v>
+        <v>0.06</v>
       </c>
       <c r="AU11">
-        <v>0.9</v>
+        <v>0.32</v>
       </c>
       <c r="AV11">
-        <v>1.45</v>
+        <v>0.88</v>
       </c>
       <c r="AW11">
-        <v>0.584</v>
+        <v>0.485</v>
       </c>
       <c r="AX11">
-        <v>0.236</v>
+        <v>0.303</v>
       </c>
       <c r="AY11">
-        <v>0.596</v>
+        <v>0.407</v>
       </c>
       <c r="AZ11">
-        <v>0.862</v>
+        <v>0.6909999999999999</v>
       </c>
       <c r="BA11">
-        <v>0.595</v>
+        <v>1.475</v>
       </c>
       <c r="BB11">
-        <v>0.229</v>
+        <v>-0.215</v>
       </c>
       <c r="BC11">
-        <v>0.75</v>
+        <v>0.872</v>
       </c>
       <c r="BD11">
-        <v>0.948</v>
+        <v>0.986</v>
       </c>
       <c r="BE11">
-        <v>0.298</v>
+        <v>0.182</v>
       </c>
       <c r="BF11">
-        <v>-0.719847568923503</v>
+        <v>-0.4581453659370775</v>
       </c>
       <c r="BG11">
-        <v>0.2420626177012166</v>
+        <v>0.2290726829685387</v>
       </c>
       <c r="BH11">
-        <v>2.8654220287008</v>
+        <v>2.384866696937037</v>
       </c>
       <c r="BI11">
-        <v>0.3839926300314498</v>
+        <v>0.3728431500535598</v>
       </c>
     </row>
     <row r="12" spans="1:61">
@@ -2747,154 +2747,154 @@
         <v>0.05</v>
       </c>
       <c r="L12">
-        <v>0.1581220079492295</v>
+        <v>0.2104130313389261</v>
       </c>
       <c r="M12">
-        <v>0.39</v>
+        <v>0.6</v>
       </c>
       <c r="N12">
         <v>0.05</v>
       </c>
       <c r="O12">
-        <v>0.07967221649907212</v>
+        <v>0.07362187899230502</v>
       </c>
       <c r="P12">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="Q12">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="R12">
-        <v>73.22377043454307</v>
+        <v>49.04131338280277</v>
       </c>
       <c r="S12">
-        <v>204</v>
+        <v>154</v>
       </c>
       <c r="T12">
-        <v>68.95</v>
+        <v>50.08</v>
       </c>
       <c r="U12">
-        <v>114.1977600127055</v>
+        <v>86.04736229402522</v>
       </c>
       <c r="V12">
-        <v>170.41</v>
+        <v>129.44</v>
       </c>
       <c r="W12">
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
       <c r="X12">
-        <v>0.3684190147519169</v>
+        <v>0.1983893834957944</v>
       </c>
       <c r="Y12">
-        <v>0.6899999999999999</v>
+        <v>0.39</v>
       </c>
       <c r="Z12">
-        <v>0.24</v>
+        <v>0.06</v>
       </c>
       <c r="AA12">
-        <v>0.4902377844310698</v>
+        <v>0.2274103162691068</v>
       </c>
       <c r="AB12">
-        <v>0.72</v>
+        <v>0.42</v>
       </c>
       <c r="AC12">
-        <v>1.7</v>
+        <v>1.37</v>
       </c>
       <c r="AD12">
-        <v>2.1306</v>
+        <v>1.7104614</v>
       </c>
       <c r="AE12">
-        <v>2.56</v>
+        <v>2.05</v>
       </c>
       <c r="AF12">
-        <v>1.46</v>
+        <v>1.02</v>
       </c>
       <c r="AG12">
-        <v>2.13</v>
+        <v>1.49</v>
       </c>
       <c r="AH12">
-        <v>3.15</v>
+        <v>2.25</v>
       </c>
       <c r="AI12">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="AJ12">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="AK12">
         <v>0.06</v>
       </c>
       <c r="AL12">
-        <v>34.48</v>
+        <v>25.04</v>
       </c>
       <c r="AM12">
-        <v>46.99</v>
+        <v>35.17</v>
       </c>
       <c r="AN12">
-        <v>85.2</v>
+        <v>64.72</v>
       </c>
       <c r="AO12">
-        <v>0.64</v>
+        <v>0.06</v>
       </c>
       <c r="AP12">
-        <v>1.56</v>
+        <v>0.17</v>
       </c>
       <c r="AQ12">
-        <v>0.16</v>
+        <v>0.1</v>
       </c>
       <c r="AR12">
-        <v>0.32</v>
+        <v>0.28</v>
       </c>
       <c r="AS12">
-        <v>0.83</v>
+        <v>4.08</v>
       </c>
       <c r="AT12">
-        <v>0.49</v>
+        <v>0.12</v>
       </c>
       <c r="AU12">
-        <v>0.99</v>
+        <v>0.45</v>
       </c>
       <c r="AV12">
-        <v>1.45</v>
+        <v>0.84</v>
       </c>
       <c r="AW12">
-        <v>0.232</v>
+        <v>0.182</v>
       </c>
       <c r="AX12">
-        <v>0.518</v>
+        <v>0.574</v>
       </c>
       <c r="AY12">
-        <v>0.394</v>
+        <v>0.275</v>
       </c>
       <c r="AZ12">
-        <v>0.6850000000000001</v>
+        <v>0.549</v>
       </c>
       <c r="BA12">
-        <v>0.453</v>
+        <v>0.889</v>
       </c>
       <c r="BB12">
-        <v>0.327</v>
+        <v>0.057</v>
       </c>
       <c r="BC12">
-        <v>0.637</v>
+        <v>0.85</v>
       </c>
       <c r="BD12">
-        <v>0.891</v>
+        <v>0.985</v>
       </c>
       <c r="BE12">
-        <v>0.45</v>
+        <v>0.148</v>
       </c>
       <c r="BF12">
-        <v>-1.968670406706218</v>
+        <v>-1.753278948659991</v>
       </c>
       <c r="BG12">
-        <v>0.5135309334238864</v>
+        <v>0.621226662447</v>
       </c>
       <c r="BH12">
-        <v>4.105425522020905</v>
+        <v>3.662123326723527</v>
       </c>
       <c r="BI12">
-        <v>0.6071664612677679</v>
+        <v>0.6889286367768268</v>
       </c>
     </row>
     <row r="13" spans="1:61">
@@ -2929,157 +2929,157 @@
         <v>90</v>
       </c>
       <c r="K13">
+        <v>0.2</v>
+      </c>
+      <c r="L13">
+        <v>0.4239249219097995</v>
+      </c>
+      <c r="M13">
+        <v>0.8</v>
+      </c>
+      <c r="N13">
+        <v>0.17</v>
+      </c>
+      <c r="O13">
+        <v>0.2421616259483194</v>
+      </c>
+      <c r="P13">
+        <v>0.35</v>
+      </c>
+      <c r="Q13">
+        <v>7</v>
+      </c>
+      <c r="R13">
+        <v>19.10535358930238</v>
+      </c>
+      <c r="S13">
+        <v>43</v>
+      </c>
+      <c r="T13">
+        <v>15.19</v>
+      </c>
+      <c r="U13">
+        <v>21.74859080204942</v>
+      </c>
+      <c r="V13">
+        <v>29.72</v>
+      </c>
+      <c r="W13">
+        <v>0.01</v>
+      </c>
+      <c r="X13">
+        <v>0.2005644107930071</v>
+      </c>
+      <c r="Y13">
+        <v>0.39</v>
+      </c>
+      <c r="Z13">
+        <v>0.04</v>
+      </c>
+      <c r="AA13">
+        <v>0.2598886618988198</v>
+      </c>
+      <c r="AB13">
+        <v>0.55</v>
+      </c>
+      <c r="AC13">
+        <v>1.37</v>
+      </c>
+      <c r="AD13">
+        <v>1.7104614</v>
+      </c>
+      <c r="AE13">
+        <v>2.05</v>
+      </c>
+      <c r="AF13">
+        <v>1.04</v>
+      </c>
+      <c r="AG13">
+        <v>1.33</v>
+      </c>
+      <c r="AH13">
+        <v>1.6</v>
+      </c>
+      <c r="AI13">
+        <v>0.08</v>
+      </c>
+      <c r="AJ13">
+        <v>0.13</v>
+      </c>
+      <c r="AK13">
+        <v>0.18</v>
+      </c>
+      <c r="AL13">
+        <v>7.59</v>
+      </c>
+      <c r="AM13">
+        <v>10.08</v>
+      </c>
+      <c r="AN13">
+        <v>14.86</v>
+      </c>
+      <c r="AO13">
+        <v>0.06</v>
+      </c>
+      <c r="AP13">
+        <v>0.17</v>
+      </c>
+      <c r="AQ13">
         <v>0.1</v>
       </c>
-      <c r="L13">
-        <v>0.2680566935185636</v>
-      </c>
-      <c r="M13">
-        <v>0.59</v>
-      </c>
-      <c r="N13">
-        <v>0.1</v>
-      </c>
-      <c r="O13">
-        <v>0.150224553913144</v>
-      </c>
-      <c r="P13">
-        <v>0.23</v>
-      </c>
-      <c r="Q13">
-        <v>12</v>
-      </c>
-      <c r="R13">
-        <v>39.85096978313215</v>
-      </c>
-      <c r="S13">
-        <v>100</v>
-      </c>
-      <c r="T13">
-        <v>34.58</v>
-      </c>
-      <c r="U13">
-        <v>53.94458208781338</v>
-      </c>
-      <c r="V13">
-        <v>78.87</v>
-      </c>
-      <c r="W13">
-        <v>0.05</v>
-      </c>
-      <c r="X13">
-        <v>0.3691791260021191</v>
-      </c>
-      <c r="Y13">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="Z13">
-        <v>0.23</v>
-      </c>
-      <c r="AA13">
-        <v>0.4505343973400982</v>
-      </c>
-      <c r="AB13">
-        <v>0.71</v>
-      </c>
-      <c r="AC13">
-        <v>1.7</v>
-      </c>
-      <c r="AD13">
-        <v>2.1306</v>
-      </c>
-      <c r="AE13">
-        <v>2.56</v>
-      </c>
-      <c r="AF13">
-        <v>1.39</v>
-      </c>
-      <c r="AG13">
-        <v>2.01</v>
-      </c>
-      <c r="AH13">
-        <v>2.77</v>
-      </c>
-      <c r="AI13">
-        <v>0.05</v>
-      </c>
-      <c r="AJ13">
-        <v>0.08</v>
-      </c>
-      <c r="AK13">
-        <v>0.12</v>
-      </c>
-      <c r="AL13">
-        <v>17.29</v>
-      </c>
-      <c r="AM13">
-        <v>23.79</v>
-      </c>
-      <c r="AN13">
-        <v>39.43</v>
-      </c>
-      <c r="AO13">
-        <v>0.64</v>
-      </c>
-      <c r="AP13">
-        <v>1.56</v>
-      </c>
-      <c r="AQ13">
-        <v>0.18</v>
-      </c>
       <c r="AR13">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="AS13">
-        <v>1.04</v>
+        <v>11.84</v>
       </c>
       <c r="AT13">
-        <v>0.46</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AU13">
-        <v>0.89</v>
+        <v>0.47</v>
       </c>
       <c r="AV13">
-        <v>1.42</v>
+        <v>1.09</v>
       </c>
       <c r="AW13">
-        <v>0.283</v>
+        <v>0.347</v>
       </c>
       <c r="AX13">
-        <v>0.468</v>
+        <v>0.411</v>
       </c>
       <c r="AY13">
-        <v>0.419</v>
+        <v>0.331</v>
       </c>
       <c r="AZ13">
-        <v>0.711</v>
+        <v>0.614</v>
       </c>
       <c r="BA13">
-        <v>0.443</v>
+        <v>1.968</v>
       </c>
       <c r="BB13">
-        <v>0.335</v>
+        <v>-0.403</v>
       </c>
       <c r="BC13">
-        <v>0.737</v>
+        <v>0.744</v>
       </c>
       <c r="BD13">
-        <v>0.927</v>
+        <v>0.9389999999999999</v>
       </c>
       <c r="BE13">
-        <v>0.407</v>
+        <v>0.142</v>
       </c>
       <c r="BF13">
-        <v>-1.415108917538209</v>
+        <v>-0.916290731874155</v>
       </c>
       <c r="BG13">
-        <v>0.4437380877279183</v>
+        <v>0.3465735902799726</v>
       </c>
       <c r="BH13">
-        <v>3.541613787543523</v>
+        <v>2.845764912034643</v>
       </c>
       <c r="BI13">
-        <v>0.5316462628520973</v>
+        <v>0.4573757109553629</v>
       </c>
     </row>
     <row r="14" spans="1:61">
@@ -3117,142 +3117,142 @@
         <v>0.1</v>
       </c>
       <c r="L14">
-        <v>0.4879118413077933</v>
+        <v>0.4831632600137727</v>
       </c>
       <c r="M14">
         <v>1.5</v>
       </c>
       <c r="N14">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="O14">
-        <v>0.1522740234520493</v>
+        <v>0.1441591908481783</v>
       </c>
       <c r="P14">
-        <v>0.24</v>
+        <v>0.23</v>
       </c>
       <c r="Q14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R14">
-        <v>29.05351567641098</v>
+        <v>23.24982774726324</v>
       </c>
       <c r="S14">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="T14">
-        <v>29.58</v>
+        <v>23.32</v>
       </c>
       <c r="U14">
-        <v>47.30021719168395</v>
+        <v>38.1405822167963</v>
       </c>
       <c r="V14">
-        <v>69.5</v>
+        <v>58.26</v>
       </c>
       <c r="W14">
-        <v>0.07000000000000001</v>
+        <v>0.02</v>
       </c>
       <c r="X14">
-        <v>0.1985997604546134</v>
+        <v>0.1199630303523375</v>
       </c>
       <c r="Y14">
-        <v>0.33</v>
+        <v>0.22</v>
       </c>
       <c r="Z14">
-        <v>0.11</v>
+        <v>0.03</v>
       </c>
       <c r="AA14">
-        <v>0.2311811759469647</v>
+        <v>0.1189305083398666</v>
       </c>
       <c r="AB14">
-        <v>0.37</v>
+        <v>0.23</v>
       </c>
       <c r="AC14">
-        <v>1.7</v>
+        <v>1.37</v>
       </c>
       <c r="AD14">
-        <v>2.1306</v>
+        <v>1.7104614</v>
       </c>
       <c r="AE14">
-        <v>2.56</v>
+        <v>2.05</v>
       </c>
       <c r="AF14">
-        <v>1.29</v>
+        <v>0.96</v>
       </c>
       <c r="AG14">
-        <v>1.78</v>
+        <v>1.33</v>
       </c>
       <c r="AH14">
-        <v>2.36</v>
+        <v>1.83</v>
       </c>
       <c r="AI14">
         <v>0.05</v>
       </c>
       <c r="AJ14">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AK14">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AL14">
-        <v>14.79</v>
+        <v>11.66</v>
       </c>
       <c r="AM14">
-        <v>20.63</v>
+        <v>16.12</v>
       </c>
       <c r="AN14">
-        <v>34.75</v>
+        <v>29.13</v>
       </c>
       <c r="AO14">
-        <v>0.64</v>
+        <v>0.06</v>
       </c>
       <c r="AP14">
-        <v>1.56</v>
+        <v>0.17</v>
       </c>
       <c r="AQ14">
-        <v>0.42</v>
+        <v>0.26</v>
       </c>
       <c r="AR14">
-        <v>0.97</v>
+        <v>1.19</v>
       </c>
       <c r="AS14">
-        <v>4.55</v>
+        <v>13.98</v>
       </c>
       <c r="AT14">
-        <v>0.22</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AU14">
+        <v>0.23</v>
+      </c>
+      <c r="AV14">
         <v>0.46</v>
       </c>
-      <c r="AV14">
-        <v>0.74</v>
-      </c>
       <c r="AW14">
-        <v>0.141</v>
+        <v>0.136</v>
       </c>
       <c r="AX14">
-        <v>0.625</v>
+        <v>0.632</v>
       </c>
       <c r="AY14">
-        <v>0.253</v>
+        <v>0.233</v>
       </c>
       <c r="AZ14">
-        <v>0.517</v>
+        <v>0.505</v>
       </c>
       <c r="BA14">
-        <v>0.884</v>
+        <v>1.095</v>
       </c>
       <c r="BB14">
-        <v>0.06</v>
+        <v>-0.047</v>
       </c>
       <c r="BC14">
-        <v>0.805</v>
+        <v>0.969</v>
       </c>
       <c r="BD14">
-        <v>0.971</v>
+        <v>0.997</v>
       </c>
       <c r="BE14">
-        <v>0.044</v>
+        <v>0.01</v>
       </c>
       <c r="BF14">
         <v>-0.9485599924429405</v>
@@ -3261,10 +3261,10 @@
         <v>0.6770125502755524</v>
       </c>
       <c r="BH14">
-        <v>3.088855389081606</v>
+        <v>2.8571159574991</v>
       </c>
       <c r="BI14">
-        <v>0.7361543259903085</v>
+        <v>0.7397514192977308</v>
       </c>
     </row>
     <row r="15" spans="1:61">
@@ -3299,157 +3299,157 @@
         <v>99</v>
       </c>
       <c r="K15">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="L15">
-        <v>0.5035285480909713</v>
+        <v>0.6484270966247414</v>
       </c>
       <c r="M15">
-        <v>0.79</v>
+        <v>1</v>
       </c>
       <c r="N15">
-        <v>0.28</v>
+        <v>0.34</v>
       </c>
       <c r="O15">
-        <v>0.3818813637601022</v>
+        <v>0.4556755355737274</v>
       </c>
       <c r="P15">
-        <v>0.53</v>
+        <v>0.65</v>
       </c>
       <c r="Q15">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="R15">
-        <v>18.6501619134247</v>
+        <v>11.6196568860577</v>
       </c>
       <c r="S15">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="T15">
-        <v>14.89</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="U15">
-        <v>20.2668547706486</v>
+        <v>12.89237321114072</v>
       </c>
       <c r="V15">
-        <v>26.07</v>
+        <v>15.87</v>
       </c>
       <c r="W15">
-        <v>0.07000000000000001</v>
+        <v>0.02</v>
       </c>
       <c r="X15">
-        <v>0.1994919173261029</v>
+        <v>0.1197989386103193</v>
       </c>
       <c r="Y15">
-        <v>0.33</v>
+        <v>0.22</v>
       </c>
       <c r="Z15">
-        <v>0.09</v>
+        <v>0.03</v>
       </c>
       <c r="AA15">
-        <v>0.2084737982325416</v>
+        <v>0.1135254003983858</v>
       </c>
       <c r="AB15">
-        <v>0.36</v>
+        <v>0.24</v>
       </c>
       <c r="AC15">
-        <v>1.7</v>
+        <v>1.37</v>
       </c>
       <c r="AD15">
-        <v>2.1306</v>
+        <v>1.7104614</v>
       </c>
       <c r="AE15">
-        <v>2.56</v>
+        <v>2.05</v>
       </c>
       <c r="AF15">
-        <v>1.63</v>
+        <v>1.25</v>
       </c>
       <c r="AG15">
-        <v>1.92</v>
+        <v>1.48</v>
       </c>
       <c r="AH15">
-        <v>2.18</v>
+        <v>1.69</v>
       </c>
       <c r="AI15">
-        <v>0.14</v>
+        <v>0.17</v>
       </c>
       <c r="AJ15">
+        <v>0.26</v>
+      </c>
+      <c r="AK15">
+        <v>0.32</v>
+      </c>
+      <c r="AL15">
+        <v>4.82</v>
+      </c>
+      <c r="AM15">
+        <v>5.78</v>
+      </c>
+      <c r="AN15">
+        <v>7.94</v>
+      </c>
+      <c r="AO15">
+        <v>0.06</v>
+      </c>
+      <c r="AP15">
+        <v>0.17</v>
+      </c>
+      <c r="AQ15">
+        <v>0.24</v>
+      </c>
+      <c r="AR15">
+        <v>1.23</v>
+      </c>
+      <c r="AS15">
+        <v>13.58</v>
+      </c>
+      <c r="AT15">
+        <v>0.06</v>
+      </c>
+      <c r="AU15">
         <v>0.21</v>
       </c>
-      <c r="AK15">
-        <v>0.27</v>
-      </c>
-      <c r="AL15">
-        <v>7.45</v>
-      </c>
-      <c r="AM15">
-        <v>9.31</v>
-      </c>
-      <c r="AN15">
-        <v>13.04</v>
-      </c>
-      <c r="AO15">
-        <v>0.64</v>
-      </c>
-      <c r="AP15">
-        <v>1.56</v>
-      </c>
-      <c r="AQ15">
-        <v>0.43</v>
-      </c>
-      <c r="AR15">
-        <v>1.09</v>
-      </c>
-      <c r="AS15">
-        <v>6.38</v>
-      </c>
-      <c r="AT15">
-        <v>0.17</v>
-      </c>
-      <c r="AU15">
-        <v>0.4</v>
-      </c>
       <c r="AV15">
-        <v>0.73</v>
+        <v>0.47</v>
       </c>
       <c r="AW15">
-        <v>0.5610000000000001</v>
+        <v>0.549</v>
       </c>
       <c r="AX15">
-        <v>0.251</v>
+        <v>0.259</v>
       </c>
       <c r="AY15">
-        <v>0.528</v>
+        <v>0.392</v>
       </c>
       <c r="AZ15">
-        <v>0.804</v>
+        <v>0.694</v>
       </c>
       <c r="BA15">
-        <v>1.107</v>
+        <v>1.084</v>
       </c>
       <c r="BB15">
-        <v>-0.052</v>
+        <v>-0.041</v>
       </c>
       <c r="BC15">
-        <v>0.9370000000000001</v>
+        <v>0.9379999999999999</v>
       </c>
       <c r="BD15">
         <v>0.996</v>
       </c>
       <c r="BE15">
-        <v>0.048</v>
+        <v>0.001</v>
       </c>
       <c r="BF15">
-        <v>-0.719847568923503</v>
+        <v>-0.4581453659370775</v>
       </c>
       <c r="BG15">
-        <v>0.2420626177012166</v>
+        <v>0.2290726829685387</v>
       </c>
       <c r="BH15">
-        <v>2.862482886782411</v>
+        <v>2.382417613376656</v>
       </c>
       <c r="BI15">
-        <v>0.3764810239142395</v>
+        <v>0.3746635712590229</v>
       </c>
     </row>
     <row r="16" spans="1:61">
@@ -3487,154 +3487,154 @@
         <v>0.05</v>
       </c>
       <c r="L16">
-        <v>0.1601918282667674</v>
+        <v>0.2085903888448674</v>
       </c>
       <c r="M16">
-        <v>0.39</v>
+        <v>0.6</v>
       </c>
       <c r="N16">
         <v>0.05</v>
       </c>
       <c r="O16">
-        <v>0.07621466794262446</v>
+        <v>0.0757349359463427</v>
       </c>
       <c r="P16">
         <v>0.12</v>
       </c>
       <c r="Q16">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="R16">
-        <v>73.63020494223035</v>
+        <v>50.77744267595575</v>
       </c>
       <c r="S16">
-        <v>205</v>
+        <v>161</v>
       </c>
       <c r="T16">
-        <v>64.09</v>
+        <v>48.16</v>
       </c>
       <c r="U16">
-        <v>111.8098874285687</v>
+        <v>89.58852845224459</v>
       </c>
       <c r="V16">
-        <v>168.16</v>
+        <v>134.38</v>
       </c>
       <c r="W16">
-        <v>0.07000000000000001</v>
+        <v>0.02</v>
       </c>
       <c r="X16">
-        <v>0.1994323166209915</v>
+        <v>0.1197950673295667</v>
       </c>
       <c r="Y16">
-        <v>0.33</v>
+        <v>0.22</v>
       </c>
       <c r="Z16">
-        <v>0.13</v>
+        <v>0.05</v>
       </c>
       <c r="AA16">
-        <v>0.2520030832883975</v>
+        <v>0.1350734147520163</v>
       </c>
       <c r="AB16">
-        <v>0.42</v>
+        <v>0.26</v>
       </c>
       <c r="AC16">
-        <v>1.7</v>
+        <v>1.37</v>
       </c>
       <c r="AD16">
-        <v>2.1306</v>
+        <v>1.7104614</v>
       </c>
       <c r="AE16">
-        <v>2.56</v>
+        <v>2.05</v>
       </c>
       <c r="AF16">
-        <v>1.39</v>
+        <v>1.1</v>
       </c>
       <c r="AG16">
-        <v>1.95</v>
+        <v>1.52</v>
       </c>
       <c r="AH16">
-        <v>2.93</v>
+        <v>2.35</v>
       </c>
       <c r="AI16">
         <v>0.02</v>
       </c>
       <c r="AJ16">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="AK16">
         <v>0.06</v>
       </c>
       <c r="AL16">
-        <v>32.05</v>
+        <v>24.08</v>
       </c>
       <c r="AM16">
-        <v>43.71</v>
+        <v>32.47</v>
       </c>
       <c r="AN16">
-        <v>84.08</v>
+        <v>67.19</v>
       </c>
       <c r="AO16">
-        <v>0.64</v>
+        <v>0.06</v>
       </c>
       <c r="AP16">
-        <v>1.56</v>
+        <v>0.17</v>
       </c>
       <c r="AQ16">
-        <v>0.32</v>
+        <v>0.18</v>
       </c>
       <c r="AR16">
-        <v>0.72</v>
+        <v>0.77</v>
       </c>
       <c r="AS16">
-        <v>2.81</v>
+        <v>4.72</v>
       </c>
       <c r="AT16">
-        <v>0.25</v>
+        <v>0.1</v>
       </c>
       <c r="AU16">
-        <v>0.49</v>
+        <v>0.26</v>
       </c>
       <c r="AV16">
-        <v>0.83</v>
+        <v>0.52</v>
       </c>
       <c r="AW16">
-        <v>0.234</v>
+        <v>0.177</v>
       </c>
       <c r="AX16">
-        <v>0.516</v>
+        <v>0.58</v>
       </c>
       <c r="AY16">
-        <v>0.367</v>
+        <v>0.292</v>
       </c>
       <c r="AZ16">
-        <v>0.661</v>
+        <v>0.586</v>
       </c>
       <c r="BA16">
-        <v>0.863</v>
+        <v>0.802</v>
       </c>
       <c r="BB16">
-        <v>0.07099999999999999</v>
+        <v>0.104</v>
       </c>
       <c r="BC16">
-        <v>0.717</v>
+        <v>0.877</v>
       </c>
       <c r="BD16">
-        <v>0.93</v>
+        <v>0.985</v>
       </c>
       <c r="BE16">
-        <v>0.1</v>
+        <v>0.025</v>
       </c>
       <c r="BF16">
-        <v>-1.968670406706218</v>
+        <v>-1.753278948659991</v>
       </c>
       <c r="BG16">
-        <v>0.5135309334238864</v>
+        <v>0.621226662447</v>
       </c>
       <c r="BH16">
-        <v>4.128191838768842</v>
+        <v>3.697698392092545</v>
       </c>
       <c r="BI16">
-        <v>0.5966369005832375</v>
+        <v>0.6916722422588122</v>
       </c>
     </row>
     <row r="17" spans="1:61">
@@ -3669,157 +3669,157 @@
         <v>99</v>
       </c>
       <c r="K17">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="L17">
-        <v>0.2659001901516455</v>
+        <v>0.4229877796347178</v>
       </c>
       <c r="M17">
-        <v>0.59</v>
+        <v>0.8</v>
       </c>
       <c r="N17">
-        <v>0.1</v>
+        <v>0.17</v>
       </c>
       <c r="O17">
-        <v>0.1442703923361103</v>
+        <v>0.2469094949737821</v>
       </c>
       <c r="P17">
-        <v>0.23</v>
+        <v>0.36</v>
       </c>
       <c r="Q17">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="R17">
-        <v>40.57350527629553</v>
+        <v>18.97687081989667</v>
       </c>
       <c r="S17">
-        <v>103</v>
+        <v>43</v>
       </c>
       <c r="T17">
-        <v>31.02</v>
+        <v>15.01</v>
       </c>
       <c r="U17">
-        <v>51.02412343029771</v>
+        <v>21.04183162341781</v>
       </c>
       <c r="V17">
-        <v>76.69</v>
+        <v>28.45</v>
       </c>
       <c r="W17">
-        <v>0.07000000000000001</v>
+        <v>0.02</v>
       </c>
       <c r="X17">
-        <v>0.2001394816502665</v>
+        <v>0.120110540260447</v>
       </c>
       <c r="Y17">
-        <v>0.33</v>
+        <v>0.22</v>
       </c>
       <c r="Z17">
-        <v>0.11</v>
+        <v>0.03</v>
       </c>
       <c r="AA17">
-        <v>0.2422653684698586</v>
+        <v>0.1118114635420077</v>
       </c>
       <c r="AB17">
-        <v>0.4</v>
+        <v>0.22</v>
       </c>
       <c r="AC17">
-        <v>1.7</v>
+        <v>1.37</v>
       </c>
       <c r="AD17">
-        <v>2.1306</v>
+        <v>1.7104614</v>
       </c>
       <c r="AE17">
-        <v>2.56</v>
+        <v>2.05</v>
       </c>
       <c r="AF17">
-        <v>1.3</v>
+        <v>1.03</v>
       </c>
       <c r="AG17">
-        <v>1.8</v>
+        <v>1.32</v>
       </c>
       <c r="AH17">
-        <v>2.49</v>
+        <v>1.58</v>
       </c>
       <c r="AI17">
-        <v>0.05</v>
+        <v>0.09</v>
       </c>
       <c r="AJ17">
-        <v>0.08</v>
+        <v>0.13</v>
       </c>
       <c r="AK17">
-        <v>0.12</v>
+        <v>0.18</v>
       </c>
       <c r="AL17">
-        <v>15.51</v>
+        <v>7.51</v>
       </c>
       <c r="AM17">
-        <v>22.06</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AN17">
-        <v>38.34</v>
+        <v>14.23</v>
       </c>
       <c r="AO17">
-        <v>0.64</v>
+        <v>0.06</v>
       </c>
       <c r="AP17">
-        <v>1.56</v>
+        <v>0.17</v>
       </c>
       <c r="AQ17">
-        <v>0.38</v>
+        <v>0.3</v>
       </c>
       <c r="AR17">
-        <v>0.88</v>
+        <v>1.41</v>
       </c>
       <c r="AS17">
-        <v>4.24</v>
+        <v>15.75</v>
       </c>
       <c r="AT17">
-        <v>0.22</v>
+        <v>0.06</v>
       </c>
       <c r="AU17">
-        <v>0.48</v>
+        <v>0.21</v>
       </c>
       <c r="AV17">
-        <v>0.79</v>
+        <v>0.44</v>
       </c>
       <c r="AW17">
-        <v>0.285</v>
+        <v>0.345</v>
       </c>
       <c r="AX17">
-        <v>0.466</v>
+        <v>0.413</v>
       </c>
       <c r="AY17">
-        <v>0.393</v>
+        <v>0.347</v>
       </c>
       <c r="AZ17">
-        <v>0.6889999999999999</v>
+        <v>0.634</v>
       </c>
       <c r="BA17">
-        <v>0.975</v>
+        <v>1.057</v>
       </c>
       <c r="BB17">
-        <v>0.013</v>
+        <v>-0.028</v>
       </c>
       <c r="BC17">
-        <v>0.769</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="BD17">
-        <v>0.957</v>
+        <v>0.994</v>
       </c>
       <c r="BE17">
-        <v>0.08</v>
+        <v>0.005</v>
       </c>
       <c r="BF17">
-        <v>-1.415108917538209</v>
+        <v>-0.916290731874155</v>
       </c>
       <c r="BG17">
-        <v>0.4437380877279183</v>
+        <v>0.3465735902799726</v>
       </c>
       <c r="BH17">
-        <v>3.546188036772913</v>
+        <v>2.832461754152476</v>
       </c>
       <c r="BI17">
-        <v>0.5422780170744782</v>
+        <v>0.4615469236443074</v>
       </c>
     </row>
   </sheetData>

--- a/Catch models/cmsy_out_macarellus_cmsy.xlsx
+++ b/Catch models/cmsy_out_macarellus_cmsy.xlsx
@@ -897,142 +897,142 @@
         <v>0.1</v>
       </c>
       <c r="L2">
-        <v>0.491675852849026</v>
+        <v>0.487690864500715</v>
       </c>
       <c r="M2">
         <v>1.5</v>
       </c>
       <c r="N2">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="O2">
-        <v>0.1541836166563351</v>
+        <v>0.142855069264874</v>
       </c>
       <c r="P2">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="Q2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R2">
-        <v>23.54940713793097</v>
+        <v>29.367163803133</v>
       </c>
       <c r="S2">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="T2">
-        <v>22.78</v>
+        <v>29.84</v>
       </c>
       <c r="U2">
-        <v>41.42459946873139</v>
+        <v>47.40943144420574</v>
       </c>
       <c r="V2">
-        <v>62.14</v>
+        <v>69.39</v>
       </c>
       <c r="W2">
         <v>0.01</v>
       </c>
       <c r="X2">
-        <v>0.5048356154464563</v>
+        <v>0.5038728433596689</v>
       </c>
       <c r="Y2">
         <v>1</v>
       </c>
       <c r="Z2">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AA2">
-        <v>0.4403198319832484</v>
+        <v>0.3744987528694565</v>
       </c>
       <c r="AB2">
-        <v>0.75</v>
+        <v>0.61</v>
       </c>
       <c r="AC2">
-        <v>1.37</v>
+        <v>1.7</v>
       </c>
       <c r="AD2">
-        <v>1.7104614</v>
+        <v>2.1306</v>
       </c>
       <c r="AE2">
-        <v>2.05</v>
+        <v>2.56</v>
       </c>
       <c r="AF2">
-        <v>1.11</v>
+        <v>1.18</v>
       </c>
       <c r="AG2">
-        <v>1.49</v>
+        <v>1.69</v>
       </c>
       <c r="AH2">
-        <v>2.07</v>
+        <v>2.25</v>
       </c>
       <c r="AI2">
         <v>0.05</v>
       </c>
       <c r="AJ2">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AK2">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AL2">
-        <v>11.39</v>
+        <v>14.92</v>
       </c>
       <c r="AM2">
-        <v>16.24</v>
+        <v>21.14</v>
       </c>
       <c r="AN2">
-        <v>31.07</v>
+        <v>34.7</v>
       </c>
       <c r="AO2">
-        <v>0.06</v>
+        <v>0.25</v>
       </c>
       <c r="AP2">
-        <v>0.17</v>
+        <v>0.36</v>
       </c>
       <c r="AQ2">
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
       <c r="AR2">
-        <v>0.12</v>
+        <v>0.18</v>
       </c>
       <c r="AS2">
-        <v>1.8</v>
+        <v>3.16</v>
       </c>
       <c r="AT2">
-        <v>0.18</v>
+        <v>0.15</v>
       </c>
       <c r="AU2">
-        <v>0.9</v>
+        <v>0.78</v>
       </c>
       <c r="AV2">
-        <v>1.5</v>
+        <v>1.23</v>
       </c>
       <c r="AW2">
-        <v>0.136</v>
+        <v>0.145</v>
       </c>
       <c r="AX2">
-        <v>0.631</v>
+        <v>0.619</v>
       </c>
       <c r="AY2">
-        <v>0.265</v>
+        <v>0.237</v>
       </c>
       <c r="AZ2">
-        <v>0.537</v>
+        <v>0.484</v>
       </c>
       <c r="BA2">
-        <v>0.379</v>
+        <v>0.335</v>
       </c>
       <c r="BB2">
-        <v>0.385</v>
+        <v>0.422</v>
       </c>
       <c r="BC2">
-        <v>0.736</v>
+        <v>0.593</v>
       </c>
       <c r="BD2">
-        <v>0.914</v>
+        <v>0.843</v>
       </c>
       <c r="BE2">
-        <v>0.619</v>
+        <v>0.614</v>
       </c>
       <c r="BF2">
         <v>-0.9485599924429405</v>
@@ -1041,10 +1041,10 @@
         <v>0.6770125502755524</v>
       </c>
       <c r="BH2">
-        <v>2.875714737352825</v>
+        <v>3.111697501832504</v>
       </c>
       <c r="BI2">
-        <v>0.7512147970114545</v>
+        <v>0.7188408482022784</v>
       </c>
     </row>
     <row r="3" spans="1:61">
@@ -1082,76 +1082,76 @@
         <v>0.4</v>
       </c>
       <c r="L3">
-        <v>0.6489503689411591</v>
+        <v>0.6485521093212695</v>
       </c>
       <c r="M3">
         <v>1</v>
       </c>
       <c r="N3">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="O3">
-        <v>0.486216409352817</v>
+        <v>0.4885579765100392</v>
       </c>
       <c r="P3">
         <v>0.68</v>
       </c>
       <c r="Q3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R3">
-        <v>11.76860740953261</v>
+        <v>14.54129149715241</v>
       </c>
       <c r="S3">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="T3">
-        <v>9.23</v>
+        <v>12.21</v>
       </c>
       <c r="U3">
-        <v>12.36288515201704</v>
+        <v>16.34932007067712</v>
       </c>
       <c r="V3">
-        <v>15.89</v>
+        <v>21.01</v>
       </c>
       <c r="W3">
         <v>0.01</v>
       </c>
       <c r="X3">
-        <v>0.5101571285450368</v>
+        <v>0.4982595252544935</v>
       </c>
       <c r="Y3">
         <v>1</v>
       </c>
       <c r="Z3">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="AA3">
-        <v>0.6604505475331751</v>
+        <v>0.6695081974534716</v>
       </c>
       <c r="AB3">
-        <v>0.95</v>
+        <v>0.93</v>
       </c>
       <c r="AC3">
-        <v>1.37</v>
+        <v>1.7</v>
       </c>
       <c r="AD3">
-        <v>1.7104614</v>
+        <v>2.1306</v>
       </c>
       <c r="AE3">
-        <v>2.05</v>
+        <v>2.56</v>
       </c>
       <c r="AF3">
-        <v>1.26</v>
+        <v>1.69</v>
       </c>
       <c r="AG3">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AH3">
-        <v>1.71</v>
+        <v>2.23</v>
       </c>
       <c r="AI3">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="AJ3">
         <v>0.27</v>
@@ -1160,19 +1160,19 @@
         <v>0.34</v>
       </c>
       <c r="AL3">
-        <v>4.62</v>
+        <v>6.1</v>
       </c>
       <c r="AM3">
-        <v>5.65</v>
+        <v>7.45</v>
       </c>
       <c r="AN3">
-        <v>7.94</v>
+        <v>10.51</v>
       </c>
       <c r="AO3">
-        <v>0.06</v>
+        <v>0.25</v>
       </c>
       <c r="AP3">
-        <v>0.17</v>
+        <v>0.36</v>
       </c>
       <c r="AQ3">
         <v>0.05</v>
@@ -1181,43 +1181,43 @@
         <v>0.08</v>
       </c>
       <c r="AS3">
-        <v>0.29</v>
+        <v>0.26</v>
       </c>
       <c r="AT3">
-        <v>0.45</v>
+        <v>0.48</v>
       </c>
       <c r="AU3">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="AV3">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="AW3">
-        <v>0.66</v>
+        <v>0.59</v>
       </c>
       <c r="AX3">
-        <v>0.188</v>
+        <v>0.232</v>
       </c>
       <c r="AY3">
-        <v>0.498</v>
+        <v>0.489</v>
       </c>
       <c r="AZ3">
-        <v>0.786</v>
+        <v>0.779</v>
       </c>
       <c r="BA3">
-        <v>0.737</v>
+        <v>0.501</v>
       </c>
       <c r="BB3">
-        <v>0.141</v>
+        <v>0.292</v>
       </c>
       <c r="BC3">
-        <v>0.723</v>
+        <v>0.668</v>
       </c>
       <c r="BD3">
-        <v>0.9370000000000001</v>
+        <v>0.909</v>
       </c>
       <c r="BE3">
-        <v>0.582</v>
+        <v>0.5659999999999999</v>
       </c>
       <c r="BF3">
         <v>-0.4581453659370775</v>
@@ -1226,10 +1226,10 @@
         <v>0.2290726829685387</v>
       </c>
       <c r="BH3">
-        <v>2.390251899774196</v>
+        <v>2.599789016888458</v>
       </c>
       <c r="BI3">
-        <v>0.3710831562350971</v>
+        <v>0.3672447780822278</v>
       </c>
     </row>
     <row r="4" spans="1:61">
@@ -1267,7 +1267,7 @@
         <v>0.05</v>
       </c>
       <c r="L4">
-        <v>0.2154609734743236</v>
+        <v>0.2098350741775947</v>
       </c>
       <c r="M4">
         <v>0.6</v>
@@ -1276,64 +1276,64 @@
         <v>0.05</v>
       </c>
       <c r="O4">
-        <v>0.07692141890233418</v>
+        <v>0.07724376497577422</v>
       </c>
       <c r="P4">
         <v>0.12</v>
       </c>
       <c r="Q4">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="R4">
-        <v>49.17004767989699</v>
+        <v>62.00839099414698</v>
       </c>
       <c r="S4">
-        <v>156</v>
+        <v>191</v>
       </c>
       <c r="T4">
-        <v>51.04</v>
+        <v>61.03</v>
       </c>
       <c r="U4">
-        <v>85.5576451004337</v>
+        <v>102.165810578136</v>
       </c>
       <c r="V4">
-        <v>128.06</v>
+        <v>153.31</v>
       </c>
       <c r="W4">
         <v>0.01</v>
       </c>
       <c r="X4">
-        <v>0.5113909820946287</v>
+        <v>0.5027342358890469</v>
       </c>
       <c r="Y4">
         <v>1</v>
       </c>
       <c r="Z4">
-        <v>0.1</v>
+        <v>0.14</v>
       </c>
       <c r="AA4">
-        <v>0.3596237132106905</v>
+        <v>0.3601428592018471</v>
       </c>
       <c r="AB4">
-        <v>0.66</v>
+        <v>0.61</v>
       </c>
       <c r="AC4">
-        <v>1.37</v>
+        <v>1.7</v>
       </c>
       <c r="AD4">
-        <v>1.7104614</v>
+        <v>2.1306</v>
       </c>
       <c r="AE4">
-        <v>2.05</v>
+        <v>2.56</v>
       </c>
       <c r="AF4">
-        <v>1.05</v>
+        <v>1.29</v>
       </c>
       <c r="AG4">
-        <v>1.56</v>
+        <v>1.88</v>
       </c>
       <c r="AH4">
-        <v>2.3</v>
+        <v>2.79</v>
       </c>
       <c r="AI4">
         <v>0.02</v>
@@ -1345,64 +1345,64 @@
         <v>0.06</v>
       </c>
       <c r="AL4">
-        <v>25.52</v>
+        <v>30.51</v>
       </c>
       <c r="AM4">
-        <v>35.29</v>
+        <v>42.95</v>
       </c>
       <c r="AN4">
-        <v>64.03</v>
+        <v>76.65000000000001</v>
       </c>
       <c r="AO4">
-        <v>0.06</v>
+        <v>0.25</v>
       </c>
       <c r="AP4">
+        <v>0.36</v>
+      </c>
+      <c r="AQ4">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="AR4">
         <v>0.17</v>
       </c>
-      <c r="AQ4">
-        <v>0.06</v>
-      </c>
-      <c r="AR4">
-        <v>0.15</v>
-      </c>
       <c r="AS4">
-        <v>1.54</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AT4">
-        <v>0.19</v>
+        <v>0.28</v>
       </c>
       <c r="AU4">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="AV4">
-        <v>1.32</v>
+        <v>1.23</v>
       </c>
       <c r="AW4">
-        <v>0.165</v>
+        <v>0.168</v>
       </c>
       <c r="AX4">
-        <v>0.594</v>
+        <v>0.59</v>
       </c>
       <c r="AY4">
-        <v>0.291</v>
+        <v>0.297</v>
       </c>
       <c r="AZ4">
-        <v>0.5669999999999999</v>
+        <v>0.5679999999999999</v>
       </c>
       <c r="BA4">
-        <v>0.294</v>
+        <v>0.153</v>
       </c>
       <c r="BB4">
-        <v>0.458</v>
+        <v>0.609</v>
       </c>
       <c r="BC4">
-        <v>0.644</v>
+        <v>0.54</v>
       </c>
       <c r="BD4">
-        <v>0.858</v>
+        <v>0.799</v>
       </c>
       <c r="BE4">
-        <v>0.68</v>
+        <v>0.671</v>
       </c>
       <c r="BF4">
         <v>-1.753278948659991</v>
@@ -1411,10 +1411,10 @@
         <v>0.621226662447</v>
       </c>
       <c r="BH4">
-        <v>3.672524970449063</v>
+        <v>3.882972794015815</v>
       </c>
       <c r="BI4">
-        <v>0.688346914557648</v>
+        <v>0.683345449522631</v>
       </c>
     </row>
     <row r="5" spans="1:61">
@@ -1452,73 +1452,73 @@
         <v>0.2</v>
       </c>
       <c r="L5">
-        <v>0.4230288165789025</v>
+        <v>0.4250831659619266</v>
       </c>
       <c r="M5">
         <v>0.8</v>
       </c>
       <c r="N5">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="O5">
-        <v>0.2572141999587597</v>
+        <v>0.2499619654801503</v>
       </c>
       <c r="P5">
-        <v>0.39</v>
+        <v>0.37</v>
       </c>
       <c r="Q5">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="R5">
-        <v>19.35678174798427</v>
+        <v>23.85454476942752</v>
       </c>
       <c r="S5">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="T5">
-        <v>14.75</v>
+        <v>20.15</v>
       </c>
       <c r="U5">
-        <v>21.36212428246962</v>
+        <v>28.27212816408936</v>
       </c>
       <c r="V5">
-        <v>28.89</v>
+        <v>37.69</v>
       </c>
       <c r="W5">
         <v>0.01</v>
       </c>
       <c r="X5">
-        <v>0.5068518019025201</v>
+        <v>0.503153023475206</v>
       </c>
       <c r="Y5">
         <v>1</v>
       </c>
       <c r="Z5">
-        <v>0.19</v>
+        <v>0.06</v>
       </c>
       <c r="AA5">
-        <v>0.5375897654080184</v>
+        <v>0.3800564538139665</v>
       </c>
       <c r="AB5">
-        <v>0.87</v>
+        <v>0.68</v>
       </c>
       <c r="AC5">
-        <v>1.37</v>
+        <v>1.7</v>
       </c>
       <c r="AD5">
-        <v>1.7104614</v>
+        <v>2.1306</v>
       </c>
       <c r="AE5">
-        <v>2.05</v>
+        <v>2.56</v>
       </c>
       <c r="AF5">
-        <v>1.06</v>
+        <v>1.41</v>
       </c>
       <c r="AG5">
-        <v>1.41</v>
+        <v>1.79</v>
       </c>
       <c r="AH5">
-        <v>1.72</v>
+        <v>2.08</v>
       </c>
       <c r="AI5">
         <v>0.09</v>
@@ -1527,67 +1527,67 @@
         <v>0.14</v>
       </c>
       <c r="AK5">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="AL5">
-        <v>7.38</v>
+        <v>10.07</v>
       </c>
       <c r="AM5">
-        <v>9.779999999999999</v>
+        <v>12.83</v>
       </c>
       <c r="AN5">
-        <v>14.44</v>
+        <v>18.85</v>
       </c>
       <c r="AO5">
-        <v>0.06</v>
+        <v>0.25</v>
       </c>
       <c r="AP5">
+        <v>0.36</v>
+      </c>
+      <c r="AQ5">
+        <v>0.08</v>
+      </c>
+      <c r="AR5">
         <v>0.17</v>
       </c>
-      <c r="AQ5">
-        <v>0.05</v>
-      </c>
-      <c r="AR5">
-        <v>0.11</v>
-      </c>
       <c r="AS5">
-        <v>0.43</v>
+        <v>4.22</v>
       </c>
       <c r="AT5">
-        <v>0.38</v>
+        <v>0.13</v>
       </c>
       <c r="AU5">
-        <v>1.07</v>
+        <v>0.8</v>
       </c>
       <c r="AV5">
-        <v>1.74</v>
+        <v>1.36</v>
       </c>
       <c r="AW5">
-        <v>0.376</v>
+        <v>0.374</v>
       </c>
       <c r="AX5">
-        <v>0.387</v>
+        <v>0.389</v>
       </c>
       <c r="AY5">
-        <v>0.404</v>
+        <v>0.37</v>
       </c>
       <c r="AZ5">
-        <v>0.6870000000000001</v>
+        <v>0.657</v>
       </c>
       <c r="BA5">
-        <v>0.327</v>
+        <v>0.439</v>
       </c>
       <c r="BB5">
-        <v>0.428</v>
+        <v>0.338</v>
       </c>
       <c r="BC5">
-        <v>0.716</v>
+        <v>0.718</v>
       </c>
       <c r="BD5">
-        <v>0.93</v>
+        <v>0.909</v>
       </c>
       <c r="BE5">
-        <v>0.642</v>
+        <v>0.624</v>
       </c>
       <c r="BF5">
         <v>-0.916290731874155</v>
@@ -1596,10 +1596,10 @@
         <v>0.3465735902799726</v>
       </c>
       <c r="BH5">
-        <v>2.850400664966368</v>
+        <v>3.07235867977124</v>
       </c>
       <c r="BI5">
-        <v>0.4550732019756537</v>
+        <v>0.4485565353810899</v>
       </c>
     </row>
     <row r="6" spans="1:61">
@@ -1637,7 +1637,7 @@
         <v>0.1</v>
       </c>
       <c r="L6">
-        <v>0.4810072577223167</v>
+        <v>0.4857609569656579</v>
       </c>
       <c r="M6">
         <v>1.5</v>
@@ -1646,133 +1646,133 @@
         <v>0.09</v>
       </c>
       <c r="O6">
-        <v>0.141961907142805</v>
+        <v>0.1430026683381858</v>
       </c>
       <c r="P6">
-        <v>0.24</v>
+        <v>0.23</v>
       </c>
       <c r="Q6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R6">
-        <v>23.71850153060247</v>
+        <v>29.18304808049134</v>
       </c>
       <c r="S6">
-        <v>77</v>
+        <v>98</v>
       </c>
       <c r="T6">
-        <v>22.41</v>
+        <v>31.13</v>
       </c>
       <c r="U6">
-        <v>38.79766015777813</v>
+        <v>49.32145592021895</v>
       </c>
       <c r="V6">
-        <v>58.46</v>
+        <v>73.64</v>
       </c>
       <c r="W6">
-        <v>0.2</v>
+        <v>0.01</v>
       </c>
       <c r="X6">
-        <v>0.4493045480402115</v>
+        <v>0.2543752477548583</v>
       </c>
       <c r="Y6">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="Z6">
-        <v>0.22</v>
+        <v>0.13</v>
       </c>
       <c r="AA6">
-        <v>0.4191014617982123</v>
+        <v>0.3074434253152815</v>
       </c>
       <c r="AB6">
-        <v>0.6</v>
+        <v>0.52</v>
       </c>
       <c r="AC6">
-        <v>1.37</v>
+        <v>1.7</v>
       </c>
       <c r="AD6">
-        <v>1.7104614</v>
+        <v>2.1306</v>
       </c>
       <c r="AE6">
-        <v>2.05</v>
+        <v>2.56</v>
       </c>
       <c r="AF6">
-        <v>0.95</v>
+        <v>1.27</v>
       </c>
       <c r="AG6">
-        <v>1.35</v>
+        <v>1.75</v>
       </c>
       <c r="AH6">
-        <v>1.86</v>
+        <v>2.31</v>
       </c>
       <c r="AI6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="AJ6">
         <v>0.08</v>
       </c>
       <c r="AK6">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AL6">
-        <v>11.21</v>
+        <v>15.57</v>
       </c>
       <c r="AM6">
-        <v>16.02</v>
+        <v>21.59</v>
       </c>
       <c r="AN6">
-        <v>29.23</v>
+        <v>36.82</v>
       </c>
       <c r="AO6">
-        <v>0.06</v>
+        <v>0.25</v>
       </c>
       <c r="AP6">
-        <v>0.17</v>
+        <v>0.36</v>
       </c>
       <c r="AQ6">
-        <v>0.08</v>
+        <v>0.1</v>
       </c>
       <c r="AR6">
-        <v>0.15</v>
+        <v>0.22</v>
       </c>
       <c r="AS6">
-        <v>0.37</v>
+        <v>1.07</v>
       </c>
       <c r="AT6">
-        <v>0.45</v>
+        <v>0.25</v>
       </c>
       <c r="AU6">
-        <v>0.84</v>
+        <v>0.6</v>
       </c>
       <c r="AV6">
-        <v>1.21</v>
+        <v>1.03</v>
       </c>
       <c r="AW6">
-        <v>0.157</v>
+        <v>0.137</v>
       </c>
       <c r="AX6">
-        <v>0.604</v>
+        <v>0.63</v>
       </c>
       <c r="AY6">
-        <v>0.242</v>
+        <v>0.235</v>
       </c>
       <c r="AZ6">
-        <v>0.522</v>
+        <v>0.491</v>
       </c>
       <c r="BA6">
-        <v>0.5669999999999999</v>
+        <v>0.467</v>
       </c>
       <c r="BB6">
-        <v>0.247</v>
+        <v>0.317</v>
       </c>
       <c r="BC6">
-        <v>0.838</v>
+        <v>0.758</v>
       </c>
       <c r="BD6">
-        <v>0.969</v>
+        <v>0.9409999999999999</v>
       </c>
       <c r="BE6">
-        <v>0.124</v>
+        <v>0.217</v>
       </c>
       <c r="BF6">
         <v>-0.9485599924429405</v>
@@ -1781,10 +1781,10 @@
         <v>0.6770125502755524</v>
       </c>
       <c r="BH6">
-        <v>2.889246458864603</v>
+        <v>3.104855183708956</v>
       </c>
       <c r="BI6">
-        <v>0.7300315680902167</v>
+        <v>0.7406042537464091</v>
       </c>
     </row>
     <row r="7" spans="1:61">
@@ -1822,142 +1822,142 @@
         <v>0.4</v>
       </c>
       <c r="L7">
-        <v>0.6453522843629236</v>
+        <v>0.6498534832876538</v>
       </c>
       <c r="M7">
         <v>1</v>
       </c>
       <c r="N7">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="O7">
-        <v>0.451968778307284</v>
+        <v>0.4562897085833419</v>
       </c>
       <c r="P7">
-        <v>0.61</v>
+        <v>0.63</v>
       </c>
       <c r="Q7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R7">
-        <v>11.83398262644842</v>
+        <v>14.49254876667416</v>
       </c>
       <c r="S7">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="T7">
-        <v>10.03</v>
+        <v>13.03</v>
       </c>
       <c r="U7">
-        <v>12.96679646573161</v>
+        <v>17.12091857194247</v>
       </c>
       <c r="V7">
-        <v>16.29</v>
+        <v>21.58</v>
       </c>
       <c r="W7">
-        <v>0.2</v>
+        <v>0.01</v>
       </c>
       <c r="X7">
-        <v>0.4513492008437517</v>
+        <v>0.2519702365776113</v>
       </c>
       <c r="Y7">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="Z7">
-        <v>0.24</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AA7">
-        <v>0.5450466723391323</v>
+        <v>0.2903951331298376</v>
       </c>
       <c r="AB7">
-        <v>0.77</v>
+        <v>0.55</v>
       </c>
       <c r="AC7">
-        <v>1.37</v>
+        <v>1.7</v>
       </c>
       <c r="AD7">
-        <v>1.7104614</v>
+        <v>2.1306</v>
       </c>
       <c r="AE7">
-        <v>2.05</v>
+        <v>2.56</v>
       </c>
       <c r="AF7">
-        <v>1.24</v>
+        <v>1.68</v>
       </c>
       <c r="AG7">
-        <v>1.48</v>
+        <v>1.96</v>
       </c>
       <c r="AH7">
-        <v>1.67</v>
+        <v>2.21</v>
       </c>
       <c r="AI7">
         <v>0.17</v>
       </c>
       <c r="AJ7">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="AK7">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="AL7">
-        <v>5.01</v>
+        <v>6.51</v>
       </c>
       <c r="AM7">
-        <v>6.04</v>
+        <v>7.84</v>
       </c>
       <c r="AN7">
-        <v>8.15</v>
+        <v>10.79</v>
       </c>
       <c r="AO7">
-        <v>0.06</v>
+        <v>0.25</v>
       </c>
       <c r="AP7">
-        <v>0.17</v>
+        <v>0.36</v>
       </c>
       <c r="AQ7">
-        <v>0.06</v>
+        <v>0.1</v>
       </c>
       <c r="AR7">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="AS7">
-        <v>0.25</v>
+        <v>2.79</v>
       </c>
       <c r="AT7">
-        <v>0.48</v>
+        <v>0.14</v>
       </c>
       <c r="AU7">
-        <v>1.13</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AV7">
-        <v>1.53</v>
+        <v>1.1</v>
       </c>
       <c r="AW7">
-        <v>0.486</v>
+        <v>0.503</v>
       </c>
       <c r="AX7">
-        <v>0.303</v>
+        <v>0.291</v>
       </c>
       <c r="AY7">
-        <v>0.378</v>
+        <v>0.379</v>
       </c>
       <c r="AZ7">
-        <v>0.67</v>
+        <v>0.667</v>
       </c>
       <c r="BA7">
-        <v>1.082</v>
+        <v>0.992</v>
       </c>
       <c r="BB7">
-        <v>-0.04</v>
+        <v>0.004</v>
       </c>
       <c r="BC7">
-        <v>0.671</v>
+        <v>0.865</v>
       </c>
       <c r="BD7">
-        <v>0.9320000000000001</v>
+        <v>0.984</v>
       </c>
       <c r="BE7">
-        <v>0.04</v>
+        <v>0.226</v>
       </c>
       <c r="BF7">
         <v>-0.4581453659370775</v>
@@ -1966,10 +1966,10 @@
         <v>0.2290726829685387</v>
       </c>
       <c r="BH7">
-        <v>2.3873081824834</v>
+        <v>2.607554678595902</v>
       </c>
       <c r="BI7">
-        <v>0.3737833072133447</v>
+        <v>0.3758130023290042</v>
       </c>
     </row>
     <row r="8" spans="1:61">
@@ -2007,7 +2007,7 @@
         <v>0.05</v>
       </c>
       <c r="L8">
-        <v>0.2103511494347962</v>
+        <v>0.2072726064686639</v>
       </c>
       <c r="M8">
         <v>0.6</v>
@@ -2016,64 +2016,64 @@
         <v>0.05</v>
       </c>
       <c r="O8">
-        <v>0.07513850728983745</v>
+        <v>0.07470532981949277</v>
       </c>
       <c r="P8">
         <v>0.12</v>
       </c>
       <c r="Q8">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="R8">
-        <v>51.28831068419486</v>
+        <v>62.08473737560019</v>
       </c>
       <c r="S8">
-        <v>156</v>
+        <v>192</v>
       </c>
       <c r="T8">
-        <v>52.44</v>
+        <v>60.42</v>
       </c>
       <c r="U8">
-        <v>88.02675496729147</v>
+        <v>103.8178388359853</v>
       </c>
       <c r="V8">
-        <v>130.73</v>
+        <v>156.4</v>
       </c>
       <c r="W8">
-        <v>0.2</v>
+        <v>0.01</v>
       </c>
       <c r="X8">
-        <v>0.4501295422533491</v>
+        <v>0.2558019979207061</v>
       </c>
       <c r="Y8">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="Z8">
-        <v>0.23</v>
+        <v>0.11</v>
       </c>
       <c r="AA8">
-        <v>0.40552801320639</v>
+        <v>0.2895246783817018</v>
       </c>
       <c r="AB8">
-        <v>0.59</v>
+        <v>0.5</v>
       </c>
       <c r="AC8">
-        <v>1.37</v>
+        <v>1.7</v>
       </c>
       <c r="AD8">
-        <v>1.7104614</v>
+        <v>2.1306</v>
       </c>
       <c r="AE8">
-        <v>2.05</v>
+        <v>2.56</v>
       </c>
       <c r="AF8">
-        <v>1.07</v>
+        <v>1.25</v>
       </c>
       <c r="AG8">
-        <v>1.56</v>
+        <v>1.84</v>
       </c>
       <c r="AH8">
-        <v>2.33</v>
+        <v>2.72</v>
       </c>
       <c r="AI8">
         <v>0.02</v>
@@ -2085,64 +2085,64 @@
         <v>0.06</v>
       </c>
       <c r="AL8">
-        <v>26.22</v>
+        <v>30.21</v>
       </c>
       <c r="AM8">
-        <v>36.14</v>
+        <v>42.72</v>
       </c>
       <c r="AN8">
-        <v>65.36</v>
+        <v>78.2</v>
       </c>
       <c r="AO8">
-        <v>0.06</v>
+        <v>0.25</v>
       </c>
       <c r="AP8">
-        <v>0.17</v>
+        <v>0.36</v>
       </c>
       <c r="AQ8">
-        <v>0.06</v>
+        <v>0.09</v>
       </c>
       <c r="AR8">
-        <v>0.13</v>
+        <v>0.22</v>
       </c>
       <c r="AS8">
-        <v>0.28</v>
+        <v>1.39</v>
       </c>
       <c r="AT8">
-        <v>0.46</v>
+        <v>0.22</v>
       </c>
       <c r="AU8">
+        <v>0.57</v>
+      </c>
+      <c r="AV8">
+        <v>1</v>
+      </c>
+      <c r="AW8">
+        <v>0.172</v>
+      </c>
+      <c r="AX8">
+        <v>0.585</v>
+      </c>
+      <c r="AY8">
+        <v>0.285</v>
+      </c>
+      <c r="AZ8">
+        <v>0.5669999999999999</v>
+      </c>
+      <c r="BA8">
+        <v>0.494</v>
+      </c>
+      <c r="BB8">
+        <v>0.297</v>
+      </c>
+      <c r="BC8">
         <v>0.8100000000000001</v>
       </c>
-      <c r="AV8">
-        <v>1.18</v>
-      </c>
-      <c r="AW8">
-        <v>0.165</v>
-      </c>
-      <c r="AX8">
-        <v>0.594</v>
-      </c>
-      <c r="AY8">
-        <v>0.291</v>
-      </c>
-      <c r="AZ8">
-        <v>0.57</v>
-      </c>
-      <c r="BA8">
-        <v>0.506</v>
-      </c>
-      <c r="BB8">
-        <v>0.288</v>
-      </c>
-      <c r="BC8">
-        <v>0.784</v>
-      </c>
       <c r="BD8">
-        <v>0.954</v>
+        <v>0.963</v>
       </c>
       <c r="BE8">
-        <v>0.262</v>
+        <v>0.24</v>
       </c>
       <c r="BF8">
         <v>-1.753278948659991</v>
@@ -2151,10 +2151,10 @@
         <v>0.621226662447</v>
       </c>
       <c r="BH8">
-        <v>3.685176336563495</v>
+        <v>3.882131668820878</v>
       </c>
       <c r="BI8">
-        <v>0.6832453480998351</v>
+        <v>0.687548271569009</v>
       </c>
     </row>
     <row r="9" spans="1:61">
@@ -2192,142 +2192,142 @@
         <v>0.2</v>
       </c>
       <c r="L9">
-        <v>0.4232690266053805</v>
+        <v>0.42402562967178</v>
       </c>
       <c r="M9">
         <v>0.8</v>
       </c>
       <c r="N9">
+        <v>0.17</v>
+      </c>
+      <c r="O9">
+        <v>0.2417624427961031</v>
+      </c>
+      <c r="P9">
+        <v>0.35</v>
+      </c>
+      <c r="Q9">
+        <v>9</v>
+      </c>
+      <c r="R9">
+        <v>23.49238030076936</v>
+      </c>
+      <c r="S9">
+        <v>52</v>
+      </c>
+      <c r="T9">
+        <v>20.44</v>
+      </c>
+      <c r="U9">
+        <v>28.61919898320236</v>
+      </c>
+      <c r="V9">
+        <v>37.98</v>
+      </c>
+      <c r="W9">
+        <v>0.01</v>
+      </c>
+      <c r="X9">
+        <v>0.2544969701616051</v>
+      </c>
+      <c r="Y9">
+        <v>0.5</v>
+      </c>
+      <c r="Z9">
+        <v>0.06</v>
+      </c>
+      <c r="AA9">
+        <v>0.2695861310103066</v>
+      </c>
+      <c r="AB9">
+        <v>0.6</v>
+      </c>
+      <c r="AC9">
+        <v>1.7</v>
+      </c>
+      <c r="AD9">
+        <v>2.1306</v>
+      </c>
+      <c r="AE9">
+        <v>2.56</v>
+      </c>
+      <c r="AF9">
+        <v>1.38</v>
+      </c>
+      <c r="AG9">
+        <v>1.74</v>
+      </c>
+      <c r="AH9">
+        <v>2.07</v>
+      </c>
+      <c r="AI9">
+        <v>0.08</v>
+      </c>
+      <c r="AJ9">
+        <v>0.13</v>
+      </c>
+      <c r="AK9">
         <v>0.18</v>
       </c>
-      <c r="O9">
-        <v>0.2517769179080505</v>
-      </c>
-      <c r="P9">
-        <v>0.37</v>
-      </c>
-      <c r="Q9">
-        <v>7</v>
-      </c>
-      <c r="R9">
-        <v>19.03604960324683</v>
-      </c>
-      <c r="S9">
-        <v>42</v>
-      </c>
-      <c r="T9">
-        <v>14.78</v>
-      </c>
-      <c r="U9">
-        <v>21.37778594006091</v>
-      </c>
-      <c r="V9">
-        <v>28.65</v>
-      </c>
-      <c r="W9">
-        <v>0.2</v>
-      </c>
-      <c r="X9">
-        <v>0.4481053744470482</v>
-      </c>
-      <c r="Y9">
-        <v>0.7</v>
-      </c>
-      <c r="Z9">
-        <v>0.27</v>
-      </c>
-      <c r="AA9">
-        <v>0.4859006883017687</v>
-      </c>
-      <c r="AB9">
-        <v>0.7</v>
-      </c>
-      <c r="AC9">
-        <v>1.37</v>
-      </c>
-      <c r="AD9">
-        <v>1.7104614</v>
-      </c>
-      <c r="AE9">
-        <v>2.05</v>
-      </c>
-      <c r="AF9">
-        <v>1.06</v>
-      </c>
-      <c r="AG9">
-        <v>1.34</v>
-      </c>
-      <c r="AH9">
-        <v>1.62</v>
-      </c>
-      <c r="AI9">
-        <v>0.09</v>
-      </c>
-      <c r="AJ9">
-        <v>0.14</v>
-      </c>
-      <c r="AK9">
-        <v>0.19</v>
-      </c>
       <c r="AL9">
-        <v>7.39</v>
+        <v>10.22</v>
       </c>
       <c r="AM9">
-        <v>9.640000000000001</v>
+        <v>13.05</v>
       </c>
       <c r="AN9">
-        <v>14.33</v>
+        <v>18.99</v>
       </c>
       <c r="AO9">
-        <v>0.06</v>
+        <v>0.25</v>
       </c>
       <c r="AP9">
-        <v>0.17</v>
+        <v>0.36</v>
       </c>
       <c r="AQ9">
-        <v>0.07000000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="AR9">
-        <v>0.13</v>
+        <v>0.29</v>
       </c>
       <c r="AS9">
-        <v>0.26</v>
+        <v>4.9</v>
       </c>
       <c r="AT9">
-        <v>0.54</v>
+        <v>0.11</v>
       </c>
       <c r="AU9">
-        <v>0.97</v>
+        <v>0.48</v>
       </c>
       <c r="AV9">
-        <v>1.41</v>
+        <v>1.2</v>
       </c>
       <c r="AW9">
-        <v>0.345</v>
+        <v>0.344</v>
       </c>
       <c r="AX9">
         <v>0.413</v>
       </c>
       <c r="AY9">
-        <v>0.369</v>
+        <v>0.328</v>
       </c>
       <c r="AZ9">
-        <v>0.67</v>
+        <v>0.608</v>
       </c>
       <c r="BA9">
-        <v>0.678</v>
+        <v>1.248</v>
       </c>
       <c r="BB9">
-        <v>0.177</v>
+        <v>-0.117</v>
       </c>
       <c r="BC9">
-        <v>0.85</v>
+        <v>0.907</v>
       </c>
       <c r="BD9">
-        <v>0.977</v>
+        <v>0.991</v>
       </c>
       <c r="BE9">
-        <v>0.11</v>
+        <v>0.196</v>
       </c>
       <c r="BF9">
         <v>-0.916290731874155</v>
@@ -2336,10 +2336,10 @@
         <v>0.3465735902799726</v>
       </c>
       <c r="BH9">
-        <v>2.838167305393239</v>
+        <v>3.053381088212915</v>
       </c>
       <c r="BI9">
-        <v>0.4494892631910257</v>
+        <v>0.4509068262923319</v>
       </c>
     </row>
     <row r="10" spans="1:61">
@@ -2377,142 +2377,142 @@
         <v>0.1</v>
       </c>
       <c r="L10">
-        <v>0.4862414173515686</v>
+        <v>0.483020209755084</v>
       </c>
       <c r="M10">
         <v>1.5</v>
       </c>
       <c r="N10">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="O10">
-        <v>0.1364650287549802</v>
+        <v>0.1530361764478661</v>
       </c>
       <c r="P10">
-        <v>0.21</v>
+        <v>0.24</v>
       </c>
       <c r="Q10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R10">
-        <v>23.73255206558759</v>
+        <v>29.43600557905924</v>
       </c>
       <c r="S10">
-        <v>80</v>
+        <v>98</v>
       </c>
       <c r="T10">
-        <v>25.34</v>
+        <v>30.72</v>
       </c>
       <c r="U10">
-        <v>41.52635480301053</v>
+        <v>49.41142817663727</v>
       </c>
       <c r="V10">
-        <v>62.68</v>
+        <v>72.27</v>
       </c>
       <c r="W10">
         <v>0.01</v>
       </c>
       <c r="X10">
-        <v>0.1984895488750122</v>
+        <v>0.2316361747204777</v>
       </c>
       <c r="Y10">
-        <v>0.39</v>
+        <v>0.45</v>
       </c>
       <c r="Z10">
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
       <c r="AA10">
-        <v>0.2288361080750454</v>
+        <v>0.2725834804724409</v>
       </c>
       <c r="AB10">
-        <v>0.45</v>
+        <v>0.5</v>
       </c>
       <c r="AC10">
-        <v>1.37</v>
+        <v>1.7</v>
       </c>
       <c r="AD10">
-        <v>1.7104614</v>
+        <v>2.1306</v>
       </c>
       <c r="AE10">
-        <v>2.05</v>
+        <v>2.56</v>
       </c>
       <c r="AF10">
-        <v>0.96</v>
+        <v>1.4</v>
       </c>
       <c r="AG10">
-        <v>1.36</v>
+        <v>1.83</v>
       </c>
       <c r="AH10">
-        <v>1.96</v>
+        <v>2.43</v>
       </c>
       <c r="AI10">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="AJ10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="AK10">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="AL10">
-        <v>12.67</v>
+        <v>15.36</v>
       </c>
       <c r="AM10">
-        <v>17.83</v>
+        <v>21.39</v>
       </c>
       <c r="AN10">
-        <v>31.34</v>
+        <v>36.14</v>
       </c>
       <c r="AO10">
-        <v>0.06</v>
+        <v>0.25</v>
       </c>
       <c r="AP10">
+        <v>0.36</v>
+      </c>
+      <c r="AQ10">
+        <v>0.1</v>
+      </c>
+      <c r="AR10">
+        <v>0.23</v>
+      </c>
+      <c r="AS10">
+        <v>2.3</v>
+      </c>
+      <c r="AT10">
         <v>0.17</v>
       </c>
-      <c r="AQ10">
-        <v>0.11</v>
-      </c>
-      <c r="AR10">
-        <v>0.32</v>
-      </c>
-      <c r="AS10">
-        <v>4.61</v>
-      </c>
-      <c r="AT10">
-        <v>0.12</v>
-      </c>
       <c r="AU10">
-        <v>0.44</v>
+        <v>0.54</v>
       </c>
       <c r="AV10">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="AW10">
-        <v>0.126</v>
+        <v>0.116</v>
       </c>
       <c r="AX10">
-        <v>0.645</v>
+        <v>0.659</v>
       </c>
       <c r="AY10">
-        <v>0.207</v>
+        <v>0.246</v>
       </c>
       <c r="AZ10">
-        <v>0.461</v>
+        <v>0.502</v>
       </c>
       <c r="BA10">
-        <v>1.09</v>
+        <v>0.8139999999999999</v>
       </c>
       <c r="BB10">
-        <v>-0.044</v>
+        <v>0.098</v>
       </c>
       <c r="BC10">
-        <v>0.872</v>
+        <v>0.831</v>
       </c>
       <c r="BD10">
-        <v>0.987</v>
+        <v>0.979</v>
       </c>
       <c r="BE10">
-        <v>0.184</v>
+        <v>0.216</v>
       </c>
       <c r="BF10">
         <v>-0.9485599924429405</v>
@@ -2521,10 +2521,10 @@
         <v>0.6770125502755524</v>
       </c>
       <c r="BH10">
-        <v>2.890433338639702</v>
+        <v>3.08989955917729</v>
       </c>
       <c r="BI10">
-        <v>0.7449064785752859</v>
+        <v>0.745962398683009</v>
       </c>
     </row>
     <row r="11" spans="1:61">
@@ -2562,7 +2562,7 @@
         <v>0.4</v>
       </c>
       <c r="L11">
-        <v>0.6504329366864346</v>
+        <v>0.6466810126860438</v>
       </c>
       <c r="M11">
         <v>1</v>
@@ -2571,133 +2571,133 @@
         <v>0.35</v>
       </c>
       <c r="O11">
-        <v>0.46345291550084</v>
+        <v>0.4667400288360941</v>
       </c>
       <c r="P11">
         <v>0.63</v>
       </c>
       <c r="Q11">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R11">
-        <v>11.59784635031798</v>
+        <v>14.65440394017846</v>
       </c>
       <c r="S11">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="T11">
-        <v>9.74</v>
+        <v>12.71</v>
       </c>
       <c r="U11">
-        <v>12.58392667347656</v>
+        <v>16.9090238702135</v>
       </c>
       <c r="V11">
-        <v>15.5</v>
+        <v>21.7</v>
       </c>
       <c r="W11">
         <v>0.01</v>
       </c>
       <c r="X11">
-        <v>0.1992673932305912</v>
+        <v>0.2294562045312139</v>
       </c>
       <c r="Y11">
-        <v>0.39</v>
+        <v>0.45</v>
       </c>
       <c r="Z11">
-        <v>0.03</v>
+        <v>0.06</v>
       </c>
       <c r="AA11">
-        <v>0.1843684096371254</v>
+        <v>0.2399830613155363</v>
       </c>
       <c r="AB11">
-        <v>0.44</v>
+        <v>0.52</v>
       </c>
       <c r="AC11">
-        <v>1.37</v>
+        <v>1.7</v>
       </c>
       <c r="AD11">
-        <v>1.7104614</v>
+        <v>2.1306</v>
       </c>
       <c r="AE11">
-        <v>2.05</v>
+        <v>2.56</v>
       </c>
       <c r="AF11">
-        <v>1.25</v>
+        <v>1.69</v>
       </c>
       <c r="AG11">
-        <v>1.47</v>
+        <v>1.96</v>
       </c>
       <c r="AH11">
-        <v>1.66</v>
+        <v>2.21</v>
       </c>
       <c r="AI11">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AJ11">
         <v>0.25</v>
       </c>
       <c r="AK11">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="AL11">
-        <v>4.87</v>
+        <v>6.35</v>
       </c>
       <c r="AM11">
-        <v>5.77</v>
+        <v>7.8</v>
       </c>
       <c r="AN11">
-        <v>7.75</v>
+        <v>10.85</v>
       </c>
       <c r="AO11">
-        <v>0.06</v>
+        <v>0.25</v>
       </c>
       <c r="AP11">
-        <v>0.17</v>
+        <v>0.36</v>
       </c>
       <c r="AQ11">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="AR11">
-        <v>0.55</v>
+        <v>0.29</v>
       </c>
       <c r="AS11">
-        <v>14.88</v>
+        <v>4.41</v>
       </c>
       <c r="AT11">
-        <v>0.06</v>
+        <v>0.11</v>
       </c>
       <c r="AU11">
-        <v>0.32</v>
+        <v>0.44</v>
       </c>
       <c r="AV11">
-        <v>0.88</v>
+        <v>1.05</v>
       </c>
       <c r="AW11">
-        <v>0.485</v>
+        <v>0.58</v>
       </c>
       <c r="AX11">
-        <v>0.303</v>
+        <v>0.239</v>
       </c>
       <c r="AY11">
-        <v>0.407</v>
+        <v>0.435</v>
       </c>
       <c r="AZ11">
-        <v>0.6909999999999999</v>
+        <v>0.706</v>
       </c>
       <c r="BA11">
-        <v>1.475</v>
+        <v>1.198</v>
       </c>
       <c r="BB11">
-        <v>-0.215</v>
+        <v>-0.095</v>
       </c>
       <c r="BC11">
-        <v>0.872</v>
+        <v>0.878</v>
       </c>
       <c r="BD11">
-        <v>0.986</v>
+        <v>0.988</v>
       </c>
       <c r="BE11">
-        <v>0.182</v>
+        <v>0.215</v>
       </c>
       <c r="BF11">
         <v>-0.4581453659370775</v>
@@ -2706,10 +2706,10 @@
         <v>0.2290726829685387</v>
       </c>
       <c r="BH11">
-        <v>2.384866696937037</v>
+        <v>2.609816334574607</v>
       </c>
       <c r="BI11">
-        <v>0.3728431500535598</v>
+        <v>0.3771034280566181</v>
       </c>
     </row>
     <row r="12" spans="1:61">
@@ -2747,7 +2747,7 @@
         <v>0.05</v>
       </c>
       <c r="L12">
-        <v>0.2104130313389261</v>
+        <v>0.208598733380828</v>
       </c>
       <c r="M12">
         <v>0.6</v>
@@ -2756,64 +2756,64 @@
         <v>0.05</v>
       </c>
       <c r="O12">
-        <v>0.07362187899230502</v>
+        <v>0.07518490594986911</v>
       </c>
       <c r="P12">
         <v>0.12</v>
       </c>
       <c r="Q12">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="R12">
-        <v>49.04131338280277</v>
+        <v>61.28498256499262</v>
       </c>
       <c r="S12">
-        <v>154</v>
+        <v>189</v>
       </c>
       <c r="T12">
-        <v>50.08</v>
+        <v>57.86</v>
       </c>
       <c r="U12">
-        <v>86.04736229402522</v>
+        <v>98.87337096517133</v>
       </c>
       <c r="V12">
-        <v>129.44</v>
+        <v>149.89</v>
       </c>
       <c r="W12">
         <v>0.01</v>
       </c>
       <c r="X12">
-        <v>0.1983893834957944</v>
+        <v>0.2294805306190982</v>
       </c>
       <c r="Y12">
-        <v>0.39</v>
+        <v>0.45</v>
       </c>
       <c r="Z12">
-        <v>0.06</v>
+        <v>0.12</v>
       </c>
       <c r="AA12">
-        <v>0.2274103162691068</v>
+        <v>0.2949090288855903</v>
       </c>
       <c r="AB12">
-        <v>0.42</v>
+        <v>0.48</v>
       </c>
       <c r="AC12">
-        <v>1.37</v>
+        <v>1.7</v>
       </c>
       <c r="AD12">
-        <v>1.7104614</v>
+        <v>2.1306</v>
       </c>
       <c r="AE12">
-        <v>2.05</v>
+        <v>2.56</v>
       </c>
       <c r="AF12">
-        <v>1.02</v>
+        <v>1.17</v>
       </c>
       <c r="AG12">
-        <v>1.49</v>
+        <v>1.77</v>
       </c>
       <c r="AH12">
-        <v>2.25</v>
+        <v>2.69</v>
       </c>
       <c r="AI12">
         <v>0.02</v>
@@ -2825,64 +2825,64 @@
         <v>0.06</v>
       </c>
       <c r="AL12">
-        <v>25.04</v>
+        <v>28.93</v>
       </c>
       <c r="AM12">
-        <v>35.17</v>
+        <v>41.09</v>
       </c>
       <c r="AN12">
-        <v>64.72</v>
+        <v>74.94</v>
       </c>
       <c r="AO12">
-        <v>0.06</v>
+        <v>0.25</v>
       </c>
       <c r="AP12">
-        <v>0.17</v>
+        <v>0.36</v>
       </c>
       <c r="AQ12">
         <v>0.1</v>
       </c>
       <c r="AR12">
-        <v>0.28</v>
+        <v>0.22</v>
       </c>
       <c r="AS12">
-        <v>4.08</v>
+        <v>1.15</v>
       </c>
       <c r="AT12">
-        <v>0.12</v>
+        <v>0.24</v>
       </c>
       <c r="AU12">
+        <v>0.59</v>
+      </c>
+      <c r="AV12">
+        <v>0.97</v>
+      </c>
+      <c r="AW12">
+        <v>0.183</v>
+      </c>
+      <c r="AX12">
+        <v>0.572</v>
+      </c>
+      <c r="AY12">
+        <v>0.293</v>
+      </c>
+      <c r="AZ12">
+        <v>0.5669999999999999</v>
+      </c>
+      <c r="BA12">
         <v>0.45</v>
       </c>
-      <c r="AV12">
-        <v>0.84</v>
-      </c>
-      <c r="AW12">
-        <v>0.182</v>
-      </c>
-      <c r="AX12">
-        <v>0.574</v>
-      </c>
-      <c r="AY12">
-        <v>0.275</v>
-      </c>
-      <c r="AZ12">
-        <v>0.549</v>
-      </c>
-      <c r="BA12">
-        <v>0.889</v>
-      </c>
       <c r="BB12">
-        <v>0.057</v>
+        <v>0.329</v>
       </c>
       <c r="BC12">
-        <v>0.85</v>
+        <v>0.697</v>
       </c>
       <c r="BD12">
-        <v>0.985</v>
+        <v>0.921</v>
       </c>
       <c r="BE12">
-        <v>0.148</v>
+        <v>0.212</v>
       </c>
       <c r="BF12">
         <v>-1.753278948659991</v>
@@ -2891,10 +2891,10 @@
         <v>0.621226662447</v>
       </c>
       <c r="BH12">
-        <v>3.662123326723527</v>
+        <v>3.882971236644802</v>
       </c>
       <c r="BI12">
-        <v>0.6889286367768268</v>
+        <v>0.6782757249540974</v>
       </c>
     </row>
     <row r="13" spans="1:61">
@@ -2932,7 +2932,7 @@
         <v>0.2</v>
       </c>
       <c r="L13">
-        <v>0.4239249219097995</v>
+        <v>0.4264053132601757</v>
       </c>
       <c r="M13">
         <v>0.8</v>
@@ -2941,133 +2941,133 @@
         <v>0.17</v>
       </c>
       <c r="O13">
-        <v>0.2421616259483194</v>
+        <v>0.242735293085972</v>
       </c>
       <c r="P13">
-        <v>0.35</v>
+        <v>0.37</v>
       </c>
       <c r="Q13">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="R13">
-        <v>19.10535358930238</v>
+        <v>23.79473291427388</v>
       </c>
       <c r="S13">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="T13">
-        <v>15.19</v>
+        <v>20.07</v>
       </c>
       <c r="U13">
-        <v>21.74859080204942</v>
+        <v>28.78755744490751</v>
       </c>
       <c r="V13">
-        <v>29.72</v>
+        <v>38.48</v>
       </c>
       <c r="W13">
         <v>0.01</v>
       </c>
       <c r="X13">
-        <v>0.2005644107930071</v>
+        <v>0.2300706623918626</v>
       </c>
       <c r="Y13">
-        <v>0.39</v>
+        <v>0.45</v>
       </c>
       <c r="Z13">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="AA13">
-        <v>0.2598886618988198</v>
+        <v>0.248919268439218</v>
       </c>
       <c r="AB13">
-        <v>0.55</v>
+        <v>0.51</v>
       </c>
       <c r="AC13">
-        <v>1.37</v>
+        <v>1.7</v>
       </c>
       <c r="AD13">
-        <v>1.7104614</v>
+        <v>2.1306</v>
       </c>
       <c r="AE13">
-        <v>2.05</v>
+        <v>2.56</v>
       </c>
       <c r="AF13">
-        <v>1.04</v>
+        <v>1.38</v>
       </c>
       <c r="AG13">
-        <v>1.33</v>
+        <v>1.77</v>
       </c>
       <c r="AH13">
-        <v>1.6</v>
+        <v>2.06</v>
       </c>
       <c r="AI13">
         <v>0.08</v>
       </c>
       <c r="AJ13">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="AK13">
         <v>0.18</v>
       </c>
       <c r="AL13">
-        <v>7.59</v>
+        <v>10.04</v>
       </c>
       <c r="AM13">
-        <v>10.08</v>
+        <v>13.05</v>
       </c>
       <c r="AN13">
-        <v>14.86</v>
+        <v>19.24</v>
       </c>
       <c r="AO13">
-        <v>0.06</v>
+        <v>0.25</v>
       </c>
       <c r="AP13">
-        <v>0.17</v>
+        <v>0.36</v>
       </c>
       <c r="AQ13">
+        <v>0.11</v>
+      </c>
+      <c r="AR13">
+        <v>0.32</v>
+      </c>
+      <c r="AS13">
+        <v>5.98</v>
+      </c>
+      <c r="AT13">
         <v>0.1</v>
       </c>
-      <c r="AR13">
-        <v>0.3</v>
-      </c>
-      <c r="AS13">
-        <v>11.84</v>
-      </c>
-      <c r="AT13">
-        <v>0.07000000000000001</v>
-      </c>
       <c r="AU13">
-        <v>0.47</v>
+        <v>0.46</v>
       </c>
       <c r="AV13">
-        <v>1.09</v>
+        <v>1.02</v>
       </c>
       <c r="AW13">
-        <v>0.347</v>
+        <v>0.399</v>
       </c>
       <c r="AX13">
-        <v>0.411</v>
+        <v>0.368</v>
       </c>
       <c r="AY13">
-        <v>0.331</v>
+        <v>0.337</v>
       </c>
       <c r="AZ13">
-        <v>0.614</v>
+        <v>0.631</v>
       </c>
       <c r="BA13">
-        <v>1.968</v>
+        <v>1.248</v>
       </c>
       <c r="BB13">
-        <v>-0.403</v>
+        <v>-0.117</v>
       </c>
       <c r="BC13">
-        <v>0.744</v>
+        <v>0.895</v>
       </c>
       <c r="BD13">
-        <v>0.9389999999999999</v>
+        <v>0.99</v>
       </c>
       <c r="BE13">
-        <v>0.142</v>
+        <v>0.2</v>
       </c>
       <c r="BF13">
         <v>-0.916290731874155</v>
@@ -3076,10 +3076,10 @@
         <v>0.3465735902799726</v>
       </c>
       <c r="BH13">
-        <v>2.845764912034643</v>
+        <v>3.072112071529144</v>
       </c>
       <c r="BI13">
-        <v>0.4573757109553629</v>
+        <v>0.4592705846385061</v>
       </c>
     </row>
     <row r="14" spans="1:61">
@@ -3117,7 +3117,7 @@
         <v>0.1</v>
       </c>
       <c r="L14">
-        <v>0.4831632600137727</v>
+        <v>0.4845458918197847</v>
       </c>
       <c r="M14">
         <v>1.5</v>
@@ -3126,67 +3126,67 @@
         <v>0.09</v>
       </c>
       <c r="O14">
-        <v>0.1441591908481783</v>
+        <v>0.1393376427894263</v>
       </c>
       <c r="P14">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="Q14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R14">
-        <v>23.24982774726324</v>
+        <v>28.69130574155313</v>
       </c>
       <c r="S14">
-        <v>76</v>
+        <v>95</v>
       </c>
       <c r="T14">
-        <v>23.32</v>
+        <v>30.16</v>
       </c>
       <c r="U14">
-        <v>38.1405822167963</v>
+        <v>46.11143919237952</v>
       </c>
       <c r="V14">
-        <v>58.26</v>
+        <v>67.84</v>
       </c>
       <c r="W14">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="X14">
-        <v>0.1199630303523375</v>
+        <v>0.1396351278660407</v>
       </c>
       <c r="Y14">
-        <v>0.22</v>
+        <v>0.25</v>
       </c>
       <c r="Z14">
-        <v>0.03</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AA14">
-        <v>0.1189305083398666</v>
+        <v>0.1557170294980393</v>
       </c>
       <c r="AB14">
-        <v>0.23</v>
+        <v>0.27</v>
       </c>
       <c r="AC14">
-        <v>1.37</v>
+        <v>1.7</v>
       </c>
       <c r="AD14">
-        <v>1.7104614</v>
+        <v>2.1306</v>
       </c>
       <c r="AE14">
-        <v>2.05</v>
+        <v>2.56</v>
       </c>
       <c r="AF14">
-        <v>0.96</v>
+        <v>1.14</v>
       </c>
       <c r="AG14">
-        <v>1.33</v>
+        <v>1.62</v>
       </c>
       <c r="AH14">
-        <v>1.83</v>
+        <v>2.13</v>
       </c>
       <c r="AI14">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="AJ14">
         <v>0.08</v>
@@ -3195,64 +3195,64 @@
         <v>0.11</v>
       </c>
       <c r="AL14">
-        <v>11.66</v>
+        <v>15.08</v>
       </c>
       <c r="AM14">
-        <v>16.12</v>
+        <v>20.53</v>
       </c>
       <c r="AN14">
-        <v>29.13</v>
+        <v>33.92</v>
       </c>
       <c r="AO14">
-        <v>0.06</v>
+        <v>0.25</v>
       </c>
       <c r="AP14">
-        <v>0.17</v>
+        <v>0.36</v>
       </c>
       <c r="AQ14">
-        <v>0.26</v>
+        <v>0.23</v>
       </c>
       <c r="AR14">
-        <v>1.19</v>
+        <v>0.8</v>
       </c>
       <c r="AS14">
-        <v>13.98</v>
+        <v>3.8</v>
       </c>
       <c r="AT14">
-        <v>0.07000000000000001</v>
+        <v>0.14</v>
       </c>
       <c r="AU14">
-        <v>0.23</v>
+        <v>0.3</v>
       </c>
       <c r="AV14">
-        <v>0.46</v>
+        <v>0.55</v>
       </c>
       <c r="AW14">
-        <v>0.136</v>
+        <v>0.148</v>
       </c>
       <c r="AX14">
-        <v>0.632</v>
+        <v>0.616</v>
       </c>
       <c r="AY14">
-        <v>0.233</v>
+        <v>0.222</v>
       </c>
       <c r="AZ14">
-        <v>0.505</v>
+        <v>0.48</v>
       </c>
       <c r="BA14">
-        <v>1.095</v>
+        <v>0.669</v>
       </c>
       <c r="BB14">
-        <v>-0.047</v>
+        <v>0.182</v>
       </c>
       <c r="BC14">
-        <v>0.969</v>
+        <v>0.863</v>
       </c>
       <c r="BD14">
-        <v>0.997</v>
+        <v>0.979</v>
       </c>
       <c r="BE14">
-        <v>0.01</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="BF14">
         <v>-0.9485599924429405</v>
@@ -3261,10 +3261,10 @@
         <v>0.6770125502755524</v>
       </c>
       <c r="BH14">
-        <v>2.8571159574991</v>
+        <v>3.083974400363417</v>
       </c>
       <c r="BI14">
-        <v>0.7397514192977308</v>
+        <v>0.7358061353735287</v>
       </c>
     </row>
     <row r="15" spans="1:61">
@@ -3302,142 +3302,142 @@
         <v>0.4</v>
       </c>
       <c r="L15">
-        <v>0.6484270966247414</v>
+        <v>0.6478821127778311</v>
       </c>
       <c r="M15">
         <v>1</v>
       </c>
       <c r="N15">
-        <v>0.34</v>
+        <v>0.36</v>
       </c>
       <c r="O15">
-        <v>0.4556755355737274</v>
+        <v>0.4701073452371923</v>
       </c>
       <c r="P15">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="Q15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R15">
-        <v>11.6196568860577</v>
+        <v>14.38825197423413</v>
       </c>
       <c r="S15">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="T15">
-        <v>9.640000000000001</v>
+        <v>12.54</v>
       </c>
       <c r="U15">
-        <v>12.89237321114072</v>
+        <v>16.75397715170136</v>
       </c>
       <c r="V15">
-        <v>15.87</v>
+        <v>20.93</v>
       </c>
       <c r="W15">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="X15">
-        <v>0.1197989386103193</v>
+        <v>0.1391199592325491</v>
       </c>
       <c r="Y15">
-        <v>0.22</v>
+        <v>0.25</v>
       </c>
       <c r="Z15">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="AA15">
-        <v>0.1135254003983858</v>
+        <v>0.1271850029442387</v>
       </c>
       <c r="AB15">
-        <v>0.24</v>
+        <v>0.26</v>
       </c>
       <c r="AC15">
-        <v>1.37</v>
+        <v>1.7</v>
       </c>
       <c r="AD15">
-        <v>1.7104614</v>
+        <v>2.1306</v>
       </c>
       <c r="AE15">
-        <v>2.05</v>
+        <v>2.56</v>
       </c>
       <c r="AF15">
-        <v>1.25</v>
+        <v>1.7</v>
       </c>
       <c r="AG15">
-        <v>1.48</v>
+        <v>1.97</v>
       </c>
       <c r="AH15">
-        <v>1.69</v>
+        <v>2.19</v>
       </c>
       <c r="AI15">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="AJ15">
         <v>0.26</v>
       </c>
       <c r="AK15">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="AL15">
-        <v>4.82</v>
+        <v>6.27</v>
       </c>
       <c r="AM15">
-        <v>5.78</v>
+        <v>7.6</v>
       </c>
       <c r="AN15">
-        <v>7.94</v>
+        <v>10.46</v>
       </c>
       <c r="AO15">
-        <v>0.06</v>
+        <v>0.25</v>
       </c>
       <c r="AP15">
-        <v>0.17</v>
+        <v>0.36</v>
       </c>
       <c r="AQ15">
+        <v>0.22</v>
+      </c>
+      <c r="AR15">
+        <v>0.98</v>
+      </c>
+      <c r="AS15">
+        <v>9.59</v>
+      </c>
+      <c r="AT15">
+        <v>0.08</v>
+      </c>
+      <c r="AU15">
         <v>0.24</v>
       </c>
-      <c r="AR15">
-        <v>1.23</v>
-      </c>
-      <c r="AS15">
-        <v>13.58</v>
-      </c>
-      <c r="AT15">
-        <v>0.06</v>
-      </c>
-      <c r="AU15">
-        <v>0.21</v>
-      </c>
       <c r="AV15">
-        <v>0.47</v>
+        <v>0.51</v>
       </c>
       <c r="AW15">
-        <v>0.549</v>
+        <v>0.547</v>
       </c>
       <c r="AX15">
-        <v>0.259</v>
+        <v>0.26</v>
       </c>
       <c r="AY15">
-        <v>0.392</v>
+        <v>0.425</v>
       </c>
       <c r="AZ15">
-        <v>0.694</v>
+        <v>0.728</v>
       </c>
       <c r="BA15">
-        <v>1.084</v>
+        <v>1.218</v>
       </c>
       <c r="BB15">
-        <v>-0.041</v>
+        <v>-0.104</v>
       </c>
       <c r="BC15">
-        <v>0.9379999999999999</v>
+        <v>0.906</v>
       </c>
       <c r="BD15">
-        <v>0.996</v>
+        <v>0.992</v>
       </c>
       <c r="BE15">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="BF15">
         <v>-0.4581453659370775</v>
@@ -3446,10 +3446,10 @@
         <v>0.2290726829685387</v>
       </c>
       <c r="BH15">
-        <v>2.382417613376656</v>
+        <v>2.599812018266248</v>
       </c>
       <c r="BI15">
-        <v>0.3746635712590229</v>
+        <v>0.3765642992558799</v>
       </c>
     </row>
     <row r="16" spans="1:61">
@@ -3487,7 +3487,7 @@
         <v>0.05</v>
       </c>
       <c r="L16">
-        <v>0.2085903888448674</v>
+        <v>0.2060191597333187</v>
       </c>
       <c r="M16">
         <v>0.6</v>
@@ -3496,64 +3496,64 @@
         <v>0.05</v>
       </c>
       <c r="O16">
-        <v>0.0757349359463427</v>
+        <v>0.07572639329945918</v>
       </c>
       <c r="P16">
         <v>0.12</v>
       </c>
       <c r="Q16">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="R16">
-        <v>50.77744267595575</v>
+        <v>63.09637118766067</v>
       </c>
       <c r="S16">
-        <v>161</v>
+        <v>198</v>
       </c>
       <c r="T16">
-        <v>48.16</v>
+        <v>58.88</v>
       </c>
       <c r="U16">
-        <v>89.58852845224459</v>
+        <v>106.7689002203136</v>
       </c>
       <c r="V16">
-        <v>134.38</v>
+        <v>160.95</v>
       </c>
       <c r="W16">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="X16">
-        <v>0.1197950673295667</v>
+        <v>0.1397793395221022</v>
       </c>
       <c r="Y16">
-        <v>0.22</v>
+        <v>0.25</v>
       </c>
       <c r="Z16">
-        <v>0.05</v>
+        <v>0.08</v>
       </c>
       <c r="AA16">
-        <v>0.1350734147520163</v>
+        <v>0.1761952326279719</v>
       </c>
       <c r="AB16">
-        <v>0.26</v>
+        <v>0.31</v>
       </c>
       <c r="AC16">
-        <v>1.37</v>
+        <v>1.7</v>
       </c>
       <c r="AD16">
-        <v>1.7104614</v>
+        <v>2.1306</v>
       </c>
       <c r="AE16">
-        <v>2.05</v>
+        <v>2.56</v>
       </c>
       <c r="AF16">
-        <v>1.1</v>
+        <v>1.31</v>
       </c>
       <c r="AG16">
-        <v>1.52</v>
+        <v>1.85</v>
       </c>
       <c r="AH16">
-        <v>2.35</v>
+        <v>2.76</v>
       </c>
       <c r="AI16">
         <v>0.02</v>
@@ -3565,64 +3565,64 @@
         <v>0.06</v>
       </c>
       <c r="AL16">
-        <v>24.08</v>
+        <v>29.44</v>
       </c>
       <c r="AM16">
-        <v>32.47</v>
+        <v>40.98</v>
       </c>
       <c r="AN16">
-        <v>67.19</v>
+        <v>80.48</v>
       </c>
       <c r="AO16">
-        <v>0.06</v>
+        <v>0.25</v>
       </c>
       <c r="AP16">
-        <v>0.17</v>
+        <v>0.36</v>
       </c>
       <c r="AQ16">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="AR16">
-        <v>0.77</v>
+        <v>0.51</v>
       </c>
       <c r="AS16">
-        <v>4.72</v>
+        <v>2.53</v>
       </c>
       <c r="AT16">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="AU16">
-        <v>0.26</v>
+        <v>0.34</v>
       </c>
       <c r="AV16">
-        <v>0.52</v>
+        <v>0.62</v>
       </c>
       <c r="AW16">
-        <v>0.177</v>
+        <v>0.171</v>
       </c>
       <c r="AX16">
-        <v>0.58</v>
+        <v>0.586</v>
       </c>
       <c r="AY16">
-        <v>0.292</v>
+        <v>0.285</v>
       </c>
       <c r="AZ16">
-        <v>0.586</v>
+        <v>0.574</v>
       </c>
       <c r="BA16">
-        <v>0.802</v>
+        <v>0.755</v>
       </c>
       <c r="BB16">
-        <v>0.104</v>
+        <v>0.131</v>
       </c>
       <c r="BC16">
-        <v>0.877</v>
+        <v>0.753</v>
       </c>
       <c r="BD16">
-        <v>0.985</v>
+        <v>0.947</v>
       </c>
       <c r="BE16">
-        <v>0.025</v>
+        <v>0.027</v>
       </c>
       <c r="BF16">
         <v>-1.753278948659991</v>
@@ -3631,10 +3631,10 @@
         <v>0.621226662447</v>
       </c>
       <c r="BH16">
-        <v>3.697698392092545</v>
+        <v>3.896842732964714</v>
       </c>
       <c r="BI16">
-        <v>0.6916722422588122</v>
+        <v>0.6969362148450884</v>
       </c>
     </row>
     <row r="17" spans="1:61">
@@ -3672,7 +3672,7 @@
         <v>0.2</v>
       </c>
       <c r="L17">
-        <v>0.4229877796347178</v>
+        <v>0.427093069625704</v>
       </c>
       <c r="M17">
         <v>0.8</v>
@@ -3681,133 +3681,133 @@
         <v>0.17</v>
       </c>
       <c r="O17">
-        <v>0.2469094949737821</v>
+        <v>0.244032546779402</v>
       </c>
       <c r="P17">
         <v>0.36</v>
       </c>
       <c r="Q17">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="R17">
-        <v>18.97687081989667</v>
+        <v>23.44803207612901</v>
       </c>
       <c r="S17">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="T17">
-        <v>15.01</v>
+        <v>20.32</v>
       </c>
       <c r="U17">
-        <v>21.04183162341781</v>
+        <v>28.53116524978489</v>
       </c>
       <c r="V17">
-        <v>28.45</v>
+        <v>37.44</v>
       </c>
       <c r="W17">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="X17">
-        <v>0.120110540260447</v>
+        <v>0.139423399118724</v>
       </c>
       <c r="Y17">
-        <v>0.22</v>
+        <v>0.25</v>
       </c>
       <c r="Z17">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="AA17">
-        <v>0.1118114635420077</v>
+        <v>0.1463654764023989</v>
       </c>
       <c r="AB17">
-        <v>0.22</v>
+        <v>0.29</v>
       </c>
       <c r="AC17">
+        <v>1.7</v>
+      </c>
+      <c r="AD17">
+        <v>2.1306</v>
+      </c>
+      <c r="AE17">
+        <v>2.56</v>
+      </c>
+      <c r="AF17">
         <v>1.37</v>
       </c>
-      <c r="AD17">
-        <v>1.7104614</v>
-      </c>
-      <c r="AE17">
-        <v>2.05</v>
-      </c>
-      <c r="AF17">
-        <v>1.03</v>
-      </c>
       <c r="AG17">
-        <v>1.32</v>
+        <v>1.76</v>
       </c>
       <c r="AH17">
-        <v>1.58</v>
+        <v>2.07</v>
       </c>
       <c r="AI17">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AJ17">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="AK17">
         <v>0.18</v>
       </c>
       <c r="AL17">
-        <v>7.51</v>
+        <v>10.16</v>
       </c>
       <c r="AM17">
-        <v>9.800000000000001</v>
+        <v>12.95</v>
       </c>
       <c r="AN17">
-        <v>14.23</v>
+        <v>18.72</v>
       </c>
       <c r="AO17">
-        <v>0.06</v>
+        <v>0.25</v>
       </c>
       <c r="AP17">
-        <v>0.17</v>
+        <v>0.36</v>
       </c>
       <c r="AQ17">
-        <v>0.3</v>
+        <v>0.21</v>
       </c>
       <c r="AR17">
-        <v>1.41</v>
+        <v>0.85</v>
       </c>
       <c r="AS17">
-        <v>15.75</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="AT17">
-        <v>0.06</v>
+        <v>0.09</v>
       </c>
       <c r="AU17">
-        <v>0.21</v>
+        <v>0.28</v>
       </c>
       <c r="AV17">
-        <v>0.44</v>
+        <v>0.59</v>
       </c>
       <c r="AW17">
-        <v>0.345</v>
+        <v>0.37</v>
       </c>
       <c r="AX17">
-        <v>0.413</v>
+        <v>0.392</v>
       </c>
       <c r="AY17">
-        <v>0.347</v>
+        <v>0.339</v>
       </c>
       <c r="AZ17">
-        <v>0.634</v>
+        <v>0.635</v>
       </c>
       <c r="BA17">
-        <v>1.057</v>
+        <v>1.186</v>
       </c>
       <c r="BB17">
-        <v>-0.028</v>
+        <v>-0.089</v>
       </c>
       <c r="BC17">
-        <v>0.9330000000000001</v>
+        <v>0.947</v>
       </c>
       <c r="BD17">
-        <v>0.994</v>
+        <v>0.995</v>
       </c>
       <c r="BE17">
-        <v>0.005</v>
+        <v>0.006</v>
       </c>
       <c r="BF17">
         <v>-0.916290731874155</v>
@@ -3816,10 +3816,10 @@
         <v>0.3465735902799726</v>
       </c>
       <c r="BH17">
-        <v>2.832461754152476</v>
+        <v>3.056453106642124</v>
       </c>
       <c r="BI17">
-        <v>0.4615469236443074</v>
+        <v>0.4580880929667634</v>
       </c>
     </row>
   </sheetData>

--- a/Catch models/cmsy_out_macarellus_cmsy.xlsx
+++ b/Catch models/cmsy_out_macarellus_cmsy.xlsx
@@ -897,16 +897,16 @@
         <v>0.1</v>
       </c>
       <c r="L2">
-        <v>0.487690864500715</v>
+        <v>0.493514255446269</v>
       </c>
       <c r="M2">
         <v>1.5</v>
       </c>
       <c r="N2">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="O2">
-        <v>0.142855069264874</v>
+        <v>0.1471124873021576</v>
       </c>
       <c r="P2">
         <v>0.23</v>
@@ -915,25 +915,25 @@
         <v>5</v>
       </c>
       <c r="R2">
-        <v>29.367163803133</v>
+        <v>29.0211839818056</v>
       </c>
       <c r="S2">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="T2">
-        <v>29.84</v>
+        <v>31.5</v>
       </c>
       <c r="U2">
-        <v>47.40943144420574</v>
+        <v>52.89859688969557</v>
       </c>
       <c r="V2">
-        <v>69.39</v>
+        <v>78.23</v>
       </c>
       <c r="W2">
         <v>0.01</v>
       </c>
       <c r="X2">
-        <v>0.5038728433596689</v>
+        <v>0.5050626527942176</v>
       </c>
       <c r="Y2">
         <v>1</v>
@@ -942,10 +942,10 @@
         <v>0.08</v>
       </c>
       <c r="AA2">
-        <v>0.3744987528694565</v>
+        <v>0.3584134523538798</v>
       </c>
       <c r="AB2">
-        <v>0.61</v>
+        <v>0.63</v>
       </c>
       <c r="AC2">
         <v>1.7</v>
@@ -957,31 +957,31 @@
         <v>2.56</v>
       </c>
       <c r="AF2">
-        <v>1.18</v>
+        <v>1.44</v>
       </c>
       <c r="AG2">
-        <v>1.69</v>
+        <v>1.88</v>
       </c>
       <c r="AH2">
-        <v>2.25</v>
+        <v>2.43</v>
       </c>
       <c r="AI2">
         <v>0.05</v>
       </c>
       <c r="AJ2">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="AK2">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="AL2">
-        <v>14.92</v>
+        <v>15.75</v>
       </c>
       <c r="AM2">
-        <v>21.14</v>
+        <v>21.67</v>
       </c>
       <c r="AN2">
-        <v>34.7</v>
+        <v>39.12</v>
       </c>
       <c r="AO2">
         <v>0.25</v>
@@ -993,46 +993,46 @@
         <v>0.08</v>
       </c>
       <c r="AR2">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="AS2">
-        <v>3.16</v>
+        <v>2.73</v>
       </c>
       <c r="AT2">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="AU2">
-        <v>0.78</v>
+        <v>0.74</v>
       </c>
       <c r="AV2">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="AW2">
-        <v>0.145</v>
+        <v>0.127</v>
       </c>
       <c r="AX2">
-        <v>0.619</v>
+        <v>0.643</v>
       </c>
       <c r="AY2">
-        <v>0.237</v>
+        <v>0.233</v>
       </c>
       <c r="AZ2">
-        <v>0.484</v>
+        <v>0.506</v>
       </c>
       <c r="BA2">
-        <v>0.335</v>
+        <v>0.302</v>
       </c>
       <c r="BB2">
-        <v>0.422</v>
+        <v>0.45</v>
       </c>
       <c r="BC2">
-        <v>0.593</v>
+        <v>0.635</v>
       </c>
       <c r="BD2">
-        <v>0.843</v>
+        <v>0.856</v>
       </c>
       <c r="BE2">
-        <v>0.614</v>
+        <v>0.584</v>
       </c>
       <c r="BF2">
         <v>-0.9485599924429405</v>
@@ -1041,10 +1041,10 @@
         <v>0.6770125502755524</v>
       </c>
       <c r="BH2">
-        <v>3.111697501832504</v>
+        <v>3.084117564756091</v>
       </c>
       <c r="BI2">
-        <v>0.7188408482022784</v>
+        <v>0.7489833948764801</v>
       </c>
     </row>
     <row r="3" spans="1:61">
@@ -1082,7 +1082,7 @@
         <v>0.4</v>
       </c>
       <c r="L3">
-        <v>0.6485521093212695</v>
+        <v>0.6496030465850088</v>
       </c>
       <c r="M3">
         <v>1</v>
@@ -1091,46 +1091,46 @@
         <v>0.36</v>
       </c>
       <c r="O3">
-        <v>0.4885579765100392</v>
+        <v>0.4802359139323749</v>
       </c>
       <c r="P3">
-        <v>0.68</v>
+        <v>0.67</v>
       </c>
       <c r="Q3">
         <v>6</v>
       </c>
       <c r="R3">
-        <v>14.54129149715241</v>
+        <v>14.38974788318465</v>
       </c>
       <c r="S3">
         <v>28</v>
       </c>
       <c r="T3">
-        <v>12.21</v>
+        <v>12.26</v>
       </c>
       <c r="U3">
-        <v>16.34932007067712</v>
+        <v>16.75811028317288</v>
       </c>
       <c r="V3">
-        <v>21.01</v>
+        <v>21.3</v>
       </c>
       <c r="W3">
         <v>0.01</v>
       </c>
       <c r="X3">
-        <v>0.4982595252544935</v>
+        <v>0.5035943054155001</v>
       </c>
       <c r="Y3">
         <v>1</v>
       </c>
       <c r="Z3">
-        <v>0.24</v>
+        <v>0.08</v>
       </c>
       <c r="AA3">
-        <v>0.6695081974534716</v>
+        <v>0.6323857974916437</v>
       </c>
       <c r="AB3">
-        <v>0.93</v>
+        <v>0.95</v>
       </c>
       <c r="AC3">
         <v>1.7</v>
@@ -1142,10 +1142,10 @@
         <v>2.56</v>
       </c>
       <c r="AF3">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="AG3">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="AH3">
         <v>2.23</v>
@@ -1160,13 +1160,13 @@
         <v>0.34</v>
       </c>
       <c r="AL3">
-        <v>6.1</v>
+        <v>6.13</v>
       </c>
       <c r="AM3">
-        <v>7.45</v>
+        <v>7.51</v>
       </c>
       <c r="AN3">
-        <v>10.51</v>
+        <v>10.65</v>
       </c>
       <c r="AO3">
         <v>0.25</v>
@@ -1181,43 +1181,43 @@
         <v>0.08</v>
       </c>
       <c r="AS3">
-        <v>0.26</v>
+        <v>2.05</v>
       </c>
       <c r="AT3">
-        <v>0.48</v>
+        <v>0.17</v>
       </c>
       <c r="AU3">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="AV3">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="AW3">
-        <v>0.59</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="AX3">
-        <v>0.232</v>
+        <v>0.252</v>
       </c>
       <c r="AY3">
-        <v>0.489</v>
+        <v>0.464</v>
       </c>
       <c r="AZ3">
-        <v>0.779</v>
+        <v>0.759</v>
       </c>
       <c r="BA3">
-        <v>0.501</v>
+        <v>1.049</v>
       </c>
       <c r="BB3">
-        <v>0.292</v>
+        <v>-0.024</v>
       </c>
       <c r="BC3">
-        <v>0.668</v>
+        <v>0.716</v>
       </c>
       <c r="BD3">
-        <v>0.909</v>
+        <v>0.944</v>
       </c>
       <c r="BE3">
-        <v>0.5659999999999999</v>
+        <v>0.571</v>
       </c>
       <c r="BF3">
         <v>-0.4581453659370775</v>
@@ -1226,10 +1226,10 @@
         <v>0.2290726829685387</v>
       </c>
       <c r="BH3">
-        <v>2.599789016888458</v>
+        <v>2.600363210771177</v>
       </c>
       <c r="BI3">
-        <v>0.3672447780822278</v>
+        <v>0.3728698774756225</v>
       </c>
     </row>
     <row r="4" spans="1:61">
@@ -1267,7 +1267,7 @@
         <v>0.05</v>
       </c>
       <c r="L4">
-        <v>0.2098350741775947</v>
+        <v>0.2127362654884989</v>
       </c>
       <c r="M4">
         <v>0.6</v>
@@ -1276,7 +1276,7 @@
         <v>0.05</v>
       </c>
       <c r="O4">
-        <v>0.07724376497577422</v>
+        <v>0.07229582081690147</v>
       </c>
       <c r="P4">
         <v>0.12</v>
@@ -1285,37 +1285,37 @@
         <v>12</v>
       </c>
       <c r="R4">
-        <v>62.00839099414698</v>
+        <v>60.53554115861854</v>
       </c>
       <c r="S4">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="T4">
-        <v>61.03</v>
+        <v>65.3</v>
       </c>
       <c r="U4">
-        <v>102.165810578136</v>
+        <v>109.6449377871041</v>
       </c>
       <c r="V4">
-        <v>153.31</v>
+        <v>163.91</v>
       </c>
       <c r="W4">
         <v>0.01</v>
       </c>
       <c r="X4">
-        <v>0.5027342358890469</v>
+        <v>0.5073215809597035</v>
       </c>
       <c r="Y4">
         <v>1</v>
       </c>
       <c r="Z4">
-        <v>0.14</v>
+        <v>0.11</v>
       </c>
       <c r="AA4">
-        <v>0.3601428592018471</v>
+        <v>0.3365673183703911</v>
       </c>
       <c r="AB4">
-        <v>0.61</v>
+        <v>0.59</v>
       </c>
       <c r="AC4">
         <v>1.7</v>
@@ -1327,13 +1327,13 @@
         <v>2.56</v>
       </c>
       <c r="AF4">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AG4">
         <v>1.88</v>
       </c>
       <c r="AH4">
-        <v>2.79</v>
+        <v>2.72</v>
       </c>
       <c r="AI4">
         <v>0.02</v>
@@ -1345,13 +1345,13 @@
         <v>0.06</v>
       </c>
       <c r="AL4">
-        <v>30.51</v>
+        <v>32.65</v>
       </c>
       <c r="AM4">
-        <v>42.95</v>
+        <v>46.08</v>
       </c>
       <c r="AN4">
-        <v>76.65000000000001</v>
+        <v>81.95</v>
       </c>
       <c r="AO4">
         <v>0.25</v>
@@ -1360,49 +1360,49 @@
         <v>0.36</v>
       </c>
       <c r="AQ4">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="AR4">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="AS4">
-        <v>0.8100000000000001</v>
+        <v>1.27</v>
       </c>
       <c r="AT4">
-        <v>0.28</v>
+        <v>0.22</v>
       </c>
       <c r="AU4">
-        <v>0.72</v>
+        <v>0.67</v>
       </c>
       <c r="AV4">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="AW4">
-        <v>0.168</v>
+        <v>0.165</v>
       </c>
       <c r="AX4">
-        <v>0.59</v>
+        <v>0.594</v>
       </c>
       <c r="AY4">
-        <v>0.297</v>
+        <v>0.268</v>
       </c>
       <c r="AZ4">
+        <v>0.536</v>
+      </c>
+      <c r="BA4">
+        <v>0.186</v>
+      </c>
+      <c r="BB4">
         <v>0.5679999999999999</v>
       </c>
-      <c r="BA4">
-        <v>0.153</v>
-      </c>
-      <c r="BB4">
-        <v>0.609</v>
-      </c>
       <c r="BC4">
-        <v>0.54</v>
+        <v>0.539</v>
       </c>
       <c r="BD4">
-        <v>0.799</v>
+        <v>0.791</v>
       </c>
       <c r="BE4">
-        <v>0.671</v>
+        <v>0.661</v>
       </c>
       <c r="BF4">
         <v>-1.753278948659991</v>
@@ -1411,10 +1411,10 @@
         <v>0.621226662447</v>
       </c>
       <c r="BH4">
-        <v>3.882972794015815</v>
+        <v>3.883050772629293</v>
       </c>
       <c r="BI4">
-        <v>0.683345449522631</v>
+        <v>0.6825057008512276</v>
       </c>
     </row>
     <row r="5" spans="1:61">
@@ -1452,7 +1452,7 @@
         <v>0.2</v>
       </c>
       <c r="L5">
-        <v>0.4250831659619266</v>
+        <v>0.4244383865550286</v>
       </c>
       <c r="M5">
         <v>0.8</v>
@@ -1461,34 +1461,34 @@
         <v>0.17</v>
       </c>
       <c r="O5">
-        <v>0.2499619654801503</v>
+        <v>0.2480525957909695</v>
       </c>
       <c r="P5">
         <v>0.37</v>
       </c>
       <c r="Q5">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="R5">
-        <v>23.85454476942752</v>
+        <v>23.66610477606836</v>
       </c>
       <c r="S5">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="T5">
-        <v>20.15</v>
+        <v>20.83</v>
       </c>
       <c r="U5">
-        <v>28.27212816408936</v>
+        <v>30.07609762329652</v>
       </c>
       <c r="V5">
-        <v>37.69</v>
+        <v>40.82</v>
       </c>
       <c r="W5">
         <v>0.01</v>
       </c>
       <c r="X5">
-        <v>0.503153023475206</v>
+        <v>0.5052146293719418</v>
       </c>
       <c r="Y5">
         <v>1</v>
@@ -1497,10 +1497,10 @@
         <v>0.06</v>
       </c>
       <c r="AA5">
-        <v>0.3800564538139665</v>
+        <v>0.4086445226317</v>
       </c>
       <c r="AB5">
-        <v>0.68</v>
+        <v>0.82</v>
       </c>
       <c r="AC5">
         <v>1.7</v>
@@ -1512,13 +1512,13 @@
         <v>2.56</v>
       </c>
       <c r="AF5">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="AG5">
-        <v>1.79</v>
+        <v>1.86</v>
       </c>
       <c r="AH5">
-        <v>2.08</v>
+        <v>2.19</v>
       </c>
       <c r="AI5">
         <v>0.09</v>
@@ -1530,13 +1530,13 @@
         <v>0.18</v>
       </c>
       <c r="AL5">
-        <v>10.07</v>
+        <v>10.41</v>
       </c>
       <c r="AM5">
-        <v>12.83</v>
+        <v>13.35</v>
       </c>
       <c r="AN5">
-        <v>18.85</v>
+        <v>20.41</v>
       </c>
       <c r="AO5">
         <v>0.25</v>
@@ -1545,49 +1545,49 @@
         <v>0.36</v>
       </c>
       <c r="AQ5">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="AR5">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="AS5">
-        <v>4.22</v>
+        <v>4.18</v>
       </c>
       <c r="AT5">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="AU5">
         <v>0.8</v>
       </c>
       <c r="AV5">
-        <v>1.36</v>
+        <v>1.63</v>
       </c>
       <c r="AW5">
-        <v>0.374</v>
+        <v>0.355</v>
       </c>
       <c r="AX5">
-        <v>0.389</v>
+        <v>0.404</v>
       </c>
       <c r="AY5">
-        <v>0.37</v>
+        <v>0.36</v>
       </c>
       <c r="AZ5">
-        <v>0.657</v>
+        <v>0.649</v>
       </c>
       <c r="BA5">
-        <v>0.439</v>
+        <v>0.494</v>
       </c>
       <c r="BB5">
-        <v>0.338</v>
+        <v>0.297</v>
       </c>
       <c r="BC5">
-        <v>0.718</v>
+        <v>0.764</v>
       </c>
       <c r="BD5">
-        <v>0.909</v>
+        <v>0.947</v>
       </c>
       <c r="BE5">
-        <v>0.624</v>
+        <v>0.608</v>
       </c>
       <c r="BF5">
         <v>-0.916290731874155</v>
@@ -1596,10 +1596,10 @@
         <v>0.3465735902799726</v>
       </c>
       <c r="BH5">
-        <v>3.07235867977124</v>
+        <v>3.055084133019253</v>
       </c>
       <c r="BI5">
-        <v>0.4485565353810899</v>
+        <v>0.4634707860088347</v>
       </c>
     </row>
     <row r="6" spans="1:61">
@@ -1637,7 +1637,7 @@
         <v>0.1</v>
       </c>
       <c r="L6">
-        <v>0.4857609569656579</v>
+        <v>0.4895327638858142</v>
       </c>
       <c r="M6">
         <v>1.5</v>
@@ -1646,46 +1646,46 @@
         <v>0.09</v>
       </c>
       <c r="O6">
-        <v>0.1430026683381858</v>
+        <v>0.1369266825728788</v>
       </c>
       <c r="P6">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="Q6">
         <v>5</v>
       </c>
       <c r="R6">
-        <v>29.18304808049134</v>
+        <v>28.65799867394828</v>
       </c>
       <c r="S6">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="T6">
-        <v>31.13</v>
+        <v>34.53</v>
       </c>
       <c r="U6">
-        <v>49.32145592021895</v>
+        <v>54.95505262217922</v>
       </c>
       <c r="V6">
-        <v>73.64</v>
+        <v>81.43000000000001</v>
       </c>
       <c r="W6">
         <v>0.01</v>
       </c>
       <c r="X6">
-        <v>0.2543752477548583</v>
+        <v>0.2566130114498313</v>
       </c>
       <c r="Y6">
         <v>0.5</v>
       </c>
       <c r="Z6">
-        <v>0.13</v>
+        <v>0.08</v>
       </c>
       <c r="AA6">
-        <v>0.3074434253152815</v>
+        <v>0.2966678745886578</v>
       </c>
       <c r="AB6">
-        <v>0.52</v>
+        <v>0.51</v>
       </c>
       <c r="AC6">
         <v>1.7</v>
@@ -1697,13 +1697,13 @@
         <v>2.56</v>
       </c>
       <c r="AF6">
-        <v>1.27</v>
+        <v>1.37</v>
       </c>
       <c r="AG6">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AH6">
-        <v>2.31</v>
+        <v>2.39</v>
       </c>
       <c r="AI6">
         <v>0.05</v>
@@ -1715,13 +1715,13 @@
         <v>0.11</v>
       </c>
       <c r="AL6">
-        <v>15.57</v>
+        <v>17.26</v>
       </c>
       <c r="AM6">
-        <v>21.59</v>
+        <v>23.63</v>
       </c>
       <c r="AN6">
-        <v>36.82</v>
+        <v>40.72</v>
       </c>
       <c r="AO6">
         <v>0.25</v>
@@ -1733,46 +1733,46 @@
         <v>0.1</v>
       </c>
       <c r="AR6">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="AS6">
-        <v>1.07</v>
+        <v>2.65</v>
       </c>
       <c r="AT6">
-        <v>0.25</v>
+        <v>0.15</v>
       </c>
       <c r="AU6">
         <v>0.6</v>
       </c>
       <c r="AV6">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AW6">
-        <v>0.137</v>
+        <v>0.124</v>
       </c>
       <c r="AX6">
-        <v>0.63</v>
+        <v>0.647</v>
       </c>
       <c r="AY6">
-        <v>0.235</v>
+        <v>0.206</v>
       </c>
       <c r="AZ6">
-        <v>0.491</v>
+        <v>0.457</v>
       </c>
       <c r="BA6">
-        <v>0.467</v>
+        <v>0.797</v>
       </c>
       <c r="BB6">
-        <v>0.317</v>
+        <v>0.107</v>
       </c>
       <c r="BC6">
-        <v>0.758</v>
+        <v>0.823</v>
       </c>
       <c r="BD6">
-        <v>0.9409999999999999</v>
+        <v>0.978</v>
       </c>
       <c r="BE6">
-        <v>0.217</v>
+        <v>0.233</v>
       </c>
       <c r="BF6">
         <v>-0.9485599924429405</v>
@@ -1781,10 +1781,10 @@
         <v>0.6770125502755524</v>
       </c>
       <c r="BH6">
-        <v>3.104855183708956</v>
+        <v>3.098748122655149</v>
       </c>
       <c r="BI6">
-        <v>0.7406042537464091</v>
+        <v>0.7462303557851317</v>
       </c>
     </row>
     <row r="7" spans="1:61">
@@ -1822,55 +1822,55 @@
         <v>0.4</v>
       </c>
       <c r="L7">
-        <v>0.6498534832876538</v>
+        <v>0.6486298357467234</v>
       </c>
       <c r="M7">
         <v>1</v>
       </c>
       <c r="N7">
-        <v>0.35</v>
+        <v>0.34</v>
       </c>
       <c r="O7">
-        <v>0.4562897085833419</v>
+        <v>0.4623482609156013</v>
       </c>
       <c r="P7">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="Q7">
         <v>6</v>
       </c>
       <c r="R7">
-        <v>14.49254876667416</v>
+        <v>14.47776709405768</v>
       </c>
       <c r="S7">
         <v>29</v>
       </c>
       <c r="T7">
-        <v>13.03</v>
+        <v>12.48</v>
       </c>
       <c r="U7">
-        <v>17.12091857194247</v>
+        <v>17.21905437244054</v>
       </c>
       <c r="V7">
-        <v>21.58</v>
+        <v>22.17</v>
       </c>
       <c r="W7">
         <v>0.01</v>
       </c>
       <c r="X7">
-        <v>0.2519702365776113</v>
+        <v>0.2522164829264932</v>
       </c>
       <c r="Y7">
         <v>0.5</v>
       </c>
       <c r="Z7">
-        <v>0.07000000000000001</v>
+        <v>0.05</v>
       </c>
       <c r="AA7">
-        <v>0.2903951331298376</v>
+        <v>0.2855445616463955</v>
       </c>
       <c r="AB7">
-        <v>0.55</v>
+        <v>0.63</v>
       </c>
       <c r="AC7">
         <v>1.7</v>
@@ -1882,10 +1882,10 @@
         <v>2.56</v>
       </c>
       <c r="AF7">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="AG7">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="AH7">
         <v>2.21</v>
@@ -1897,16 +1897,16 @@
         <v>0.25</v>
       </c>
       <c r="AK7">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="AL7">
-        <v>6.51</v>
+        <v>6.24</v>
       </c>
       <c r="AM7">
-        <v>7.84</v>
+        <v>7.83</v>
       </c>
       <c r="AN7">
-        <v>10.79</v>
+        <v>11.09</v>
       </c>
       <c r="AO7">
         <v>0.25</v>
@@ -1915,46 +1915,46 @@
         <v>0.36</v>
       </c>
       <c r="AQ7">
+        <v>0.08</v>
+      </c>
+      <c r="AR7">
+        <v>0.22</v>
+      </c>
+      <c r="AS7">
+        <v>5.26</v>
+      </c>
+      <c r="AT7">
         <v>0.1</v>
       </c>
-      <c r="AR7">
-        <v>0.2</v>
-      </c>
-      <c r="AS7">
-        <v>2.79</v>
-      </c>
-      <c r="AT7">
-        <v>0.14</v>
-      </c>
       <c r="AU7">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="AV7">
-        <v>1.1</v>
+        <v>1.26</v>
       </c>
       <c r="AW7">
-        <v>0.503</v>
+        <v>0.614</v>
       </c>
       <c r="AX7">
-        <v>0.291</v>
+        <v>0.216</v>
       </c>
       <c r="AY7">
-        <v>0.379</v>
+        <v>0.421</v>
       </c>
       <c r="AZ7">
-        <v>0.667</v>
+        <v>0.708</v>
       </c>
       <c r="BA7">
-        <v>0.992</v>
+        <v>1.265</v>
       </c>
       <c r="BB7">
-        <v>0.004</v>
+        <v>-0.125</v>
       </c>
       <c r="BC7">
-        <v>0.865</v>
+        <v>0.901</v>
       </c>
       <c r="BD7">
-        <v>0.984</v>
+        <v>0.987</v>
       </c>
       <c r="BE7">
         <v>0.226</v>
@@ -1966,10 +1966,10 @@
         <v>0.2290726829685387</v>
       </c>
       <c r="BH7">
-        <v>2.607554678595902</v>
+        <v>2.606119736556675</v>
       </c>
       <c r="BI7">
-        <v>0.3758130023290042</v>
+        <v>0.3740894856558739</v>
       </c>
     </row>
     <row r="8" spans="1:61">
@@ -2007,55 +2007,55 @@
         <v>0.05</v>
       </c>
       <c r="L8">
-        <v>0.2072726064686639</v>
+        <v>0.212283270078021</v>
       </c>
       <c r="M8">
         <v>0.6</v>
       </c>
       <c r="N8">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="O8">
-        <v>0.07470532981949277</v>
+        <v>0.07015867855081925</v>
       </c>
       <c r="P8">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="Q8">
         <v>12</v>
       </c>
       <c r="R8">
-        <v>62.08473737560019</v>
+        <v>60.51192085333134</v>
       </c>
       <c r="S8">
         <v>192</v>
       </c>
       <c r="T8">
-        <v>60.42</v>
+        <v>65.27</v>
       </c>
       <c r="U8">
-        <v>103.8178388359853</v>
+        <v>109.8108869965677</v>
       </c>
       <c r="V8">
-        <v>156.4</v>
+        <v>168.63</v>
       </c>
       <c r="W8">
         <v>0.01</v>
       </c>
       <c r="X8">
-        <v>0.2558019979207061</v>
+        <v>0.2541403161082374</v>
       </c>
       <c r="Y8">
         <v>0.5</v>
       </c>
       <c r="Z8">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AA8">
-        <v>0.2895246783817018</v>
+        <v>0.2985706411386448</v>
       </c>
       <c r="AB8">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="AC8">
         <v>1.7</v>
@@ -2067,13 +2067,13 @@
         <v>2.56</v>
       </c>
       <c r="AF8">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AG8">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="AH8">
-        <v>2.72</v>
+        <v>2.66</v>
       </c>
       <c r="AI8">
         <v>0.02</v>
@@ -2085,13 +2085,13 @@
         <v>0.06</v>
       </c>
       <c r="AL8">
-        <v>30.21</v>
+        <v>32.63</v>
       </c>
       <c r="AM8">
-        <v>42.72</v>
+        <v>45.38</v>
       </c>
       <c r="AN8">
-        <v>78.2</v>
+        <v>84.31999999999999</v>
       </c>
       <c r="AO8">
         <v>0.25</v>
@@ -2100,49 +2100,49 @@
         <v>0.36</v>
       </c>
       <c r="AQ8">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="AR8">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AS8">
-        <v>1.39</v>
+        <v>1.46</v>
       </c>
       <c r="AT8">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AU8">
-        <v>0.57</v>
+        <v>0.61</v>
       </c>
       <c r="AV8">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="AW8">
-        <v>0.172</v>
+        <v>0.165</v>
       </c>
       <c r="AX8">
-        <v>0.585</v>
+        <v>0.593</v>
       </c>
       <c r="AY8">
-        <v>0.285</v>
+        <v>0.246</v>
       </c>
       <c r="AZ8">
-        <v>0.5669999999999999</v>
+        <v>0.518</v>
       </c>
       <c r="BA8">
-        <v>0.494</v>
+        <v>0.483</v>
       </c>
       <c r="BB8">
-        <v>0.297</v>
+        <v>0.305</v>
       </c>
       <c r="BC8">
-        <v>0.8100000000000001</v>
+        <v>0.748</v>
       </c>
       <c r="BD8">
-        <v>0.963</v>
+        <v>0.949</v>
       </c>
       <c r="BE8">
-        <v>0.24</v>
+        <v>0.258</v>
       </c>
       <c r="BF8">
         <v>-1.753278948659991</v>
@@ -2151,10 +2151,10 @@
         <v>0.621226662447</v>
       </c>
       <c r="BH8">
-        <v>3.882131668820878</v>
+        <v>3.882104259325276</v>
       </c>
       <c r="BI8">
-        <v>0.687548271569009</v>
+        <v>0.6880890831832995</v>
       </c>
     </row>
     <row r="9" spans="1:61">
@@ -2192,55 +2192,55 @@
         <v>0.2</v>
       </c>
       <c r="L9">
-        <v>0.42402562967178</v>
+        <v>0.4236982874701743</v>
       </c>
       <c r="M9">
         <v>0.8</v>
       </c>
       <c r="N9">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="O9">
-        <v>0.2417624427961031</v>
+        <v>0.2359115589321722</v>
       </c>
       <c r="P9">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="Q9">
         <v>9</v>
       </c>
       <c r="R9">
-        <v>23.49238030076936</v>
+        <v>23.75669906766467</v>
       </c>
       <c r="S9">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="T9">
-        <v>20.44</v>
+        <v>21.42</v>
       </c>
       <c r="U9">
-        <v>28.61919898320236</v>
+        <v>30.82442396525587</v>
       </c>
       <c r="V9">
-        <v>37.98</v>
+        <v>41.4</v>
       </c>
       <c r="W9">
         <v>0.01</v>
       </c>
       <c r="X9">
-        <v>0.2544969701616051</v>
+        <v>0.25553552695869</v>
       </c>
       <c r="Y9">
         <v>0.5</v>
       </c>
       <c r="Z9">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="AA9">
-        <v>0.2695861310103066</v>
+        <v>0.2611892027109871</v>
       </c>
       <c r="AB9">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="AC9">
         <v>1.7</v>
@@ -2252,13 +2252,13 @@
         <v>2.56</v>
       </c>
       <c r="AF9">
-        <v>1.38</v>
+        <v>1.45</v>
       </c>
       <c r="AG9">
-        <v>1.74</v>
+        <v>1.81</v>
       </c>
       <c r="AH9">
-        <v>2.07</v>
+        <v>2.13</v>
       </c>
       <c r="AI9">
         <v>0.08</v>
@@ -2270,13 +2270,13 @@
         <v>0.18</v>
       </c>
       <c r="AL9">
-        <v>10.22</v>
+        <v>10.71</v>
       </c>
       <c r="AM9">
-        <v>13.05</v>
+        <v>13.79</v>
       </c>
       <c r="AN9">
-        <v>18.99</v>
+        <v>20.7</v>
       </c>
       <c r="AO9">
         <v>0.25</v>
@@ -2291,43 +2291,43 @@
         <v>0.29</v>
       </c>
       <c r="AS9">
-        <v>4.9</v>
+        <v>5.83</v>
       </c>
       <c r="AT9">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AU9">
-        <v>0.48</v>
+        <v>0.47</v>
       </c>
       <c r="AV9">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AW9">
-        <v>0.344</v>
+        <v>0.368</v>
       </c>
       <c r="AX9">
-        <v>0.413</v>
+        <v>0.393</v>
       </c>
       <c r="AY9">
-        <v>0.328</v>
+        <v>0.312</v>
       </c>
       <c r="AZ9">
-        <v>0.608</v>
+        <v>0.602</v>
       </c>
       <c r="BA9">
-        <v>1.248</v>
+        <v>1.201</v>
       </c>
       <c r="BB9">
-        <v>-0.117</v>
+        <v>-0.096</v>
       </c>
       <c r="BC9">
-        <v>0.907</v>
+        <v>0.901</v>
       </c>
       <c r="BD9">
-        <v>0.991</v>
+        <v>0.992</v>
       </c>
       <c r="BE9">
-        <v>0.196</v>
+        <v>0.21</v>
       </c>
       <c r="BF9">
         <v>-0.916290731874155</v>
@@ -2336,10 +2336,10 @@
         <v>0.3465735902799726</v>
       </c>
       <c r="BH9">
-        <v>3.053381088212915</v>
+        <v>3.063518120841473</v>
       </c>
       <c r="BI9">
-        <v>0.4509068262923319</v>
+        <v>0.4505744866633468</v>
       </c>
     </row>
     <row r="10" spans="1:61">
@@ -2377,55 +2377,55 @@
         <v>0.1</v>
       </c>
       <c r="L10">
-        <v>0.483020209755084</v>
+        <v>0.4864518932989964</v>
       </c>
       <c r="M10">
         <v>1.5</v>
       </c>
       <c r="N10">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="O10">
-        <v>0.1530361764478661</v>
+        <v>0.1363284421768528</v>
       </c>
       <c r="P10">
-        <v>0.24</v>
+        <v>0.21</v>
       </c>
       <c r="Q10">
         <v>5</v>
       </c>
       <c r="R10">
-        <v>29.43600557905924</v>
+        <v>29.24925281693997</v>
       </c>
       <c r="S10">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="T10">
-        <v>30.72</v>
+        <v>33.79</v>
       </c>
       <c r="U10">
-        <v>49.41142817663727</v>
+        <v>54.60868709423248</v>
       </c>
       <c r="V10">
-        <v>72.27</v>
+        <v>80.2</v>
       </c>
       <c r="W10">
         <v>0.01</v>
       </c>
       <c r="X10">
-        <v>0.2316361747204777</v>
+        <v>0.2326972717161555</v>
       </c>
       <c r="Y10">
         <v>0.45</v>
       </c>
       <c r="Z10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="AA10">
-        <v>0.2725834804724409</v>
+        <v>0.2611071265813333</v>
       </c>
       <c r="AB10">
-        <v>0.5</v>
+        <v>0.49</v>
       </c>
       <c r="AC10">
         <v>1.7</v>
@@ -2437,31 +2437,31 @@
         <v>2.56</v>
       </c>
       <c r="AF10">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AG10">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="AH10">
-        <v>2.43</v>
+        <v>2.35</v>
       </c>
       <c r="AI10">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="AJ10">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AK10">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AL10">
-        <v>15.36</v>
+        <v>16.9</v>
       </c>
       <c r="AM10">
-        <v>21.39</v>
+        <v>23.61</v>
       </c>
       <c r="AN10">
-        <v>36.14</v>
+        <v>40.1</v>
       </c>
       <c r="AO10">
         <v>0.25</v>
@@ -2470,49 +2470,49 @@
         <v>0.36</v>
       </c>
       <c r="AQ10">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="AR10">
-        <v>0.23</v>
+        <v>0.26</v>
       </c>
       <c r="AS10">
-        <v>2.3</v>
+        <v>2.07</v>
       </c>
       <c r="AT10">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="AU10">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="AV10">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AW10">
-        <v>0.116</v>
+        <v>0.121</v>
       </c>
       <c r="AX10">
-        <v>0.659</v>
+        <v>0.651</v>
       </c>
       <c r="AY10">
-        <v>0.246</v>
+        <v>0.207</v>
       </c>
       <c r="AZ10">
-        <v>0.502</v>
+        <v>0.454</v>
       </c>
       <c r="BA10">
-        <v>0.8139999999999999</v>
+        <v>0.716</v>
       </c>
       <c r="BB10">
-        <v>0.098</v>
+        <v>0.154</v>
       </c>
       <c r="BC10">
-        <v>0.831</v>
+        <v>0.884</v>
       </c>
       <c r="BD10">
-        <v>0.979</v>
+        <v>0.983</v>
       </c>
       <c r="BE10">
-        <v>0.216</v>
+        <v>0.223</v>
       </c>
       <c r="BF10">
         <v>-0.9485599924429405</v>
@@ -2521,10 +2521,10 @@
         <v>0.6770125502755524</v>
       </c>
       <c r="BH10">
-        <v>3.08989955917729</v>
+        <v>3.095807733111553</v>
       </c>
       <c r="BI10">
-        <v>0.745962398683009</v>
+        <v>0.7419167006490941</v>
       </c>
     </row>
     <row r="11" spans="1:61">
@@ -2562,7 +2562,7 @@
         <v>0.4</v>
       </c>
       <c r="L11">
-        <v>0.6466810126860438</v>
+        <v>0.6517206334362765</v>
       </c>
       <c r="M11">
         <v>1</v>
@@ -2571,46 +2571,46 @@
         <v>0.35</v>
       </c>
       <c r="O11">
-        <v>0.4667400288360941</v>
+        <v>0.465771768765134</v>
       </c>
       <c r="P11">
-        <v>0.63</v>
+        <v>0.65</v>
       </c>
       <c r="Q11">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="R11">
-        <v>14.65440394017846</v>
+        <v>14.52141666167883</v>
       </c>
       <c r="S11">
         <v>29</v>
       </c>
       <c r="T11">
-        <v>12.71</v>
+        <v>12.83</v>
       </c>
       <c r="U11">
-        <v>16.9090238702135</v>
+        <v>17.14505161525011</v>
       </c>
       <c r="V11">
-        <v>21.7</v>
+        <v>22.15</v>
       </c>
       <c r="W11">
         <v>0.01</v>
       </c>
       <c r="X11">
-        <v>0.2294562045312139</v>
+        <v>0.229676384418259</v>
       </c>
       <c r="Y11">
         <v>0.45</v>
       </c>
       <c r="Z11">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="AA11">
-        <v>0.2399830613155363</v>
+        <v>0.2152108485992011</v>
       </c>
       <c r="AB11">
-        <v>0.52</v>
+        <v>0.5</v>
       </c>
       <c r="AC11">
         <v>1.7</v>
@@ -2622,13 +2622,13 @@
         <v>2.56</v>
       </c>
       <c r="AF11">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="AG11">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="AH11">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="AI11">
         <v>0.17</v>
@@ -2640,13 +2640,13 @@
         <v>0.32</v>
       </c>
       <c r="AL11">
-        <v>6.35</v>
+        <v>6.41</v>
       </c>
       <c r="AM11">
-        <v>7.8</v>
+        <v>7.87</v>
       </c>
       <c r="AN11">
-        <v>10.85</v>
+        <v>11.07</v>
       </c>
       <c r="AO11">
         <v>0.25</v>
@@ -2655,49 +2655,49 @@
         <v>0.36</v>
       </c>
       <c r="AQ11">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="AR11">
-        <v>0.29</v>
+        <v>0.39</v>
       </c>
       <c r="AS11">
-        <v>4.41</v>
+        <v>7.3</v>
       </c>
       <c r="AT11">
-        <v>0.11</v>
+        <v>0.09</v>
       </c>
       <c r="AU11">
-        <v>0.44</v>
+        <v>0.37</v>
       </c>
       <c r="AV11">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="AW11">
-        <v>0.58</v>
+        <v>0.556</v>
       </c>
       <c r="AX11">
-        <v>0.239</v>
+        <v>0.254</v>
       </c>
       <c r="AY11">
-        <v>0.435</v>
+        <v>0.397</v>
       </c>
       <c r="AZ11">
-        <v>0.706</v>
+        <v>0.705</v>
       </c>
       <c r="BA11">
-        <v>1.198</v>
+        <v>1.195</v>
       </c>
       <c r="BB11">
-        <v>-0.095</v>
+        <v>-0.093</v>
       </c>
       <c r="BC11">
-        <v>0.878</v>
+        <v>0.886</v>
       </c>
       <c r="BD11">
-        <v>0.988</v>
+        <v>0.992</v>
       </c>
       <c r="BE11">
-        <v>0.215</v>
+        <v>0.229</v>
       </c>
       <c r="BF11">
         <v>-0.4581453659370775</v>
@@ -2706,10 +2706,10 @@
         <v>0.2290726829685387</v>
       </c>
       <c r="BH11">
-        <v>2.609816334574607</v>
+        <v>2.613807537532667</v>
       </c>
       <c r="BI11">
-        <v>0.3771034280566181</v>
+        <v>0.370394782327945</v>
       </c>
     </row>
     <row r="12" spans="1:61">
@@ -2747,52 +2747,52 @@
         <v>0.05</v>
       </c>
       <c r="L12">
-        <v>0.208598733380828</v>
+        <v>0.2109826596265518</v>
       </c>
       <c r="M12">
         <v>0.6</v>
       </c>
       <c r="N12">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="O12">
-        <v>0.07518490594986911</v>
+        <v>0.06932589461148007</v>
       </c>
       <c r="P12">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="Q12">
         <v>13</v>
       </c>
       <c r="R12">
-        <v>61.28498256499262</v>
+        <v>62.82688397632828</v>
       </c>
       <c r="S12">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="T12">
-        <v>57.86</v>
+        <v>66.26000000000001</v>
       </c>
       <c r="U12">
-        <v>98.87337096517133</v>
+        <v>113.3175101824582</v>
       </c>
       <c r="V12">
-        <v>149.89</v>
+        <v>169.16</v>
       </c>
       <c r="W12">
         <v>0.01</v>
       </c>
       <c r="X12">
-        <v>0.2294805306190982</v>
+        <v>0.2308807143702199</v>
       </c>
       <c r="Y12">
         <v>0.45</v>
       </c>
       <c r="Z12">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AA12">
-        <v>0.2949090288855903</v>
+        <v>0.2787940059164546</v>
       </c>
       <c r="AB12">
         <v>0.48</v>
@@ -2807,13 +2807,13 @@
         <v>2.56</v>
       </c>
       <c r="AF12">
-        <v>1.17</v>
+        <v>1.26</v>
       </c>
       <c r="AG12">
-        <v>1.77</v>
+        <v>1.87</v>
       </c>
       <c r="AH12">
-        <v>2.69</v>
+        <v>2.79</v>
       </c>
       <c r="AI12">
         <v>0.02</v>
@@ -2825,13 +2825,13 @@
         <v>0.06</v>
       </c>
       <c r="AL12">
-        <v>28.93</v>
+        <v>33.13</v>
       </c>
       <c r="AM12">
-        <v>41.09</v>
+        <v>46.27</v>
       </c>
       <c r="AN12">
-        <v>74.94</v>
+        <v>84.58</v>
       </c>
       <c r="AO12">
         <v>0.25</v>
@@ -2846,43 +2846,43 @@
         <v>0.22</v>
       </c>
       <c r="AS12">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AT12">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
       <c r="AU12">
-        <v>0.59</v>
+        <v>0.55</v>
       </c>
       <c r="AV12">
-        <v>0.97</v>
+        <v>0.95</v>
       </c>
       <c r="AW12">
-        <v>0.183</v>
+        <v>0.171</v>
       </c>
       <c r="AX12">
-        <v>0.572</v>
+        <v>0.587</v>
       </c>
       <c r="AY12">
-        <v>0.293</v>
+        <v>0.252</v>
       </c>
       <c r="AZ12">
-        <v>0.5669999999999999</v>
+        <v>0.522</v>
       </c>
       <c r="BA12">
-        <v>0.45</v>
+        <v>0.507</v>
       </c>
       <c r="BB12">
-        <v>0.329</v>
+        <v>0.288</v>
       </c>
       <c r="BC12">
-        <v>0.697</v>
+        <v>0.783</v>
       </c>
       <c r="BD12">
-        <v>0.921</v>
+        <v>0.949</v>
       </c>
       <c r="BE12">
-        <v>0.212</v>
+        <v>0.219</v>
       </c>
       <c r="BF12">
         <v>-1.753278948659991</v>
@@ -2891,10 +2891,10 @@
         <v>0.621226662447</v>
       </c>
       <c r="BH12">
-        <v>3.882971236644802</v>
+        <v>3.920593977603936</v>
       </c>
       <c r="BI12">
-        <v>0.6782757249540974</v>
+        <v>0.6809279546647162</v>
       </c>
     </row>
     <row r="13" spans="1:61">
@@ -2932,7 +2932,7 @@
         <v>0.2</v>
       </c>
       <c r="L13">
-        <v>0.4264053132601757</v>
+        <v>0.4230812423692322</v>
       </c>
       <c r="M13">
         <v>0.8</v>
@@ -2941,34 +2941,34 @@
         <v>0.17</v>
       </c>
       <c r="O13">
-        <v>0.242735293085972</v>
+        <v>0.2361957707524948</v>
       </c>
       <c r="P13">
-        <v>0.37</v>
+        <v>0.34</v>
       </c>
       <c r="Q13">
         <v>9</v>
       </c>
       <c r="R13">
-        <v>23.79473291427388</v>
+        <v>24.05920714754135</v>
       </c>
       <c r="S13">
         <v>54</v>
       </c>
       <c r="T13">
-        <v>20.07</v>
+        <v>21.8</v>
       </c>
       <c r="U13">
-        <v>28.78755744490751</v>
+        <v>30.66598474767515</v>
       </c>
       <c r="V13">
-        <v>38.48</v>
+        <v>40.52</v>
       </c>
       <c r="W13">
         <v>0.01</v>
       </c>
       <c r="X13">
-        <v>0.2300706623918626</v>
+        <v>0.2327522559235002</v>
       </c>
       <c r="Y13">
         <v>0.45</v>
@@ -2977,10 +2977,10 @@
         <v>0.05</v>
       </c>
       <c r="AA13">
-        <v>0.248919268439218</v>
+        <v>0.2376481788645683</v>
       </c>
       <c r="AB13">
-        <v>0.51</v>
+        <v>0.48</v>
       </c>
       <c r="AC13">
         <v>1.7</v>
@@ -2992,31 +2992,31 @@
         <v>2.56</v>
       </c>
       <c r="AF13">
-        <v>1.38</v>
+        <v>1.47</v>
       </c>
       <c r="AG13">
-        <v>1.77</v>
+        <v>1.81</v>
       </c>
       <c r="AH13">
-        <v>2.06</v>
+        <v>2.16</v>
       </c>
       <c r="AI13">
         <v>0.08</v>
       </c>
       <c r="AJ13">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="AK13">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AL13">
-        <v>10.04</v>
+        <v>10.9</v>
       </c>
       <c r="AM13">
-        <v>13.05</v>
+        <v>13.94</v>
       </c>
       <c r="AN13">
-        <v>19.24</v>
+        <v>20.26</v>
       </c>
       <c r="AO13">
         <v>0.25</v>
@@ -3025,49 +3025,49 @@
         <v>0.36</v>
       </c>
       <c r="AQ13">
+        <v>0.12</v>
+      </c>
+      <c r="AR13">
+        <v>0.31</v>
+      </c>
+      <c r="AS13">
+        <v>5.63</v>
+      </c>
+      <c r="AT13">
         <v>0.11</v>
       </c>
-      <c r="AR13">
-        <v>0.32</v>
-      </c>
-      <c r="AS13">
-        <v>5.98</v>
-      </c>
-      <c r="AT13">
-        <v>0.1</v>
-      </c>
       <c r="AU13">
-        <v>0.46</v>
+        <v>0.45</v>
       </c>
       <c r="AV13">
-        <v>1.02</v>
+        <v>0.96</v>
       </c>
       <c r="AW13">
-        <v>0.399</v>
+        <v>0.318</v>
       </c>
       <c r="AX13">
-        <v>0.368</v>
+        <v>0.436</v>
       </c>
       <c r="AY13">
-        <v>0.337</v>
+        <v>0.312</v>
       </c>
       <c r="AZ13">
-        <v>0.631</v>
+        <v>0.586</v>
       </c>
       <c r="BA13">
-        <v>1.248</v>
+        <v>0.995</v>
       </c>
       <c r="BB13">
-        <v>-0.117</v>
+        <v>0.003</v>
       </c>
       <c r="BC13">
-        <v>0.895</v>
+        <v>0.951</v>
       </c>
       <c r="BD13">
-        <v>0.99</v>
+        <v>0.997</v>
       </c>
       <c r="BE13">
-        <v>0.2</v>
+        <v>0.199</v>
       </c>
       <c r="BF13">
         <v>-0.916290731874155</v>
@@ -3076,10 +3076,10 @@
         <v>0.3465735902799726</v>
       </c>
       <c r="BH13">
-        <v>3.072112071529144</v>
+        <v>3.072900550368233</v>
       </c>
       <c r="BI13">
-        <v>0.4592705846385061</v>
+        <v>0.4604666068100136</v>
       </c>
     </row>
     <row r="14" spans="1:61">
@@ -3117,55 +3117,55 @@
         <v>0.1</v>
       </c>
       <c r="L14">
-        <v>0.4845458918197847</v>
+        <v>0.4864702928984845</v>
       </c>
       <c r="M14">
         <v>1.5</v>
       </c>
       <c r="N14">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="O14">
-        <v>0.1393376427894263</v>
+        <v>0.126824138109385</v>
       </c>
       <c r="P14">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="Q14">
         <v>5</v>
       </c>
       <c r="R14">
-        <v>28.69130574155313</v>
+        <v>28.52658015627107</v>
       </c>
       <c r="S14">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="T14">
-        <v>30.16</v>
+        <v>34.74</v>
       </c>
       <c r="U14">
-        <v>46.11143919237952</v>
+        <v>53.22749973267759</v>
       </c>
       <c r="V14">
-        <v>67.84</v>
+        <v>77.77</v>
       </c>
       <c r="W14">
         <v>0.03</v>
       </c>
       <c r="X14">
-        <v>0.1396351278660407</v>
+        <v>0.1399858510101243</v>
       </c>
       <c r="Y14">
         <v>0.25</v>
       </c>
       <c r="Z14">
-        <v>0.07000000000000001</v>
+        <v>0.05</v>
       </c>
       <c r="AA14">
-        <v>0.1557170294980393</v>
+        <v>0.1368375273232987</v>
       </c>
       <c r="AB14">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="AC14">
         <v>1.7</v>
@@ -3177,31 +3177,31 @@
         <v>2.56</v>
       </c>
       <c r="AF14">
-        <v>1.14</v>
+        <v>1.21</v>
       </c>
       <c r="AG14">
-        <v>1.62</v>
+        <v>1.68</v>
       </c>
       <c r="AH14">
-        <v>2.13</v>
+        <v>2.2</v>
       </c>
       <c r="AI14">
         <v>0.04</v>
       </c>
       <c r="AJ14">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AK14">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AL14">
-        <v>15.08</v>
+        <v>17.37</v>
       </c>
       <c r="AM14">
-        <v>20.53</v>
+        <v>23.89</v>
       </c>
       <c r="AN14">
-        <v>33.92</v>
+        <v>38.88</v>
       </c>
       <c r="AO14">
         <v>0.25</v>
@@ -3210,49 +3210,49 @@
         <v>0.36</v>
       </c>
       <c r="AQ14">
-        <v>0.23</v>
+        <v>0.26</v>
       </c>
       <c r="AR14">
-        <v>0.8</v>
+        <v>0.96</v>
       </c>
       <c r="AS14">
-        <v>3.8</v>
+        <v>6.16</v>
       </c>
       <c r="AT14">
-        <v>0.14</v>
+        <v>0.11</v>
       </c>
       <c r="AU14">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="AV14">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AW14">
-        <v>0.148</v>
+        <v>0.135</v>
       </c>
       <c r="AX14">
-        <v>0.616</v>
+        <v>0.632</v>
       </c>
       <c r="AY14">
-        <v>0.222</v>
+        <v>0.174</v>
       </c>
       <c r="AZ14">
-        <v>0.48</v>
+        <v>0.409</v>
       </c>
       <c r="BA14">
-        <v>0.669</v>
+        <v>0.776</v>
       </c>
       <c r="BB14">
-        <v>0.182</v>
+        <v>0.119</v>
       </c>
       <c r="BC14">
-        <v>0.863</v>
+        <v>0.924</v>
       </c>
       <c r="BD14">
-        <v>0.979</v>
+        <v>0.993</v>
       </c>
       <c r="BE14">
-        <v>0.008999999999999999</v>
+        <v>0.01</v>
       </c>
       <c r="BF14">
         <v>-0.9485599924429405</v>
@@ -3261,10 +3261,10 @@
         <v>0.6770125502755524</v>
       </c>
       <c r="BH14">
-        <v>3.083974400363417</v>
+        <v>3.084408953536393</v>
       </c>
       <c r="BI14">
-        <v>0.7358061353735287</v>
+        <v>0.7380946888154623</v>
       </c>
     </row>
     <row r="15" spans="1:61">
@@ -3302,55 +3302,55 @@
         <v>0.4</v>
       </c>
       <c r="L15">
-        <v>0.6478821127778311</v>
+        <v>0.6484093782193361</v>
       </c>
       <c r="M15">
         <v>1</v>
       </c>
       <c r="N15">
-        <v>0.36</v>
+        <v>0.35</v>
       </c>
       <c r="O15">
-        <v>0.4701073452371923</v>
+        <v>0.4651078483125608</v>
       </c>
       <c r="P15">
-        <v>0.66</v>
+        <v>0.62</v>
       </c>
       <c r="Q15">
         <v>6</v>
       </c>
       <c r="R15">
-        <v>14.38825197423413</v>
+        <v>14.33655999630412</v>
       </c>
       <c r="S15">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="T15">
-        <v>12.54</v>
+        <v>12.91</v>
       </c>
       <c r="U15">
-        <v>16.75397715170136</v>
+        <v>17.02370390314845</v>
       </c>
       <c r="V15">
-        <v>20.93</v>
+        <v>22.08</v>
       </c>
       <c r="W15">
         <v>0.03</v>
       </c>
       <c r="X15">
-        <v>0.1391199592325491</v>
+        <v>0.1391102301635943</v>
       </c>
       <c r="Y15">
         <v>0.25</v>
       </c>
       <c r="Z15">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="AA15">
-        <v>0.1271850029442387</v>
+        <v>0.1270302348915198</v>
       </c>
       <c r="AB15">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="AC15">
         <v>1.7</v>
@@ -3362,31 +3362,31 @@
         <v>2.56</v>
       </c>
       <c r="AF15">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AG15">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="AH15">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="AI15">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AJ15">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="AK15">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="AL15">
-        <v>6.27</v>
+        <v>6.45</v>
       </c>
       <c r="AM15">
-        <v>7.6</v>
+        <v>7.94</v>
       </c>
       <c r="AN15">
-        <v>10.46</v>
+        <v>11.04</v>
       </c>
       <c r="AO15">
         <v>0.25</v>
@@ -3401,43 +3401,43 @@
         <v>0.98</v>
       </c>
       <c r="AS15">
-        <v>9.59</v>
+        <v>7.05</v>
       </c>
       <c r="AT15">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="AU15">
         <v>0.24</v>
       </c>
       <c r="AV15">
-        <v>0.51</v>
+        <v>0.5</v>
       </c>
       <c r="AW15">
-        <v>0.547</v>
+        <v>0.503</v>
       </c>
       <c r="AX15">
-        <v>0.26</v>
+        <v>0.291</v>
       </c>
       <c r="AY15">
-        <v>0.425</v>
+        <v>0.4</v>
       </c>
       <c r="AZ15">
-        <v>0.728</v>
+        <v>0.6860000000000001</v>
       </c>
       <c r="BA15">
-        <v>1.218</v>
+        <v>1.048</v>
       </c>
       <c r="BB15">
-        <v>-0.104</v>
+        <v>-0.024</v>
       </c>
       <c r="BC15">
-        <v>0.906</v>
+        <v>0.904</v>
       </c>
       <c r="BD15">
-        <v>0.992</v>
+        <v>0.993</v>
       </c>
       <c r="BE15">
-        <v>0</v>
+        <v>0.002</v>
       </c>
       <c r="BF15">
         <v>-0.4581453659370775</v>
@@ -3446,10 +3446,10 @@
         <v>0.2290726829685387</v>
       </c>
       <c r="BH15">
-        <v>2.599812018266248</v>
+        <v>2.596144591125226</v>
       </c>
       <c r="BI15">
-        <v>0.3765642992558799</v>
+        <v>0.3763660846384678</v>
       </c>
     </row>
     <row r="16" spans="1:61">
@@ -3487,55 +3487,55 @@
         <v>0.05</v>
       </c>
       <c r="L16">
-        <v>0.2060191597333187</v>
+        <v>0.2108794154840056</v>
       </c>
       <c r="M16">
         <v>0.6</v>
       </c>
       <c r="N16">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="O16">
-        <v>0.07572639329945918</v>
+        <v>0.06982456950926232</v>
       </c>
       <c r="P16">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="Q16">
         <v>12</v>
       </c>
       <c r="R16">
-        <v>63.09637118766067</v>
+        <v>61.45521805003185</v>
       </c>
       <c r="S16">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="T16">
-        <v>58.88</v>
+        <v>65.48999999999999</v>
       </c>
       <c r="U16">
-        <v>106.7689002203136</v>
+        <v>112.1005667755153</v>
       </c>
       <c r="V16">
-        <v>160.95</v>
+        <v>168.72</v>
       </c>
       <c r="W16">
         <v>0.03</v>
       </c>
       <c r="X16">
-        <v>0.1397793395221022</v>
+        <v>0.13970337181353</v>
       </c>
       <c r="Y16">
         <v>0.25</v>
       </c>
       <c r="Z16">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AA16">
-        <v>0.1761952326279719</v>
+        <v>0.1697774851773167</v>
       </c>
       <c r="AB16">
-        <v>0.31</v>
+        <v>0.3</v>
       </c>
       <c r="AC16">
         <v>1.7</v>
@@ -3547,31 +3547,31 @@
         <v>2.56</v>
       </c>
       <c r="AF16">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="AG16">
         <v>1.85</v>
       </c>
       <c r="AH16">
-        <v>2.76</v>
+        <v>2.77</v>
       </c>
       <c r="AI16">
         <v>0.02</v>
       </c>
       <c r="AJ16">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="AK16">
         <v>0.06</v>
       </c>
       <c r="AL16">
-        <v>29.44</v>
+        <v>32.74</v>
       </c>
       <c r="AM16">
-        <v>40.98</v>
+        <v>45.85</v>
       </c>
       <c r="AN16">
-        <v>80.48</v>
+        <v>84.36</v>
       </c>
       <c r="AO16">
         <v>0.25</v>
@@ -3580,49 +3580,49 @@
         <v>0.36</v>
       </c>
       <c r="AQ16">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="AR16">
-        <v>0.51</v>
+        <v>0.55</v>
       </c>
       <c r="AS16">
-        <v>2.53</v>
+        <v>3.15</v>
       </c>
       <c r="AT16">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="AU16">
-        <v>0.34</v>
+        <v>0.33</v>
       </c>
       <c r="AV16">
-        <v>0.62</v>
+        <v>0.61</v>
       </c>
       <c r="AW16">
-        <v>0.171</v>
+        <v>0.168</v>
       </c>
       <c r="AX16">
-        <v>0.586</v>
+        <v>0.59</v>
       </c>
       <c r="AY16">
-        <v>0.285</v>
+        <v>0.254</v>
       </c>
       <c r="AZ16">
-        <v>0.574</v>
+        <v>0.524</v>
       </c>
       <c r="BA16">
-        <v>0.755</v>
+        <v>0.793</v>
       </c>
       <c r="BB16">
-        <v>0.131</v>
+        <v>0.11</v>
       </c>
       <c r="BC16">
-        <v>0.753</v>
+        <v>0.793</v>
       </c>
       <c r="BD16">
-        <v>0.947</v>
+        <v>0.963</v>
       </c>
       <c r="BE16">
-        <v>0.027</v>
+        <v>0.033</v>
       </c>
       <c r="BF16">
         <v>-1.753278948659991</v>
@@ -3631,10 +3631,10 @@
         <v>0.621226662447</v>
       </c>
       <c r="BH16">
-        <v>3.896842732964714</v>
+        <v>3.894476298196476</v>
       </c>
       <c r="BI16">
-        <v>0.6969362148450884</v>
+        <v>0.6947981732991657</v>
       </c>
     </row>
     <row r="17" spans="1:61">
@@ -3672,16 +3672,16 @@
         <v>0.2</v>
       </c>
       <c r="L17">
-        <v>0.427093069625704</v>
+        <v>0.4224313219804622</v>
       </c>
       <c r="M17">
         <v>0.8</v>
       </c>
       <c r="N17">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="O17">
-        <v>0.244032546779402</v>
+        <v>0.2386175184861667</v>
       </c>
       <c r="P17">
         <v>0.36</v>
@@ -3690,37 +3690,37 @@
         <v>9</v>
       </c>
       <c r="R17">
-        <v>23.44803207612901</v>
+        <v>23.49796978989266</v>
       </c>
       <c r="S17">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="T17">
-        <v>20.32</v>
+        <v>20.98</v>
       </c>
       <c r="U17">
-        <v>28.53116524978489</v>
+        <v>29.87142693580196</v>
       </c>
       <c r="V17">
-        <v>37.44</v>
+        <v>40.01</v>
       </c>
       <c r="W17">
         <v>0.03</v>
       </c>
       <c r="X17">
-        <v>0.139423399118724</v>
+        <v>0.1393518746655876</v>
       </c>
       <c r="Y17">
         <v>0.25</v>
       </c>
       <c r="Z17">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="AA17">
-        <v>0.1463654764023989</v>
+        <v>0.1388556830292542</v>
       </c>
       <c r="AB17">
-        <v>0.29</v>
+        <v>0.26</v>
       </c>
       <c r="AC17">
         <v>1.7</v>
@@ -3732,31 +3732,31 @@
         <v>2.56</v>
       </c>
       <c r="AF17">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="AG17">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="AH17">
-        <v>2.07</v>
+        <v>2.09</v>
       </c>
       <c r="AI17">
         <v>0.08</v>
       </c>
       <c r="AJ17">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="AK17">
         <v>0.18</v>
       </c>
       <c r="AL17">
-        <v>10.16</v>
+        <v>10.49</v>
       </c>
       <c r="AM17">
-        <v>12.95</v>
+        <v>13.49</v>
       </c>
       <c r="AN17">
-        <v>18.72</v>
+        <v>20.01</v>
       </c>
       <c r="AO17">
         <v>0.25</v>
@@ -3765,49 +3765,49 @@
         <v>0.36</v>
       </c>
       <c r="AQ17">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="AR17">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="AS17">
-        <v>8.859999999999999</v>
+        <v>6.28</v>
       </c>
       <c r="AT17">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="AU17">
-        <v>0.28</v>
+        <v>0.27</v>
       </c>
       <c r="AV17">
-        <v>0.59</v>
+        <v>0.53</v>
       </c>
       <c r="AW17">
-        <v>0.37</v>
+        <v>0.411</v>
       </c>
       <c r="AX17">
-        <v>0.392</v>
+        <v>0.359</v>
       </c>
       <c r="AY17">
-        <v>0.339</v>
+        <v>0.336</v>
       </c>
       <c r="AZ17">
-        <v>0.635</v>
+        <v>0.617</v>
       </c>
       <c r="BA17">
-        <v>1.186</v>
+        <v>0.96</v>
       </c>
       <c r="BB17">
-        <v>-0.089</v>
+        <v>0.02</v>
       </c>
       <c r="BC17">
-        <v>0.947</v>
+        <v>0.968</v>
       </c>
       <c r="BD17">
-        <v>0.995</v>
+        <v>0.998</v>
       </c>
       <c r="BE17">
-        <v>0.006</v>
+        <v>0.004</v>
       </c>
       <c r="BF17">
         <v>-0.916290731874155</v>
@@ -3816,10 +3816,10 @@
         <v>0.3465735902799726</v>
       </c>
       <c r="BH17">
-        <v>3.056453106642124</v>
+        <v>3.049438453683126</v>
       </c>
       <c r="BI17">
-        <v>0.4580880929667634</v>
+        <v>0.4496065896265531</v>
       </c>
     </row>
   </sheetData>

--- a/Catch models/cmsy_out_macarellus_cmsy.xlsx
+++ b/Catch models/cmsy_out_macarellus_cmsy.xlsx
@@ -897,55 +897,55 @@
         <v>0.1</v>
       </c>
       <c r="L2">
-        <v>0.493514255446269</v>
+        <v>0.4877863116728848</v>
       </c>
       <c r="M2">
         <v>1.5</v>
       </c>
       <c r="N2">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="O2">
-        <v>0.1471124873021576</v>
+        <v>0.1396959433640875</v>
       </c>
       <c r="P2">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="Q2">
         <v>5</v>
       </c>
       <c r="R2">
-        <v>29.0211839818056</v>
+        <v>29.194216526403</v>
       </c>
       <c r="S2">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="T2">
-        <v>31.5</v>
+        <v>32.72</v>
       </c>
       <c r="U2">
-        <v>52.89859688969557</v>
+        <v>53.51539768538233</v>
       </c>
       <c r="V2">
-        <v>78.23</v>
+        <v>79.34999999999999</v>
       </c>
       <c r="W2">
         <v>0.01</v>
       </c>
       <c r="X2">
-        <v>0.5050626527942176</v>
+        <v>0.5017118231402615</v>
       </c>
       <c r="Y2">
         <v>1</v>
       </c>
       <c r="Z2">
-        <v>0.08</v>
+        <v>0.1</v>
       </c>
       <c r="AA2">
-        <v>0.3584134523538798</v>
+        <v>0.3343732570324568</v>
       </c>
       <c r="AB2">
-        <v>0.63</v>
+        <v>0.59</v>
       </c>
       <c r="AC2">
         <v>1.7</v>
@@ -957,31 +957,31 @@
         <v>2.56</v>
       </c>
       <c r="AF2">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AG2">
-        <v>1.88</v>
+        <v>1.82</v>
       </c>
       <c r="AH2">
-        <v>2.43</v>
+        <v>2.36</v>
       </c>
       <c r="AI2">
         <v>0.05</v>
       </c>
       <c r="AJ2">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AK2">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AL2">
-        <v>15.75</v>
+        <v>16.36</v>
       </c>
       <c r="AM2">
-        <v>21.67</v>
+        <v>22.76</v>
       </c>
       <c r="AN2">
-        <v>39.12</v>
+        <v>39.68</v>
       </c>
       <c r="AO2">
         <v>0.25</v>
@@ -993,46 +993,46 @@
         <v>0.08</v>
       </c>
       <c r="AR2">
-        <v>0.16</v>
+        <v>0.19</v>
       </c>
       <c r="AS2">
-        <v>2.73</v>
+        <v>1.51</v>
       </c>
       <c r="AT2">
-        <v>0.16</v>
+        <v>0.21</v>
       </c>
       <c r="AU2">
-        <v>0.74</v>
+        <v>0.67</v>
       </c>
       <c r="AV2">
-        <v>1.26</v>
+        <v>1.18</v>
       </c>
       <c r="AW2">
-        <v>0.127</v>
+        <v>0.133</v>
       </c>
       <c r="AX2">
-        <v>0.643</v>
+        <v>0.636</v>
       </c>
       <c r="AY2">
-        <v>0.233</v>
+        <v>0.224</v>
       </c>
       <c r="AZ2">
-        <v>0.506</v>
+        <v>0.475</v>
       </c>
       <c r="BA2">
-        <v>0.302</v>
+        <v>0.205</v>
       </c>
       <c r="BB2">
-        <v>0.45</v>
+        <v>0.547</v>
       </c>
       <c r="BC2">
-        <v>0.635</v>
+        <v>0.5570000000000001</v>
       </c>
       <c r="BD2">
-        <v>0.856</v>
+        <v>0.801</v>
       </c>
       <c r="BE2">
-        <v>0.584</v>
+        <v>0.603</v>
       </c>
       <c r="BF2">
         <v>-0.9485599924429405</v>
@@ -1041,10 +1041,10 @@
         <v>0.6770125502755524</v>
       </c>
       <c r="BH2">
-        <v>3.084117564756091</v>
+        <v>3.085134941712052</v>
       </c>
       <c r="BI2">
-        <v>0.7489833948764801</v>
+        <v>0.745223135033105</v>
       </c>
     </row>
     <row r="3" spans="1:61">
@@ -1082,7 +1082,7 @@
         <v>0.4</v>
       </c>
       <c r="L3">
-        <v>0.6496030465850088</v>
+        <v>0.6473254460565999</v>
       </c>
       <c r="M3">
         <v>1</v>
@@ -1091,46 +1091,46 @@
         <v>0.36</v>
       </c>
       <c r="O3">
-        <v>0.4802359139323749</v>
+        <v>0.4762406568668859</v>
       </c>
       <c r="P3">
-        <v>0.67</v>
+        <v>0.64</v>
       </c>
       <c r="Q3">
         <v>6</v>
       </c>
       <c r="R3">
-        <v>14.38974788318465</v>
+        <v>14.428375991092</v>
       </c>
       <c r="S3">
         <v>28</v>
       </c>
       <c r="T3">
-        <v>12.26</v>
+        <v>12.55</v>
       </c>
       <c r="U3">
-        <v>16.75811028317288</v>
+        <v>16.89227038783771</v>
       </c>
       <c r="V3">
-        <v>21.3</v>
+        <v>21.32</v>
       </c>
       <c r="W3">
         <v>0.01</v>
       </c>
       <c r="X3">
-        <v>0.5035943054155001</v>
+        <v>0.5049573524701095</v>
       </c>
       <c r="Y3">
         <v>1</v>
       </c>
       <c r="Z3">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="AA3">
-        <v>0.6323857974916437</v>
+        <v>0.4733041648451154</v>
       </c>
       <c r="AB3">
-        <v>0.95</v>
+        <v>0.84</v>
       </c>
       <c r="AC3">
         <v>1.7</v>
@@ -1142,10 +1142,10 @@
         <v>2.56</v>
       </c>
       <c r="AF3">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="AG3">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="AH3">
         <v>2.23</v>
@@ -1154,19 +1154,19 @@
         <v>0.18</v>
       </c>
       <c r="AJ3">
-        <v>0.27</v>
+        <v>0.26</v>
       </c>
       <c r="AK3">
-        <v>0.34</v>
+        <v>0.32</v>
       </c>
       <c r="AL3">
-        <v>6.13</v>
+        <v>6.28</v>
       </c>
       <c r="AM3">
-        <v>7.51</v>
+        <v>7.64</v>
       </c>
       <c r="AN3">
-        <v>10.65</v>
+        <v>10.66</v>
       </c>
       <c r="AO3">
         <v>0.25</v>
@@ -1175,46 +1175,46 @@
         <v>0.36</v>
       </c>
       <c r="AQ3">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="AR3">
-        <v>0.08</v>
+        <v>0.11</v>
       </c>
       <c r="AS3">
-        <v>2.05</v>
+        <v>4.25</v>
       </c>
       <c r="AT3">
-        <v>0.17</v>
+        <v>0.11</v>
       </c>
       <c r="AU3">
-        <v>1.42</v>
+        <v>1</v>
       </c>
       <c r="AV3">
-        <v>1.91</v>
+        <v>1.69</v>
       </c>
       <c r="AW3">
-        <v>0.5590000000000001</v>
+        <v>0.518</v>
       </c>
       <c r="AX3">
-        <v>0.252</v>
+        <v>0.28</v>
       </c>
       <c r="AY3">
-        <v>0.464</v>
+        <v>0.448</v>
       </c>
       <c r="AZ3">
-        <v>0.759</v>
+        <v>0.739</v>
       </c>
       <c r="BA3">
-        <v>1.049</v>
+        <v>0.763</v>
       </c>
       <c r="BB3">
-        <v>-0.024</v>
+        <v>0.127</v>
       </c>
       <c r="BC3">
-        <v>0.716</v>
+        <v>0.887</v>
       </c>
       <c r="BD3">
-        <v>0.944</v>
+        <v>0.977</v>
       </c>
       <c r="BE3">
         <v>0.571</v>
@@ -1226,10 +1226,10 @@
         <v>0.2290726829685387</v>
       </c>
       <c r="BH3">
-        <v>2.600363210771177</v>
+        <v>2.596591443973727</v>
       </c>
       <c r="BI3">
-        <v>0.3728698774756225</v>
+        <v>0.3754179678283673</v>
       </c>
     </row>
     <row r="4" spans="1:61">
@@ -1267,7 +1267,7 @@
         <v>0.05</v>
       </c>
       <c r="L4">
-        <v>0.2127362654884989</v>
+        <v>0.2094610188914432</v>
       </c>
       <c r="M4">
         <v>0.6</v>
@@ -1276,34 +1276,34 @@
         <v>0.05</v>
       </c>
       <c r="O4">
-        <v>0.07229582081690147</v>
+        <v>0.0731860044753528</v>
       </c>
       <c r="P4">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="Q4">
         <v>12</v>
       </c>
       <c r="R4">
-        <v>60.53554115861854</v>
+        <v>64.54876852108109</v>
       </c>
       <c r="S4">
-        <v>190</v>
+        <v>201</v>
       </c>
       <c r="T4">
-        <v>65.3</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="U4">
-        <v>109.6449377871041</v>
+        <v>118.1957584672903</v>
       </c>
       <c r="V4">
-        <v>163.91</v>
+        <v>175.41</v>
       </c>
       <c r="W4">
         <v>0.01</v>
       </c>
       <c r="X4">
-        <v>0.5073215809597035</v>
+        <v>0.5070138892221304</v>
       </c>
       <c r="Y4">
         <v>1</v>
@@ -1312,7 +1312,7 @@
         <v>0.11</v>
       </c>
       <c r="AA4">
-        <v>0.3365673183703911</v>
+        <v>0.324270389695461</v>
       </c>
       <c r="AB4">
         <v>0.59</v>
@@ -1327,13 +1327,13 @@
         <v>2.56</v>
       </c>
       <c r="AF4">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="AG4">
-        <v>1.88</v>
+        <v>2.04</v>
       </c>
       <c r="AH4">
-        <v>2.72</v>
+        <v>2.85</v>
       </c>
       <c r="AI4">
         <v>0.02</v>
@@ -1345,13 +1345,13 @@
         <v>0.06</v>
       </c>
       <c r="AL4">
-        <v>32.65</v>
+        <v>35.55</v>
       </c>
       <c r="AM4">
-        <v>46.08</v>
+        <v>49.13</v>
       </c>
       <c r="AN4">
-        <v>81.95</v>
+        <v>87.7</v>
       </c>
       <c r="AO4">
         <v>0.25</v>
@@ -1360,49 +1360,49 @@
         <v>0.36</v>
       </c>
       <c r="AQ4">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AR4">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AS4">
-        <v>1.27</v>
+        <v>1.04</v>
       </c>
       <c r="AT4">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="AU4">
-        <v>0.67</v>
+        <v>0.64</v>
       </c>
       <c r="AV4">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AW4">
-        <v>0.165</v>
+        <v>0.14</v>
       </c>
       <c r="AX4">
-        <v>0.594</v>
+        <v>0.626</v>
       </c>
       <c r="AY4">
-        <v>0.268</v>
+        <v>0.262</v>
       </c>
       <c r="AZ4">
-        <v>0.536</v>
+        <v>0.527</v>
       </c>
       <c r="BA4">
-        <v>0.186</v>
+        <v>0.178</v>
       </c>
       <c r="BB4">
-        <v>0.5679999999999999</v>
+        <v>0.578</v>
       </c>
       <c r="BC4">
-        <v>0.539</v>
+        <v>0.501</v>
       </c>
       <c r="BD4">
-        <v>0.791</v>
+        <v>0.793</v>
       </c>
       <c r="BE4">
-        <v>0.661</v>
+        <v>0.663</v>
       </c>
       <c r="BF4">
         <v>-1.753278948659991</v>
@@ -1411,10 +1411,10 @@
         <v>0.621226662447</v>
       </c>
       <c r="BH4">
-        <v>3.883050772629293</v>
+        <v>3.899220346130775</v>
       </c>
       <c r="BI4">
-        <v>0.6825057008512276</v>
+        <v>0.7025053105833852</v>
       </c>
     </row>
     <row r="5" spans="1:61">
@@ -1452,7 +1452,7 @@
         <v>0.2</v>
       </c>
       <c r="L5">
-        <v>0.4244383865550286</v>
+        <v>0.4238452357040193</v>
       </c>
       <c r="M5">
         <v>0.8</v>
@@ -1461,46 +1461,46 @@
         <v>0.17</v>
       </c>
       <c r="O5">
-        <v>0.2480525957909695</v>
+        <v>0.2451301424226419</v>
       </c>
       <c r="P5">
-        <v>0.37</v>
+        <v>0.35</v>
       </c>
       <c r="Q5">
         <v>8</v>
       </c>
       <c r="R5">
-        <v>23.66610477606836</v>
+        <v>23.646675075135</v>
       </c>
       <c r="S5">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="T5">
-        <v>20.83</v>
+        <v>21.86</v>
       </c>
       <c r="U5">
-        <v>30.07609762329652</v>
+        <v>30.37369206648107</v>
       </c>
       <c r="V5">
-        <v>40.82</v>
+        <v>41.49</v>
       </c>
       <c r="W5">
         <v>0.01</v>
       </c>
       <c r="X5">
-        <v>0.5052146293719418</v>
+        <v>0.5063993830836986</v>
       </c>
       <c r="Y5">
         <v>1</v>
       </c>
       <c r="Z5">
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
       <c r="AA5">
-        <v>0.4086445226317</v>
+        <v>0.3792538877755247</v>
       </c>
       <c r="AB5">
-        <v>0.82</v>
+        <v>0.67</v>
       </c>
       <c r="AC5">
         <v>1.7</v>
@@ -1515,28 +1515,28 @@
         <v>1.5</v>
       </c>
       <c r="AG5">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="AH5">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="AI5">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AJ5">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="AK5">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AL5">
-        <v>10.41</v>
+        <v>10.93</v>
       </c>
       <c r="AM5">
-        <v>13.35</v>
+        <v>14.04</v>
       </c>
       <c r="AN5">
-        <v>20.41</v>
+        <v>20.74</v>
       </c>
       <c r="AO5">
         <v>0.25</v>
@@ -1545,49 +1545,49 @@
         <v>0.36</v>
       </c>
       <c r="AQ5">
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
       <c r="AR5">
+        <v>0.16</v>
+      </c>
+      <c r="AS5">
+        <v>2.63</v>
+      </c>
+      <c r="AT5">
         <v>0.15</v>
       </c>
-      <c r="AS5">
-        <v>4.18</v>
-      </c>
-      <c r="AT5">
-        <v>0.12</v>
-      </c>
       <c r="AU5">
-        <v>0.8</v>
+        <v>0.78</v>
       </c>
       <c r="AV5">
-        <v>1.63</v>
+        <v>1.34</v>
       </c>
       <c r="AW5">
-        <v>0.355</v>
+        <v>0.347</v>
       </c>
       <c r="AX5">
-        <v>0.404</v>
+        <v>0.411</v>
       </c>
       <c r="AY5">
-        <v>0.36</v>
+        <v>0.338</v>
       </c>
       <c r="AZ5">
-        <v>0.649</v>
+        <v>0.612</v>
       </c>
       <c r="BA5">
-        <v>0.494</v>
+        <v>0.353</v>
       </c>
       <c r="BB5">
-        <v>0.297</v>
+        <v>0.405</v>
       </c>
       <c r="BC5">
-        <v>0.764</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BD5">
-        <v>0.947</v>
+        <v>0.883</v>
       </c>
       <c r="BE5">
-        <v>0.608</v>
+        <v>0.621</v>
       </c>
       <c r="BF5">
         <v>-0.916290731874155</v>
@@ -1596,10 +1596,10 @@
         <v>0.3465735902799726</v>
       </c>
       <c r="BH5">
-        <v>3.055084133019253</v>
+        <v>3.047862049680882</v>
       </c>
       <c r="BI5">
-        <v>0.4634707860088347</v>
+        <v>0.4652660505122928</v>
       </c>
     </row>
     <row r="6" spans="1:61">
@@ -1637,7 +1637,7 @@
         <v>0.1</v>
       </c>
       <c r="L6">
-        <v>0.4895327638858142</v>
+        <v>0.476000333634423</v>
       </c>
       <c r="M6">
         <v>1.5</v>
@@ -1646,46 +1646,46 @@
         <v>0.09</v>
       </c>
       <c r="O6">
-        <v>0.1369266825728788</v>
+        <v>0.1371444486332072</v>
       </c>
       <c r="P6">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="Q6">
         <v>5</v>
       </c>
       <c r="R6">
-        <v>28.65799867394828</v>
+        <v>28.90658332942769</v>
       </c>
       <c r="S6">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="T6">
-        <v>34.53</v>
+        <v>33.6</v>
       </c>
       <c r="U6">
-        <v>54.95505262217922</v>
+        <v>54.56627227080511</v>
       </c>
       <c r="V6">
-        <v>81.43000000000001</v>
+        <v>80</v>
       </c>
       <c r="W6">
         <v>0.01</v>
       </c>
       <c r="X6">
-        <v>0.2566130114498313</v>
+        <v>0.2571434600779495</v>
       </c>
       <c r="Y6">
         <v>0.5</v>
       </c>
       <c r="Z6">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="AA6">
-        <v>0.2966678745886578</v>
+        <v>0.2767788108701297</v>
       </c>
       <c r="AB6">
-        <v>0.51</v>
+        <v>0.48</v>
       </c>
       <c r="AC6">
         <v>1.7</v>
@@ -1697,16 +1697,16 @@
         <v>2.56</v>
       </c>
       <c r="AF6">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="AG6">
         <v>1.83</v>
       </c>
       <c r="AH6">
-        <v>2.39</v>
+        <v>2.38</v>
       </c>
       <c r="AI6">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="AJ6">
         <v>0.08</v>
@@ -1715,13 +1715,13 @@
         <v>0.11</v>
       </c>
       <c r="AL6">
-        <v>17.26</v>
+        <v>16.8</v>
       </c>
       <c r="AM6">
-        <v>23.63</v>
+        <v>23.1</v>
       </c>
       <c r="AN6">
-        <v>40.72</v>
+        <v>40</v>
       </c>
       <c r="AO6">
         <v>0.25</v>
@@ -1730,49 +1730,49 @@
         <v>0.36</v>
       </c>
       <c r="AQ6">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="AR6">
+        <v>0.23</v>
+      </c>
+      <c r="AS6">
+        <v>1.76</v>
+      </c>
+      <c r="AT6">
+        <v>0.19</v>
+      </c>
+      <c r="AU6">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="AV6">
+        <v>0.95</v>
+      </c>
+      <c r="AW6">
+        <v>0.139</v>
+      </c>
+      <c r="AX6">
+        <v>0.627</v>
+      </c>
+      <c r="AY6">
         <v>0.21</v>
       </c>
-      <c r="AS6">
-        <v>2.65</v>
-      </c>
-      <c r="AT6">
-        <v>0.15</v>
-      </c>
-      <c r="AU6">
-        <v>0.6</v>
-      </c>
-      <c r="AV6">
-        <v>1.02</v>
-      </c>
-      <c r="AW6">
-        <v>0.124</v>
-      </c>
-      <c r="AX6">
-        <v>0.647</v>
-      </c>
-      <c r="AY6">
-        <v>0.206</v>
-      </c>
       <c r="AZ6">
-        <v>0.457</v>
+        <v>0.476</v>
       </c>
       <c r="BA6">
-        <v>0.797</v>
+        <v>0.546</v>
       </c>
       <c r="BB6">
-        <v>0.107</v>
+        <v>0.261</v>
       </c>
       <c r="BC6">
-        <v>0.823</v>
+        <v>0.831</v>
       </c>
       <c r="BD6">
-        <v>0.978</v>
+        <v>0.972</v>
       </c>
       <c r="BE6">
-        <v>0.233</v>
+        <v>0.24</v>
       </c>
       <c r="BF6">
         <v>-0.9485599924429405</v>
@@ -1781,10 +1781,10 @@
         <v>0.6770125502755524</v>
       </c>
       <c r="BH6">
-        <v>3.098748122655149</v>
+        <v>3.088222030379219</v>
       </c>
       <c r="BI6">
-        <v>0.7462303557851317</v>
+        <v>0.7475668565411295</v>
       </c>
     </row>
     <row r="7" spans="1:61">
@@ -1822,55 +1822,55 @@
         <v>0.4</v>
       </c>
       <c r="L7">
-        <v>0.6486298357467234</v>
+        <v>0.6479401728874485</v>
       </c>
       <c r="M7">
         <v>1</v>
       </c>
       <c r="N7">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="O7">
-        <v>0.4623482609156013</v>
+        <v>0.4611011081122637</v>
       </c>
       <c r="P7">
-        <v>0.64</v>
+        <v>0.62</v>
       </c>
       <c r="Q7">
         <v>6</v>
       </c>
       <c r="R7">
-        <v>14.47776709405768</v>
+        <v>14.4694074932179</v>
       </c>
       <c r="S7">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="T7">
-        <v>12.48</v>
+        <v>13.11</v>
       </c>
       <c r="U7">
-        <v>17.21905437244054</v>
+        <v>17.26166958327597</v>
       </c>
       <c r="V7">
-        <v>22.17</v>
+        <v>22.28</v>
       </c>
       <c r="W7">
         <v>0.01</v>
       </c>
       <c r="X7">
-        <v>0.2522164829264932</v>
+        <v>0.2525994733709277</v>
       </c>
       <c r="Y7">
         <v>0.5</v>
       </c>
       <c r="Z7">
-        <v>0.05</v>
+        <v>0.03</v>
       </c>
       <c r="AA7">
-        <v>0.2855445616463955</v>
+        <v>0.2400213215690779</v>
       </c>
       <c r="AB7">
-        <v>0.63</v>
+        <v>0.5</v>
       </c>
       <c r="AC7">
         <v>1.7</v>
@@ -1882,13 +1882,13 @@
         <v>2.56</v>
       </c>
       <c r="AF7">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="AG7">
         <v>1.98</v>
       </c>
       <c r="AH7">
-        <v>2.21</v>
+        <v>2.19</v>
       </c>
       <c r="AI7">
         <v>0.17</v>
@@ -1897,16 +1897,16 @@
         <v>0.25</v>
       </c>
       <c r="AK7">
-        <v>0.32</v>
+        <v>0.31</v>
       </c>
       <c r="AL7">
-        <v>6.24</v>
+        <v>6.55</v>
       </c>
       <c r="AM7">
-        <v>7.83</v>
+        <v>8.07</v>
       </c>
       <c r="AN7">
-        <v>11.09</v>
+        <v>11.14</v>
       </c>
       <c r="AO7">
         <v>0.25</v>
@@ -1915,49 +1915,49 @@
         <v>0.36</v>
       </c>
       <c r="AQ7">
-        <v>0.08</v>
+        <v>0.1</v>
       </c>
       <c r="AR7">
-        <v>0.22</v>
+        <v>0.28</v>
       </c>
       <c r="AS7">
-        <v>5.26</v>
+        <v>11.57</v>
       </c>
       <c r="AT7">
-        <v>0.1</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AU7">
-        <v>0.53</v>
+        <v>0.45</v>
       </c>
       <c r="AV7">
-        <v>1.26</v>
+        <v>1.01</v>
       </c>
       <c r="AW7">
-        <v>0.614</v>
+        <v>0.501</v>
       </c>
       <c r="AX7">
-        <v>0.216</v>
+        <v>0.292</v>
       </c>
       <c r="AY7">
-        <v>0.421</v>
+        <v>0.384</v>
       </c>
       <c r="AZ7">
-        <v>0.708</v>
+        <v>0.674</v>
       </c>
       <c r="BA7">
-        <v>1.265</v>
+        <v>1.306</v>
       </c>
       <c r="BB7">
-        <v>-0.125</v>
+        <v>-0.143</v>
       </c>
       <c r="BC7">
-        <v>0.901</v>
+        <v>0.914</v>
       </c>
       <c r="BD7">
-        <v>0.987</v>
+        <v>0.99</v>
       </c>
       <c r="BE7">
-        <v>0.226</v>
+        <v>0.237</v>
       </c>
       <c r="BF7">
         <v>-0.4581453659370775</v>
@@ -1966,10 +1966,10 @@
         <v>0.2290726829685387</v>
       </c>
       <c r="BH7">
-        <v>2.606119736556675</v>
+        <v>2.602812545434199</v>
       </c>
       <c r="BI7">
-        <v>0.3740894856558739</v>
+        <v>0.3728098099038761</v>
       </c>
     </row>
     <row r="8" spans="1:61">
@@ -2007,7 +2007,7 @@
         <v>0.05</v>
       </c>
       <c r="L8">
-        <v>0.212283270078021</v>
+        <v>0.2073273490603038</v>
       </c>
       <c r="M8">
         <v>0.6</v>
@@ -2016,46 +2016,46 @@
         <v>0.04</v>
       </c>
       <c r="O8">
-        <v>0.07015867855081925</v>
+        <v>0.06982746198657354</v>
       </c>
       <c r="P8">
         <v>0.11</v>
       </c>
       <c r="Q8">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="R8">
-        <v>60.51192085333134</v>
+        <v>63.00538730376422</v>
       </c>
       <c r="S8">
         <v>192</v>
       </c>
       <c r="T8">
-        <v>65.27</v>
+        <v>67.36</v>
       </c>
       <c r="U8">
-        <v>109.8108869965677</v>
+        <v>111.1115598238149</v>
       </c>
       <c r="V8">
-        <v>168.63</v>
+        <v>165.57</v>
       </c>
       <c r="W8">
         <v>0.01</v>
       </c>
       <c r="X8">
-        <v>0.2541403161082374</v>
+        <v>0.2539263938653233</v>
       </c>
       <c r="Y8">
         <v>0.5</v>
       </c>
       <c r="Z8">
-        <v>0.1</v>
+        <v>0.12</v>
       </c>
       <c r="AA8">
-        <v>0.2985706411386448</v>
+        <v>0.2769667731088494</v>
       </c>
       <c r="AB8">
-        <v>0.47</v>
+        <v>0.45</v>
       </c>
       <c r="AC8">
         <v>1.7</v>
@@ -2070,10 +2070,10 @@
         <v>1.27</v>
       </c>
       <c r="AG8">
-        <v>1.82</v>
+        <v>1.87</v>
       </c>
       <c r="AH8">
-        <v>2.66</v>
+        <v>2.72</v>
       </c>
       <c r="AI8">
         <v>0.02</v>
@@ -2085,13 +2085,13 @@
         <v>0.06</v>
       </c>
       <c r="AL8">
-        <v>32.63</v>
+        <v>33.68</v>
       </c>
       <c r="AM8">
-        <v>45.38</v>
+        <v>46.8</v>
       </c>
       <c r="AN8">
-        <v>84.31999999999999</v>
+        <v>82.78</v>
       </c>
       <c r="AO8">
         <v>0.25</v>
@@ -2103,46 +2103,46 @@
         <v>0.1</v>
       </c>
       <c r="AR8">
-        <v>0.2</v>
+        <v>0.22</v>
       </c>
       <c r="AS8">
-        <v>1.46</v>
+        <v>1.13</v>
       </c>
       <c r="AT8">
-        <v>0.2</v>
+        <v>0.24</v>
       </c>
       <c r="AU8">
-        <v>0.61</v>
+        <v>0.55</v>
       </c>
       <c r="AV8">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="AW8">
-        <v>0.165</v>
+        <v>0.168</v>
       </c>
       <c r="AX8">
-        <v>0.593</v>
+        <v>0.59</v>
       </c>
       <c r="AY8">
-        <v>0.246</v>
+        <v>0.248</v>
       </c>
       <c r="AZ8">
-        <v>0.518</v>
+        <v>0.525</v>
       </c>
       <c r="BA8">
-        <v>0.483</v>
+        <v>0.399</v>
       </c>
       <c r="BB8">
-        <v>0.305</v>
+        <v>0.369</v>
       </c>
       <c r="BC8">
-        <v>0.748</v>
+        <v>0.781</v>
       </c>
       <c r="BD8">
-        <v>0.949</v>
+        <v>0.948</v>
       </c>
       <c r="BE8">
-        <v>0.258</v>
+        <v>0.26</v>
       </c>
       <c r="BF8">
         <v>-1.753278948659991</v>
@@ -2151,10 +2151,10 @@
         <v>0.621226662447</v>
       </c>
       <c r="BH8">
-        <v>3.882104259325276</v>
+        <v>3.90342778264239</v>
       </c>
       <c r="BI8">
-        <v>0.6880890831832995</v>
+        <v>0.6780830303509365</v>
       </c>
     </row>
     <row r="9" spans="1:61">
@@ -2192,55 +2192,55 @@
         <v>0.2</v>
       </c>
       <c r="L9">
-        <v>0.4236982874701743</v>
+        <v>0.424653419252554</v>
       </c>
       <c r="M9">
         <v>0.8</v>
       </c>
       <c r="N9">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="O9">
-        <v>0.2359115589321722</v>
+        <v>0.2401266203477887</v>
       </c>
       <c r="P9">
-        <v>0.36</v>
+        <v>0.35</v>
       </c>
       <c r="Q9">
         <v>9</v>
       </c>
       <c r="R9">
-        <v>23.75669906766467</v>
+        <v>23.69402363738481</v>
       </c>
       <c r="S9">
         <v>53</v>
       </c>
       <c r="T9">
-        <v>21.42</v>
+        <v>21.24</v>
       </c>
       <c r="U9">
-        <v>30.82442396525587</v>
+        <v>30.43144508157107</v>
       </c>
       <c r="V9">
-        <v>41.4</v>
+        <v>40.1</v>
       </c>
       <c r="W9">
         <v>0.01</v>
       </c>
       <c r="X9">
-        <v>0.25553552695869</v>
+        <v>0.2561764960020633</v>
       </c>
       <c r="Y9">
         <v>0.5</v>
       </c>
       <c r="Z9">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="AA9">
-        <v>0.2611892027109871</v>
+        <v>0.2744298249933112</v>
       </c>
       <c r="AB9">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AC9">
         <v>1.7</v>
@@ -2252,10 +2252,10 @@
         <v>2.56</v>
       </c>
       <c r="AF9">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="AG9">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="AH9">
         <v>2.13</v>
@@ -2270,13 +2270,13 @@
         <v>0.18</v>
       </c>
       <c r="AL9">
-        <v>10.71</v>
+        <v>10.62</v>
       </c>
       <c r="AM9">
-        <v>13.79</v>
+        <v>13.81</v>
       </c>
       <c r="AN9">
-        <v>20.7</v>
+        <v>20.05</v>
       </c>
       <c r="AO9">
         <v>0.25</v>
@@ -2288,46 +2288,46 @@
         <v>0.1</v>
       </c>
       <c r="AR9">
-        <v>0.29</v>
+        <v>0.23</v>
       </c>
       <c r="AS9">
-        <v>5.83</v>
+        <v>4.29</v>
       </c>
       <c r="AT9">
-        <v>0.1</v>
+        <v>0.12</v>
       </c>
       <c r="AU9">
-        <v>0.47</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AV9">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AW9">
-        <v>0.368</v>
+        <v>0.341</v>
       </c>
       <c r="AX9">
-        <v>0.393</v>
+        <v>0.416</v>
       </c>
       <c r="AY9">
-        <v>0.312</v>
+        <v>0.328</v>
       </c>
       <c r="AZ9">
-        <v>0.602</v>
+        <v>0.604</v>
       </c>
       <c r="BA9">
-        <v>1.201</v>
+        <v>0.999</v>
       </c>
       <c r="BB9">
-        <v>-0.096</v>
+        <v>0</v>
       </c>
       <c r="BC9">
-        <v>0.901</v>
+        <v>0.877</v>
       </c>
       <c r="BD9">
-        <v>0.992</v>
+        <v>0.989</v>
       </c>
       <c r="BE9">
-        <v>0.21</v>
+        <v>0.224</v>
       </c>
       <c r="BF9">
         <v>-0.916290731874155</v>
@@ -2336,10 +2336,10 @@
         <v>0.3465735902799726</v>
       </c>
       <c r="BH9">
-        <v>3.063518120841473</v>
+        <v>3.062273804290784</v>
       </c>
       <c r="BI9">
-        <v>0.4505744866633468</v>
+        <v>0.4499334462890472</v>
       </c>
     </row>
     <row r="10" spans="1:61">
@@ -2377,55 +2377,55 @@
         <v>0.1</v>
       </c>
       <c r="L10">
-        <v>0.4864518932989964</v>
+        <v>0.4870625335568778</v>
       </c>
       <c r="M10">
         <v>1.5</v>
       </c>
       <c r="N10">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="O10">
-        <v>0.1363284421768528</v>
+        <v>0.125020320549345</v>
       </c>
       <c r="P10">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="Q10">
         <v>5</v>
       </c>
       <c r="R10">
-        <v>29.24925281693997</v>
+        <v>29.2147937202894</v>
       </c>
       <c r="S10">
         <v>97</v>
       </c>
       <c r="T10">
-        <v>33.79</v>
+        <v>34.97</v>
       </c>
       <c r="U10">
-        <v>54.60868709423248</v>
+        <v>54.69360063723625</v>
       </c>
       <c r="V10">
-        <v>80.2</v>
+        <v>79.3</v>
       </c>
       <c r="W10">
         <v>0.01</v>
       </c>
       <c r="X10">
-        <v>0.2326972717161555</v>
+        <v>0.2278320023474466</v>
       </c>
       <c r="Y10">
-        <v>0.45</v>
+        <v>0.44</v>
       </c>
       <c r="Z10">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="AA10">
-        <v>0.2611071265813333</v>
+        <v>0.2381115423824078</v>
       </c>
       <c r="AB10">
-        <v>0.49</v>
+        <v>0.42</v>
       </c>
       <c r="AC10">
         <v>1.7</v>
@@ -2437,31 +2437,31 @@
         <v>2.56</v>
       </c>
       <c r="AF10">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AG10">
-        <v>1.81</v>
+        <v>1.7</v>
       </c>
       <c r="AH10">
-        <v>2.35</v>
+        <v>2.21</v>
       </c>
       <c r="AI10">
         <v>0.04</v>
       </c>
       <c r="AJ10">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AK10">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AL10">
-        <v>16.9</v>
+        <v>17.49</v>
       </c>
       <c r="AM10">
-        <v>23.61</v>
+        <v>23.91</v>
       </c>
       <c r="AN10">
-        <v>40.1</v>
+        <v>39.65</v>
       </c>
       <c r="AO10">
         <v>0.25</v>
@@ -2470,49 +2470,49 @@
         <v>0.36</v>
       </c>
       <c r="AQ10">
-        <v>0.11</v>
+        <v>0.13</v>
       </c>
       <c r="AR10">
-        <v>0.26</v>
+        <v>0.33</v>
       </c>
       <c r="AS10">
-        <v>2.07</v>
+        <v>1.93</v>
       </c>
       <c r="AT10">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="AU10">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AV10">
+        <v>0.84</v>
+      </c>
+      <c r="AW10">
+        <v>0.142</v>
+      </c>
+      <c r="AX10">
+        <v>0.623</v>
+      </c>
+      <c r="AY10">
+        <v>0.187</v>
+      </c>
+      <c r="AZ10">
+        <v>0.43</v>
+      </c>
+      <c r="BA10">
+        <v>0.495</v>
+      </c>
+      <c r="BB10">
+        <v>0.297</v>
+      </c>
+      <c r="BC10">
+        <v>0.836</v>
+      </c>
+      <c r="BD10">
         <v>0.97</v>
       </c>
-      <c r="AW10">
-        <v>0.121</v>
-      </c>
-      <c r="AX10">
-        <v>0.651</v>
-      </c>
-      <c r="AY10">
-        <v>0.207</v>
-      </c>
-      <c r="AZ10">
-        <v>0.454</v>
-      </c>
-      <c r="BA10">
-        <v>0.716</v>
-      </c>
-      <c r="BB10">
-        <v>0.154</v>
-      </c>
-      <c r="BC10">
-        <v>0.884</v>
-      </c>
-      <c r="BD10">
-        <v>0.983</v>
-      </c>
       <c r="BE10">
-        <v>0.223</v>
+        <v>0.232</v>
       </c>
       <c r="BF10">
         <v>-0.9485599924429405</v>
@@ -2521,10 +2521,10 @@
         <v>0.6770125502755524</v>
       </c>
       <c r="BH10">
-        <v>3.095807733111553</v>
+        <v>3.1022208808515</v>
       </c>
       <c r="BI10">
-        <v>0.7419167006490941</v>
+        <v>0.7343666690800769</v>
       </c>
     </row>
     <row r="11" spans="1:61">
@@ -2562,7 +2562,7 @@
         <v>0.4</v>
       </c>
       <c r="L11">
-        <v>0.6517206334362765</v>
+        <v>0.6529002301751102</v>
       </c>
       <c r="M11">
         <v>1</v>
@@ -2571,43 +2571,43 @@
         <v>0.35</v>
       </c>
       <c r="O11">
-        <v>0.465771768765134</v>
+        <v>0.4693665370560364</v>
       </c>
       <c r="P11">
         <v>0.65</v>
       </c>
       <c r="Q11">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R11">
-        <v>14.52141666167883</v>
+        <v>14.50660702173137</v>
       </c>
       <c r="S11">
         <v>29</v>
       </c>
       <c r="T11">
-        <v>12.83</v>
+        <v>12.14</v>
       </c>
       <c r="U11">
-        <v>17.14505161525011</v>
+        <v>17.04876902778649</v>
       </c>
       <c r="V11">
-        <v>22.15</v>
+        <v>21.38</v>
       </c>
       <c r="W11">
         <v>0.01</v>
       </c>
       <c r="X11">
-        <v>0.229676384418259</v>
+        <v>0.2262104312082857</v>
       </c>
       <c r="Y11">
-        <v>0.45</v>
+        <v>0.44</v>
       </c>
       <c r="Z11">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="AA11">
-        <v>0.2152108485992011</v>
+        <v>0.2137123687853013</v>
       </c>
       <c r="AB11">
         <v>0.5</v>
@@ -2622,31 +2622,31 @@
         <v>2.56</v>
       </c>
       <c r="AF11">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AG11">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="AH11">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="AI11">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="AJ11">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="AK11">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="AL11">
-        <v>6.41</v>
+        <v>6.07</v>
       </c>
       <c r="AM11">
-        <v>7.87</v>
+        <v>7.65</v>
       </c>
       <c r="AN11">
-        <v>11.07</v>
+        <v>10.69</v>
       </c>
       <c r="AO11">
         <v>0.25</v>
@@ -2658,46 +2658,46 @@
         <v>0.11</v>
       </c>
       <c r="AR11">
-        <v>0.39</v>
+        <v>0.37</v>
       </c>
       <c r="AS11">
-        <v>7.3</v>
+        <v>6.43</v>
       </c>
       <c r="AT11">
         <v>0.09</v>
       </c>
       <c r="AU11">
-        <v>0.37</v>
+        <v>0.39</v>
       </c>
       <c r="AV11">
-        <v>1</v>
+        <v>0.99</v>
       </c>
       <c r="AW11">
-        <v>0.556</v>
+        <v>0.526</v>
       </c>
       <c r="AX11">
-        <v>0.254</v>
+        <v>0.275</v>
       </c>
       <c r="AY11">
-        <v>0.397</v>
+        <v>0.408</v>
       </c>
       <c r="AZ11">
-        <v>0.705</v>
+        <v>0.722</v>
       </c>
       <c r="BA11">
-        <v>1.195</v>
+        <v>1.185</v>
       </c>
       <c r="BB11">
-        <v>-0.093</v>
+        <v>-0.089</v>
       </c>
       <c r="BC11">
-        <v>0.886</v>
+        <v>0.921</v>
       </c>
       <c r="BD11">
-        <v>0.992</v>
+        <v>0.994</v>
       </c>
       <c r="BE11">
-        <v>0.229</v>
+        <v>0.24</v>
       </c>
       <c r="BF11">
         <v>-0.4581453659370775</v>
@@ -2706,10 +2706,10 @@
         <v>0.2290726829685387</v>
       </c>
       <c r="BH11">
-        <v>2.613807537532667</v>
+        <v>2.607745909857972</v>
       </c>
       <c r="BI11">
-        <v>0.370394782327945</v>
+        <v>0.3735361634651526</v>
       </c>
     </row>
     <row r="12" spans="1:61">
@@ -2747,7 +2747,7 @@
         <v>0.05</v>
       </c>
       <c r="L12">
-        <v>0.2109826596265518</v>
+        <v>0.2099822824208502</v>
       </c>
       <c r="M12">
         <v>0.6</v>
@@ -2756,7 +2756,7 @@
         <v>0.04</v>
       </c>
       <c r="O12">
-        <v>0.06932589461148007</v>
+        <v>0.06887806502294574</v>
       </c>
       <c r="P12">
         <v>0.11</v>
@@ -2765,37 +2765,37 @@
         <v>13</v>
       </c>
       <c r="R12">
-        <v>62.82688397632828</v>
+        <v>61.37698568406925</v>
       </c>
       <c r="S12">
-        <v>197</v>
+        <v>189</v>
       </c>
       <c r="T12">
-        <v>66.26000000000001</v>
+        <v>63.26</v>
       </c>
       <c r="U12">
-        <v>113.3175101824582</v>
+        <v>108.1052775074143</v>
       </c>
       <c r="V12">
-        <v>169.16</v>
+        <v>162.53</v>
       </c>
       <c r="W12">
         <v>0.01</v>
       </c>
       <c r="X12">
-        <v>0.2308807143702199</v>
+        <v>0.2245029377217642</v>
       </c>
       <c r="Y12">
+        <v>0.44</v>
+      </c>
+      <c r="Z12">
+        <v>0.1</v>
+      </c>
+      <c r="AA12">
+        <v>0.2626565768984048</v>
+      </c>
+      <c r="AB12">
         <v>0.45</v>
-      </c>
-      <c r="Z12">
-        <v>0.11</v>
-      </c>
-      <c r="AA12">
-        <v>0.2787940059164546</v>
-      </c>
-      <c r="AB12">
-        <v>0.48</v>
       </c>
       <c r="AC12">
         <v>1.7</v>
@@ -2807,13 +2807,13 @@
         <v>2.56</v>
       </c>
       <c r="AF12">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="AG12">
-        <v>1.87</v>
+        <v>1.77</v>
       </c>
       <c r="AH12">
-        <v>2.79</v>
+        <v>2.63</v>
       </c>
       <c r="AI12">
         <v>0.02</v>
@@ -2825,13 +2825,13 @@
         <v>0.06</v>
       </c>
       <c r="AL12">
-        <v>33.13</v>
+        <v>31.63</v>
       </c>
       <c r="AM12">
-        <v>46.27</v>
+        <v>44.14</v>
       </c>
       <c r="AN12">
-        <v>84.58</v>
+        <v>81.26000000000001</v>
       </c>
       <c r="AO12">
         <v>0.25</v>
@@ -2840,49 +2840,49 @@
         <v>0.36</v>
       </c>
       <c r="AQ12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="AR12">
-        <v>0.22</v>
+        <v>0.25</v>
       </c>
       <c r="AS12">
-        <v>1.29</v>
+        <v>1.68</v>
       </c>
       <c r="AT12">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AU12">
-        <v>0.55</v>
+        <v>0.52</v>
       </c>
       <c r="AV12">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="AW12">
-        <v>0.171</v>
+        <v>0.184</v>
       </c>
       <c r="AX12">
-        <v>0.587</v>
+        <v>0.571</v>
       </c>
       <c r="AY12">
-        <v>0.252</v>
+        <v>0.25</v>
       </c>
       <c r="AZ12">
-        <v>0.522</v>
+        <v>0.528</v>
       </c>
       <c r="BA12">
-        <v>0.507</v>
+        <v>0.487</v>
       </c>
       <c r="BB12">
-        <v>0.288</v>
+        <v>0.302</v>
       </c>
       <c r="BC12">
-        <v>0.783</v>
+        <v>0.758</v>
       </c>
       <c r="BD12">
-        <v>0.949</v>
+        <v>0.953</v>
       </c>
       <c r="BE12">
-        <v>0.219</v>
+        <v>0.224</v>
       </c>
       <c r="BF12">
         <v>-1.753278948659991</v>
@@ -2891,10 +2891,10 @@
         <v>0.621226662447</v>
       </c>
       <c r="BH12">
-        <v>3.920593977603936</v>
+        <v>3.891465863901269</v>
       </c>
       <c r="BI12">
-        <v>0.6809279546647162</v>
+        <v>0.6757166739748789</v>
       </c>
     </row>
     <row r="13" spans="1:61">
@@ -2932,7 +2932,7 @@
         <v>0.2</v>
       </c>
       <c r="L13">
-        <v>0.4230812423692322</v>
+        <v>0.422741199952604</v>
       </c>
       <c r="M13">
         <v>0.8</v>
@@ -2941,46 +2941,46 @@
         <v>0.17</v>
       </c>
       <c r="O13">
-        <v>0.2361957707524948</v>
+        <v>0.2421986027428149</v>
       </c>
       <c r="P13">
-        <v>0.34</v>
+        <v>0.36</v>
       </c>
       <c r="Q13">
         <v>9</v>
       </c>
       <c r="R13">
-        <v>24.05920714754135</v>
+        <v>23.74182397781664</v>
       </c>
       <c r="S13">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="T13">
-        <v>21.8</v>
+        <v>20.47</v>
       </c>
       <c r="U13">
-        <v>30.66598474767515</v>
+        <v>30.13125523787879</v>
       </c>
       <c r="V13">
-        <v>40.52</v>
+        <v>40.49</v>
       </c>
       <c r="W13">
         <v>0.01</v>
       </c>
       <c r="X13">
-        <v>0.2327522559235002</v>
+        <v>0.2245054006527132</v>
       </c>
       <c r="Y13">
-        <v>0.45</v>
+        <v>0.44</v>
       </c>
       <c r="Z13">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="AA13">
-        <v>0.2376481788645683</v>
+        <v>0.206722218160354</v>
       </c>
       <c r="AB13">
-        <v>0.48</v>
+        <v>0.41</v>
       </c>
       <c r="AC13">
         <v>1.7</v>
@@ -2992,31 +2992,31 @@
         <v>2.56</v>
       </c>
       <c r="AF13">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="AG13">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="AH13">
-        <v>2.16</v>
+        <v>2.13</v>
       </c>
       <c r="AI13">
         <v>0.08</v>
       </c>
       <c r="AJ13">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="AK13">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="AL13">
-        <v>10.9</v>
+        <v>10.23</v>
       </c>
       <c r="AM13">
-        <v>13.94</v>
+        <v>13.4</v>
       </c>
       <c r="AN13">
-        <v>20.26</v>
+        <v>20.25</v>
       </c>
       <c r="AO13">
         <v>0.25</v>
@@ -3025,49 +3025,49 @@
         <v>0.36</v>
       </c>
       <c r="AQ13">
+        <v>0.14</v>
+      </c>
+      <c r="AR13">
+        <v>0.4</v>
+      </c>
+      <c r="AS13">
+        <v>4.41</v>
+      </c>
+      <c r="AT13">
         <v>0.12</v>
       </c>
-      <c r="AR13">
-        <v>0.31</v>
-      </c>
-      <c r="AS13">
-        <v>5.63</v>
-      </c>
-      <c r="AT13">
-        <v>0.11</v>
-      </c>
       <c r="AU13">
-        <v>0.45</v>
+        <v>0.4</v>
       </c>
       <c r="AV13">
-        <v>0.96</v>
+        <v>0.82</v>
       </c>
       <c r="AW13">
-        <v>0.318</v>
+        <v>0.371</v>
       </c>
       <c r="AX13">
-        <v>0.436</v>
+        <v>0.391</v>
       </c>
       <c r="AY13">
-        <v>0.312</v>
+        <v>0.346</v>
       </c>
       <c r="AZ13">
-        <v>0.586</v>
+        <v>0.636</v>
       </c>
       <c r="BA13">
-        <v>0.995</v>
+        <v>0.773</v>
       </c>
       <c r="BB13">
-        <v>0.003</v>
+        <v>0.121</v>
       </c>
       <c r="BC13">
-        <v>0.951</v>
+        <v>0.897</v>
       </c>
       <c r="BD13">
-        <v>0.997</v>
+        <v>0.99</v>
       </c>
       <c r="BE13">
-        <v>0.199</v>
+        <v>0.221</v>
       </c>
       <c r="BF13">
         <v>-0.916290731874155</v>
@@ -3076,10 +3076,10 @@
         <v>0.3465735902799726</v>
       </c>
       <c r="BH13">
-        <v>3.072900550368233</v>
+        <v>3.056190464506186</v>
       </c>
       <c r="BI13">
-        <v>0.4604666068100136</v>
+        <v>0.4576701191362917</v>
       </c>
     </row>
     <row r="14" spans="1:61">
@@ -3117,7 +3117,7 @@
         <v>0.1</v>
       </c>
       <c r="L14">
-        <v>0.4864702928984845</v>
+        <v>0.4805689629580134</v>
       </c>
       <c r="M14">
         <v>1.5</v>
@@ -3126,7 +3126,7 @@
         <v>0.08</v>
       </c>
       <c r="O14">
-        <v>0.126824138109385</v>
+        <v>0.1308140663636755</v>
       </c>
       <c r="P14">
         <v>0.2</v>
@@ -3135,37 +3135,37 @@
         <v>5</v>
       </c>
       <c r="R14">
-        <v>28.52658015627107</v>
+        <v>28.84921708958573</v>
       </c>
       <c r="S14">
         <v>96</v>
       </c>
       <c r="T14">
-        <v>34.74</v>
+        <v>34.28</v>
       </c>
       <c r="U14">
-        <v>53.22749973267759</v>
+        <v>52.57367200356111</v>
       </c>
       <c r="V14">
-        <v>77.77</v>
+        <v>77.73999999999999</v>
       </c>
       <c r="W14">
         <v>0.03</v>
       </c>
       <c r="X14">
-        <v>0.1399858510101243</v>
+        <v>0.1411158538218078</v>
       </c>
       <c r="Y14">
         <v>0.25</v>
       </c>
       <c r="Z14">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="AA14">
-        <v>0.1368375273232987</v>
+        <v>0.1557510637466443</v>
       </c>
       <c r="AB14">
-        <v>0.25</v>
+        <v>0.27</v>
       </c>
       <c r="AC14">
         <v>1.7</v>
@@ -3177,13 +3177,13 @@
         <v>2.56</v>
       </c>
       <c r="AF14">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="AG14">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="AH14">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="AI14">
         <v>0.04</v>
@@ -3195,13 +3195,13 @@
         <v>0.1</v>
       </c>
       <c r="AL14">
-        <v>17.37</v>
+        <v>17.14</v>
       </c>
       <c r="AM14">
-        <v>23.89</v>
+        <v>23.34</v>
       </c>
       <c r="AN14">
-        <v>38.88</v>
+        <v>38.87</v>
       </c>
       <c r="AO14">
         <v>0.25</v>
@@ -3210,49 +3210,49 @@
         <v>0.36</v>
       </c>
       <c r="AQ14">
-        <v>0.26</v>
+        <v>0.22</v>
       </c>
       <c r="AR14">
-        <v>0.96</v>
+        <v>0.72</v>
       </c>
       <c r="AS14">
-        <v>6.16</v>
+        <v>4.98</v>
       </c>
       <c r="AT14">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="AU14">
-        <v>0.27</v>
+        <v>0.3</v>
       </c>
       <c r="AV14">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="AW14">
-        <v>0.135</v>
+        <v>0.133</v>
       </c>
       <c r="AX14">
-        <v>0.632</v>
+        <v>0.636</v>
       </c>
       <c r="AY14">
-        <v>0.174</v>
+        <v>0.2</v>
       </c>
       <c r="AZ14">
-        <v>0.409</v>
+        <v>0.453</v>
       </c>
       <c r="BA14">
-        <v>0.776</v>
+        <v>0.801</v>
       </c>
       <c r="BB14">
-        <v>0.119</v>
+        <v>0.105</v>
       </c>
       <c r="BC14">
-        <v>0.924</v>
+        <v>0.863</v>
       </c>
       <c r="BD14">
-        <v>0.993</v>
+        <v>0.986</v>
       </c>
       <c r="BE14">
-        <v>0.01</v>
+        <v>0.008</v>
       </c>
       <c r="BF14">
         <v>-0.9485599924429405</v>
@@ -3261,10 +3261,10 @@
         <v>0.6770125502755524</v>
       </c>
       <c r="BH14">
-        <v>3.084408953536393</v>
+        <v>3.083713219634165</v>
       </c>
       <c r="BI14">
-        <v>0.7380946888154623</v>
+        <v>0.7386854500932691</v>
       </c>
     </row>
     <row r="15" spans="1:61">
@@ -3302,7 +3302,7 @@
         <v>0.4</v>
       </c>
       <c r="L15">
-        <v>0.6484093782193361</v>
+        <v>0.6481525371047359</v>
       </c>
       <c r="M15">
         <v>1</v>
@@ -3311,34 +3311,34 @@
         <v>0.35</v>
       </c>
       <c r="O15">
-        <v>0.4651078483125608</v>
+        <v>0.4667458582529379</v>
       </c>
       <c r="P15">
-        <v>0.62</v>
+        <v>0.65</v>
       </c>
       <c r="Q15">
         <v>6</v>
       </c>
       <c r="R15">
-        <v>14.33655999630412</v>
+        <v>14.351724252805</v>
       </c>
       <c r="S15">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="T15">
-        <v>12.91</v>
+        <v>12.59</v>
       </c>
       <c r="U15">
-        <v>17.02370390314845</v>
+        <v>17.15917999496488</v>
       </c>
       <c r="V15">
-        <v>22.08</v>
+        <v>21.56</v>
       </c>
       <c r="W15">
         <v>0.03</v>
       </c>
       <c r="X15">
-        <v>0.1391102301635943</v>
+        <v>0.1390543802614168</v>
       </c>
       <c r="Y15">
         <v>0.25</v>
@@ -3347,10 +3347,10 @@
         <v>0.05</v>
       </c>
       <c r="AA15">
-        <v>0.1270302348915198</v>
+        <v>0.1387787023035832</v>
       </c>
       <c r="AB15">
-        <v>0.25</v>
+        <v>0.27</v>
       </c>
       <c r="AC15">
         <v>1.7</v>
@@ -3362,13 +3362,13 @@
         <v>2.56</v>
       </c>
       <c r="AF15">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="AG15">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="AH15">
-        <v>2.18</v>
+        <v>2.23</v>
       </c>
       <c r="AI15">
         <v>0.17</v>
@@ -3377,16 +3377,16 @@
         <v>0.25</v>
       </c>
       <c r="AK15">
-        <v>0.31</v>
+        <v>0.33</v>
       </c>
       <c r="AL15">
-        <v>6.45</v>
+        <v>6.29</v>
       </c>
       <c r="AM15">
-        <v>7.94</v>
+        <v>7.81</v>
       </c>
       <c r="AN15">
-        <v>11.04</v>
+        <v>10.78</v>
       </c>
       <c r="AO15">
         <v>0.25</v>
@@ -3395,49 +3395,49 @@
         <v>0.36</v>
       </c>
       <c r="AQ15">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AR15">
-        <v>0.98</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AS15">
-        <v>7.05</v>
+        <v>6.04</v>
       </c>
       <c r="AT15">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="AU15">
-        <v>0.24</v>
+        <v>0.26</v>
       </c>
       <c r="AV15">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="AW15">
-        <v>0.503</v>
+        <v>0.592</v>
       </c>
       <c r="AX15">
-        <v>0.291</v>
+        <v>0.231</v>
       </c>
       <c r="AY15">
-        <v>0.4</v>
+        <v>0.415</v>
       </c>
       <c r="AZ15">
-        <v>0.6860000000000001</v>
+        <v>0.722</v>
       </c>
       <c r="BA15">
-        <v>1.048</v>
+        <v>1.087</v>
       </c>
       <c r="BB15">
-        <v>-0.024</v>
+        <v>-0.043</v>
       </c>
       <c r="BC15">
-        <v>0.904</v>
+        <v>0.96</v>
       </c>
       <c r="BD15">
-        <v>0.993</v>
+        <v>0.998</v>
       </c>
       <c r="BE15">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="BF15">
         <v>-0.4581453659370775</v>
@@ -3446,10 +3446,10 @@
         <v>0.2290726829685387</v>
       </c>
       <c r="BH15">
-        <v>2.596144591125226</v>
+        <v>2.598640866015968</v>
       </c>
       <c r="BI15">
-        <v>0.3763660846384678</v>
+        <v>0.3764940239991139</v>
       </c>
     </row>
     <row r="16" spans="1:61">
@@ -3487,7 +3487,7 @@
         <v>0.05</v>
       </c>
       <c r="L16">
-        <v>0.2108794154840056</v>
+        <v>0.2113629535890721</v>
       </c>
       <c r="M16">
         <v>0.6</v>
@@ -3496,7 +3496,7 @@
         <v>0.04</v>
       </c>
       <c r="O16">
-        <v>0.06982456950926232</v>
+        <v>0.06920107231329092</v>
       </c>
       <c r="P16">
         <v>0.11</v>
@@ -3505,34 +3505,34 @@
         <v>12</v>
       </c>
       <c r="R16">
-        <v>61.45521805003185</v>
+        <v>60.45852839384596</v>
       </c>
       <c r="S16">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="T16">
-        <v>65.48999999999999</v>
+        <v>63.32</v>
       </c>
       <c r="U16">
-        <v>112.1005667755153</v>
+        <v>107.1531962331294</v>
       </c>
       <c r="V16">
-        <v>168.72</v>
+        <v>163.09</v>
       </c>
       <c r="W16">
         <v>0.03</v>
       </c>
       <c r="X16">
-        <v>0.13970337181353</v>
+        <v>0.1398407976766043</v>
       </c>
       <c r="Y16">
         <v>0.25</v>
       </c>
       <c r="Z16">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="AA16">
-        <v>0.1697774851773167</v>
+        <v>0.1719450266516626</v>
       </c>
       <c r="AB16">
         <v>0.3</v>
@@ -3547,13 +3547,13 @@
         <v>2.56</v>
       </c>
       <c r="AF16">
-        <v>1.27</v>
+        <v>1.21</v>
       </c>
       <c r="AG16">
-        <v>1.85</v>
+        <v>1.78</v>
       </c>
       <c r="AH16">
-        <v>2.77</v>
+        <v>2.63</v>
       </c>
       <c r="AI16">
         <v>0.02</v>
@@ -3562,16 +3562,16 @@
         <v>0.04</v>
       </c>
       <c r="AK16">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="AL16">
-        <v>32.74</v>
+        <v>31.66</v>
       </c>
       <c r="AM16">
-        <v>45.85</v>
+        <v>45.33</v>
       </c>
       <c r="AN16">
-        <v>84.36</v>
+        <v>81.54000000000001</v>
       </c>
       <c r="AO16">
         <v>0.25</v>
@@ -3580,49 +3580,49 @@
         <v>0.36</v>
       </c>
       <c r="AQ16">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="AR16">
-        <v>0.55</v>
+        <v>0.57</v>
       </c>
       <c r="AS16">
-        <v>3.15</v>
+        <v>2.71</v>
       </c>
       <c r="AT16">
-        <v>0.14</v>
+        <v>0.16</v>
       </c>
       <c r="AU16">
         <v>0.33</v>
       </c>
       <c r="AV16">
-        <v>0.61</v>
+        <v>0.6</v>
       </c>
       <c r="AW16">
-        <v>0.168</v>
+        <v>0.169</v>
       </c>
       <c r="AX16">
-        <v>0.59</v>
+        <v>0.589</v>
       </c>
       <c r="AY16">
-        <v>0.254</v>
+        <v>0.247</v>
       </c>
       <c r="AZ16">
-        <v>0.524</v>
+        <v>0.515</v>
       </c>
       <c r="BA16">
-        <v>0.793</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="BB16">
-        <v>0.11</v>
+        <v>0.173</v>
       </c>
       <c r="BC16">
-        <v>0.793</v>
+        <v>0.765</v>
       </c>
       <c r="BD16">
-        <v>0.963</v>
+        <v>0.951</v>
       </c>
       <c r="BE16">
-        <v>0.033</v>
+        <v>0.038</v>
       </c>
       <c r="BF16">
         <v>-1.753278948659991</v>
@@ -3631,10 +3631,10 @@
         <v>0.621226662447</v>
       </c>
       <c r="BH16">
-        <v>3.894476298196476</v>
+        <v>3.886108093300067</v>
       </c>
       <c r="BI16">
-        <v>0.6947981732991657</v>
+        <v>0.6843592543293426</v>
       </c>
     </row>
     <row r="17" spans="1:61">
@@ -3672,43 +3672,43 @@
         <v>0.2</v>
       </c>
       <c r="L17">
-        <v>0.4224313219804622</v>
+        <v>0.423049959809711</v>
       </c>
       <c r="M17">
         <v>0.8</v>
       </c>
       <c r="N17">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="O17">
-        <v>0.2386175184861667</v>
+        <v>0.2445081407626339</v>
       </c>
       <c r="P17">
         <v>0.36</v>
       </c>
       <c r="Q17">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="R17">
-        <v>23.49796978989266</v>
+        <v>23.64759739034131</v>
       </c>
       <c r="S17">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="T17">
-        <v>20.98</v>
+        <v>20.52</v>
       </c>
       <c r="U17">
-        <v>29.87142693580196</v>
+        <v>29.92312010886883</v>
       </c>
       <c r="V17">
-        <v>40.01</v>
+        <v>40.54</v>
       </c>
       <c r="W17">
         <v>0.03</v>
       </c>
       <c r="X17">
-        <v>0.1393518746655876</v>
+        <v>0.1395958173584682</v>
       </c>
       <c r="Y17">
         <v>0.25</v>
@@ -3717,7 +3717,7 @@
         <v>0.05</v>
       </c>
       <c r="AA17">
-        <v>0.1388556830292542</v>
+        <v>0.1378296194926305</v>
       </c>
       <c r="AB17">
         <v>0.26</v>
@@ -3732,31 +3732,31 @@
         <v>2.56</v>
       </c>
       <c r="AF17">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="AG17">
-        <v>1.77</v>
+        <v>1.81</v>
       </c>
       <c r="AH17">
-        <v>2.09</v>
+        <v>2.14</v>
       </c>
       <c r="AI17">
         <v>0.08</v>
       </c>
       <c r="AJ17">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="AK17">
         <v>0.18</v>
       </c>
       <c r="AL17">
-        <v>10.49</v>
+        <v>10.26</v>
       </c>
       <c r="AM17">
-        <v>13.49</v>
+        <v>13.28</v>
       </c>
       <c r="AN17">
-        <v>20.01</v>
+        <v>20.27</v>
       </c>
       <c r="AO17">
         <v>0.25</v>
@@ -3765,49 +3765,49 @@
         <v>0.36</v>
       </c>
       <c r="AQ17">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="AR17">
-        <v>0.9</v>
+        <v>0.87</v>
       </c>
       <c r="AS17">
-        <v>6.28</v>
+        <v>6.93</v>
       </c>
       <c r="AT17">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AU17">
         <v>0.27</v>
       </c>
       <c r="AV17">
-        <v>0.53</v>
+        <v>0.51</v>
       </c>
       <c r="AW17">
-        <v>0.411</v>
+        <v>0.388</v>
       </c>
       <c r="AX17">
-        <v>0.359</v>
+        <v>0.377</v>
       </c>
       <c r="AY17">
-        <v>0.336</v>
+        <v>0.353</v>
       </c>
       <c r="AZ17">
-        <v>0.617</v>
+        <v>0.655</v>
       </c>
       <c r="BA17">
-        <v>0.96</v>
+        <v>0.88</v>
       </c>
       <c r="BB17">
-        <v>0.02</v>
+        <v>0.062</v>
       </c>
       <c r="BC17">
-        <v>0.968</v>
+        <v>0.93</v>
       </c>
       <c r="BD17">
-        <v>0.998</v>
+        <v>0.995</v>
       </c>
       <c r="BE17">
-        <v>0.004</v>
+        <v>0.007</v>
       </c>
       <c r="BF17">
         <v>-0.916290731874155</v>
@@ -3816,10 +3816,10 @@
         <v>0.3465735902799726</v>
       </c>
       <c r="BH17">
-        <v>3.049438453683126</v>
+        <v>3.05689020936319</v>
       </c>
       <c r="BI17">
-        <v>0.4496065896265531</v>
+        <v>0.4584121859681733</v>
       </c>
     </row>
   </sheetData>
